--- a/data/inputs/sw3_validation.xlsx
+++ b/data/inputs/sw3_validation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carolineadkins/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF0B86E-CBDF-854E-A6C2-A8B94A718F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2D10A4-0E66-004A-9C3A-74BACDB6917A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="28400" windowHeight="21680" xr2:uid="{DD733A40-C352-434B-90DD-0C52971768EC}"/>
+    <workbookView xWindow="17800" yWindow="-26680" windowWidth="28400" windowHeight="21000" activeTab="6" xr2:uid="{DD733A40-C352-434B-90DD-0C52971768EC}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="12" r:id="rId1"/>
@@ -38,7 +38,7 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version warnBelowVersion="2" setVersion="2"/>
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="311">
   <si>
     <t>Major End-Use Markets</t>
   </si>
@@ -142,9 +142,6 @@
   </si>
   <si>
     <t>Water treatment</t>
-  </si>
-  <si>
-    <t>(1) Source: Ullmann's Encyclopedia for Industrial Chemistry, Bromine</t>
   </si>
   <si>
     <t>Butyl Rubber</t>
@@ -194,7 +191,7 @@
         <b/>
         <vertAlign val="superscript"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow (Body)"/>
       </rPr>
       <t>1</t>
@@ -209,7 +206,7 @@
         <b/>
         <vertAlign val="superscript"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow (Body)"/>
       </rPr>
       <t>1</t>
@@ -227,7 +224,7 @@
         <b/>
         <vertAlign val="superscript"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow (Body)"/>
       </rPr>
       <t>1</t>
@@ -312,9 +309,6 @@
     <t>Benchmark Demand (kt)</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>BaSO4</t>
   </si>
   <si>
@@ -342,9 +336,6 @@
     <t>Market Reports World, Borates Market Size, Share, Growth, and Industry Analysis, By Type (Borax, Boric Acid, Ulexite), By Application (Glass &amp; Ceramics, Agriculture, Detergents), Regional Insights and Forecast to 2033</t>
   </si>
   <si>
-    <t xml:space="preserve">Market Reports World, Barite Products Market Size, Share, Growth, and Industry Analysis, By Type (Up to Grade 3.9, Grade 4.0, Grade 4.1, Grade 4.2, Grade 4.3, Grade above 4.3), By Application (Drilling Industry (Rig), Medical Industry, Rubber &amp; Plastics, </t>
-  </si>
-  <si>
     <t>represents US consumption of bromine when it was last reported in 2006</t>
   </si>
   <si>
@@ -363,12 +354,6 @@
     <t>EPA Water Treatment Chemical Supply Chain Profile, Hydrochloric Acid</t>
   </si>
   <si>
-    <t>represnts US consumption of liquid anhydrous hydrogen fluoride (2024)</t>
-  </si>
-  <si>
-    <t>Market Growth Reports, Liquid Anhydrous Hydrogen Fluoride Market Report is Segmented by Types (99.99 AHF, 99.90 AHF, 99.70 AHF), Application (Chemical Industry, Mining &amp; Metallurgical, Etching, Pharmaceuticals, Others), and Geography (North America, Europ</t>
-  </si>
-  <si>
     <t>represents lithium content of reported US lithium carbonate equivalent consumption in 2024</t>
   </si>
   <si>
@@ -390,9 +375,6 @@
     <t>EPA Water Treatment Chemical Supply Chain Profile, Sodium Hydroxide</t>
   </si>
   <si>
-    <t>represnts P2O5 content of phosphate rock sold or used by producers (2023)</t>
-  </si>
-  <si>
     <t>USGS Minerals Yearbook 2023, Phosphate Rock</t>
   </si>
   <si>
@@ -400,9 +382,6 @@
   </si>
   <si>
     <t>represents barite consumption for oil and gas industry in North America (2025)</t>
-  </si>
-  <si>
-    <t>represents borate consumption in North America (2024)</t>
   </si>
   <si>
     <t>Disaggregation Proxies</t>
@@ -587,7 +566,7 @@
         <b/>
         <vertAlign val="superscript"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow (Body)"/>
       </rPr>
       <t>1</t>
@@ -659,7 +638,7 @@
     </r>
   </si>
   <si>
-    <t>(1) Districts based on those in USGS Minerals Yearbook 2023, Cement. Districts with sub-state resolution (e.g. Texas, northern) are aggregated to the state level to ensure consistency in tier resolution</t>
+    <t>(1) Districts based on those in USGS Minerals Yearbook 2023, Cement. Districts with sub-state resolution (e.g. Texas, northern) are aggregated to the state level to ensure consistency in tier resolution.</t>
   </si>
   <si>
     <t>Tier 1: Direct Scale Proxy</t>
@@ -679,7 +658,7 @@
         <b/>
         <vertAlign val="superscript"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow (Body)"/>
       </rPr>
       <t>1</t>
@@ -700,7 +679,7 @@
         <b/>
         <vertAlign val="subscript"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow (Body)"/>
       </rPr>
       <t>2</t>
@@ -709,7 +688,7 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
@@ -867,9 +846,6 @@
     <t>HOLCIM (US) INC. D/B/A LAFARGE ALPENA</t>
   </si>
   <si>
-    <t>HOLCIM (US) INC. DEVIL\S SLIDE PLANT</t>
-  </si>
-  <si>
     <t>HOLCIM (US) INC JOPPA PLANT</t>
   </si>
   <si>
@@ -942,9 +918,6 @@
     <t>NEVADA CEMENT COMPANY</t>
   </si>
   <si>
-    <t>PHOENIX CEMENT COMPANY\S CLARKDALE FACILITY</t>
-  </si>
-  <si>
     <t>RIVER CEMENT COMPANY DBA BUZZI UNICEM USA</t>
   </si>
   <si>
@@ -981,22 +954,7 @@
     <t>(1) Source: US EPA Greenhouse Gas Reporting Program</t>
   </si>
   <si>
-    <r>
-      <t>Carbon Dioxide Emissions from Cement Production Facilities in 2023, by Facility</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Body)"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <t>(1) TRUE if all states within district report quantity (i.e. none withhold)</t>
+    <t>(1) TRUE if all states within district report quantity (i.e. none withhold).</t>
   </si>
   <si>
     <r>
@@ -1007,7 +965,7 @@
         <b/>
         <vertAlign val="superscript"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow (Body)"/>
       </rPr>
       <t>1</t>
@@ -1015,9 +973,6 @@
   </si>
   <si>
     <t>Portland and Blended Cement Production in 2023, by District</t>
-  </si>
-  <si>
-    <t>Carbon Dioxide Emissions from Cement Production Facilities in 2023, by District</t>
   </si>
   <si>
     <r>
@@ -1028,14 +983,14 @@
         <b/>
         <vertAlign val="superscript"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow (Body)"/>
       </rPr>
       <t>1,2</t>
     </r>
   </si>
   <si>
-    <t>(2) See sources of data for each tier below</t>
+    <t>(2) See sources of data for each tier below.</t>
   </si>
   <si>
     <t>Tier 3: Direct Capacity Proxy</t>
@@ -1049,7 +1004,7 @@
         <b/>
         <vertAlign val="superscript"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow (Body)"/>
       </rPr>
       <t>1</t>
@@ -1070,7 +1025,7 @@
         <b/>
         <vertAlign val="superscript"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow (Body)"/>
       </rPr>
       <t>1</t>
@@ -1146,24 +1101,83 @@
     <t>Machine-readable table of demand validation data</t>
   </si>
   <si>
-    <t>Machine-readable table of cross-tier validation for disaggregation proxies.</t>
+    <t>Machine-readable table of cross-tier validation for disaggregation proxies</t>
+  </si>
+  <si>
+    <t>Demand (t)</t>
+  </si>
+  <si>
+    <t>(1) Source: Ullmann's Encyclopedia of Industrial Chemistry, Bromine</t>
+  </si>
+  <si>
+    <t>We map externally sourced benchmark end-use markets to end-use categories using the same procedure applied to the main source of data: end-uses with a market share &lt;5% are assigned to "Other".</t>
+  </si>
+  <si>
+    <t>% of Revenue</t>
+  </si>
+  <si>
+    <t>represents US consumption of liquid anhydrous hydrogen fluoride (2024)</t>
+  </si>
+  <si>
+    <t>represents P2O5 content of phosphate rock sold or used by producers (2023)</t>
+  </si>
+  <si>
+    <t>Barite Products Market Size, Share, Growth, and Industry Analysis, By Type (Up to Grade 3.9, Grade 4.0, Grade 4.1, Grade 4.2, Grade 4.3, Grade above 4.3), By Application (Drilling Industry (Rig), Medical Industry, Rubber &amp; Plastics, Pulps and Papers, Paints and Coatings, Cosmetic Industry, Others), Regional Insights and Forecast From 2026 To 2035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Liquid Anhydrous Hydrogen Fluoride Market Report is Segmented by Types (99.99 AHF, 99.90 AHF, 99.70 AHF), Application (Chemical Industry, Mining &amp; Metallurgical, Etching, Pharmaceuticals, Others), and Geography (North America, Europe, Asia-Pacific, South America, and Middle East and Africa).
+Liquid Anhydrous Hydrogen Fluoride Market Report is Segmented by Types (?99.99 AHF, ?99.90 AHF, ?99.70 AHF), Application (Chemical Industry, Mining &amp; Metallurgical, Etching, Pharmaceuticals, Others), and Geography (North America, Europe, Asia-Pacific, South America, and Middle East and Africa).</t>
+  </si>
+  <si>
+    <t>External Benchmark Validation</t>
+  </si>
+  <si>
+    <t>represents gross weight borate consumption in North America (2024)</t>
+  </si>
+  <si>
+    <t>HOLCIM (US) INC. DEVIL'S SLIDE PLANT</t>
+  </si>
+  <si>
+    <t>PHOENIX CEMENT COMPANY'S CLARKDALE FACILITY</t>
+  </si>
+  <si>
+    <r>
+      <t>Greenhouse Gas Emissions from Cement Production Facilities in 2023, by Facility</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>Greenhouse Gas Emissions from Cement Production Facilities in 2023, by District</t>
+  </si>
+  <si>
+    <t>B2O3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1171,34 +1185,34 @@
     <font>
       <b/>
       <sz val="20"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
-      <color theme="2" tint="-0.499984740745262"/>
+      <color rgb="FF747474"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
-      <color theme="10"/>
+      <color rgb="FF467886"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1219,7 +1233,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -1227,14 +1241,14 @@
       <b/>
       <vertAlign val="superscript"/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow (Body)"/>
     </font>
     <font>
       <b/>
       <vertAlign val="subscript"/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow (Body)"/>
     </font>
     <font>
@@ -1258,6 +1272,12 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1268,13 +1288,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFE97132"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFBE3D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1286,13 +1306,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2"/>
+        <fgColor rgb="FFE8E8E8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1391,7 +1411,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1443,17 +1463,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1472,24 +1487,11 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1501,11 +1503,42 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1847,7 +1880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{775D9A92-8258-8E42-AE91-EA1F6F9AF473}">
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="3.5" customWidth="1"/>
@@ -1857,454 +1890,354 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" s="42"/>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="42"/>
-      <c r="W1" s="42"/>
-      <c r="X1" s="42"/>
-      <c r="Y1" s="42"/>
-      <c r="Z1" s="42"/>
+      <c r="A1" s="39"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
     </row>
     <row r="2" spans="1:26" ht="27">
-      <c r="A2" s="44"/>
-      <c r="B2" s="45" t="s">
+      <c r="A2" s="41"/>
+      <c r="B2" s="42" t="s">
+        <v>279</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="41"/>
+    </row>
+    <row r="3" spans="1:26" ht="19">
+      <c r="A3" s="41"/>
+      <c r="B3" s="43" t="s">
+        <v>280</v>
+      </c>
+      <c r="C3" s="43"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="41"/>
+      <c r="W3" s="41"/>
+      <c r="X3" s="41"/>
+      <c r="Y3" s="41"/>
+      <c r="Z3" s="41"/>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+    </row>
+    <row r="5" spans="1:26" ht="42" customHeight="1">
+      <c r="A5" s="41"/>
+      <c r="B5" s="67" t="s">
+        <v>281</v>
+      </c>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="41"/>
+      <c r="Y5" s="41"/>
+      <c r="Z5" s="41"/>
+    </row>
+    <row r="6" spans="1:26">
+      <c r="A6" s="41"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="41"/>
+      <c r="Z6" s="41"/>
+    </row>
+    <row r="7" spans="1:26">
+      <c r="A7" s="39"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
+      <c r="S7" s="39"/>
+      <c r="T7" s="39"/>
+      <c r="U7" s="39"/>
+      <c r="V7" s="39"/>
+      <c r="W7" s="39"/>
+      <c r="X7" s="39"/>
+      <c r="Y7" s="39"/>
+      <c r="Z7" s="39"/>
+    </row>
+    <row r="8" spans="1:26">
+      <c r="A8" s="41"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="41"/>
+      <c r="T8" s="41"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="41"/>
+      <c r="W8" s="41"/>
+      <c r="X8" s="41"/>
+      <c r="Y8" s="41"/>
+      <c r="Z8" s="41"/>
+    </row>
+    <row r="9" spans="1:26" ht="27">
+      <c r="A9" s="41"/>
+      <c r="B9" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="41"/>
+      <c r="Q9" s="41"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="41"/>
+      <c r="T9" s="41"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="41"/>
+      <c r="W9" s="41"/>
+      <c r="X9" s="41"/>
+      <c r="Y9" s="41"/>
+      <c r="Z9" s="41"/>
+    </row>
+    <row r="10" spans="1:26" ht="17">
+      <c r="A10" s="41"/>
+      <c r="B10" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>277</v>
+      </c>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="41"/>
+      <c r="S10" s="41"/>
+      <c r="T10" s="41"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="41"/>
+      <c r="W10" s="41"/>
+      <c r="X10" s="41"/>
+      <c r="Y10" s="41"/>
+      <c r="Z10" s="41"/>
+    </row>
+    <row r="11" spans="1:26" ht="50" customHeight="1">
+      <c r="B11" s="68" t="s">
+        <v>282</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>283</v>
+      </c>
+      <c r="D11" s="50" t="s">
         <v>290</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="44"/>
-      <c r="V2" s="44"/>
-      <c r="W2" s="44"/>
-      <c r="X2" s="44"/>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="44"/>
-    </row>
-    <row r="3" spans="1:26" ht="19">
-      <c r="A3" s="44"/>
-      <c r="B3" s="46" t="s">
+    </row>
+    <row r="12" spans="1:26" ht="50" customHeight="1">
+      <c r="B12" s="68"/>
+      <c r="C12" s="55" t="s">
+        <v>284</v>
+      </c>
+      <c r="D12" s="50" t="s">
         <v>291</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="44"/>
-      <c r="T3" s="44"/>
-      <c r="U3" s="44"/>
-      <c r="V3" s="44"/>
-      <c r="W3" s="44"/>
-      <c r="X3" s="44"/>
-      <c r="Y3" s="44"/>
-      <c r="Z3" s="44"/>
-    </row>
-    <row r="4" spans="1:26">
-      <c r="A4" s="44"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44"/>
-      <c r="V4" s="44"/>
-      <c r="W4" s="44"/>
-      <c r="X4" s="44"/>
-      <c r="Y4" s="44"/>
-      <c r="Z4" s="44"/>
-    </row>
-    <row r="5" spans="1:26" ht="42" customHeight="1">
-      <c r="A5" s="44"/>
-      <c r="B5" s="53" t="s">
+    </row>
+    <row r="13" spans="1:26" ht="50" customHeight="1">
+      <c r="B13" s="68"/>
+      <c r="C13" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="D13" s="50" t="s">
         <v>292</v>
       </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="44"/>
-      <c r="T5" s="44"/>
-      <c r="U5" s="44"/>
-      <c r="V5" s="44"/>
-      <c r="W5" s="44"/>
-      <c r="X5" s="44"/>
-      <c r="Y5" s="44"/>
-      <c r="Z5" s="44"/>
-    </row>
-    <row r="6" spans="1:26">
-      <c r="A6" s="44"/>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="44"/>
-      <c r="U6" s="44"/>
-      <c r="V6" s="44"/>
-      <c r="W6" s="44"/>
-      <c r="X6" s="44"/>
-      <c r="Y6" s="44"/>
-      <c r="Z6" s="44"/>
-    </row>
-    <row r="7" spans="1:26">
-      <c r="A7" s="42"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="42"/>
-      <c r="S7" s="42"/>
-      <c r="T7" s="42"/>
-      <c r="U7" s="42"/>
-      <c r="V7" s="42"/>
-      <c r="W7" s="42"/>
-      <c r="X7" s="42"/>
-      <c r="Y7" s="42"/>
-      <c r="Z7" s="42"/>
-    </row>
-    <row r="8" spans="1:26">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="44"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="44"/>
-      <c r="P8" s="44"/>
-      <c r="Q8" s="44"/>
-      <c r="R8" s="44"/>
-      <c r="S8" s="44"/>
-      <c r="T8" s="44"/>
-      <c r="U8" s="44"/>
-      <c r="V8" s="44"/>
-      <c r="W8" s="44"/>
-      <c r="X8" s="44"/>
-      <c r="Y8" s="44"/>
-      <c r="Z8" s="44"/>
-    </row>
-    <row r="9" spans="1:26" ht="27">
-      <c r="A9" s="44"/>
-      <c r="B9" s="2" t="s">
+    </row>
+    <row r="14" spans="1:26" ht="50" customHeight="1">
+      <c r="B14" s="69" t="s">
+        <v>289</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="44"/>
-      <c r="P9" s="44"/>
-      <c r="Q9" s="44"/>
-      <c r="R9" s="44"/>
-      <c r="S9" s="44"/>
-      <c r="T9" s="44"/>
-      <c r="U9" s="44"/>
-      <c r="V9" s="44"/>
-      <c r="W9" s="44"/>
-      <c r="X9" s="44"/>
-      <c r="Y9" s="44"/>
-      <c r="Z9" s="44"/>
-    </row>
-    <row r="10" spans="1:26" ht="17">
-      <c r="A10" s="44"/>
-      <c r="B10" s="49" t="s">
-        <v>289</v>
-      </c>
-      <c r="C10" s="50" t="s">
+      <c r="D14" s="50" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="50" customHeight="1">
+      <c r="B15" s="69"/>
+      <c r="C15" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D15" s="50" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="50" customHeight="1">
+      <c r="B16" s="70"/>
+      <c r="C16" s="56" t="s">
         <v>288</v>
       </c>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="44"/>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="44"/>
-      <c r="R10" s="44"/>
-      <c r="S10" s="44"/>
-      <c r="T10" s="44"/>
-      <c r="U10" s="44"/>
-      <c r="V10" s="44"/>
-      <c r="W10" s="44"/>
-      <c r="X10" s="44"/>
-      <c r="Y10" s="44"/>
-      <c r="Z10" s="44"/>
-    </row>
-    <row r="11" spans="1:26" ht="50" customHeight="1">
-      <c r="B11" s="63" t="s">
-        <v>293</v>
-      </c>
-      <c r="C11" s="64" t="s">
-        <v>294</v>
-      </c>
-      <c r="D11" s="56" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="50" customHeight="1">
-      <c r="B12" s="63"/>
-      <c r="C12" s="64" t="s">
+      <c r="D16" s="51" t="s">
         <v>295</v>
       </c>
-      <c r="D12" s="56" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" ht="50" customHeight="1">
-      <c r="B13" s="63"/>
-      <c r="C13" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="D13" s="56" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" ht="50" customHeight="1">
-      <c r="B14" s="57" t="s">
-        <v>300</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="D14" s="56" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" ht="50" customHeight="1">
-      <c r="B15" s="57"/>
-      <c r="C15" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="D15" s="56" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" ht="50" customHeight="1">
-      <c r="B16" s="58"/>
-      <c r="C16" s="65" t="s">
-        <v>299</v>
-      </c>
-      <c r="D16" s="59" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4">
-      <c r="B17" s="52"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="55"/>
-    </row>
-    <row r="18" spans="2:4">
-      <c r="B18" s="52"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="55"/>
-    </row>
-    <row r="19" spans="2:4">
-      <c r="B19" s="52"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="55"/>
-    </row>
-    <row r="20" spans="2:4">
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="55"/>
-    </row>
-    <row r="21" spans="2:4">
-      <c r="B21" s="52"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="55"/>
-    </row>
-    <row r="22" spans="2:4">
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="55"/>
-    </row>
-    <row r="23" spans="2:4">
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="55"/>
-    </row>
-    <row r="24" spans="2:4">
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="55"/>
-    </row>
-    <row r="25" spans="2:4">
-      <c r="B25" s="52"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="55"/>
-    </row>
-    <row r="26" spans="2:4">
-      <c r="B26" s="52"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="55"/>
-    </row>
-    <row r="27" spans="2:4">
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="55"/>
-    </row>
-    <row r="28" spans="2:4">
-      <c r="B28" s="52"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="55"/>
-    </row>
-    <row r="29" spans="2:4">
-      <c r="B29" s="52"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="55"/>
-    </row>
-    <row r="30" spans="2:4">
-      <c r="B30" s="52"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="55"/>
-    </row>
-    <row r="31" spans="2:4">
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="55"/>
-    </row>
-    <row r="32" spans="2:4">
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="55"/>
-    </row>
-    <row r="33" spans="2:4">
-      <c r="B33" s="52"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="55"/>
-    </row>
-    <row r="34" spans="2:4">
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="55"/>
-    </row>
-    <row r="35" spans="2:4">
-      <c r="B35" s="52"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="55"/>
-    </row>
-    <row r="36" spans="2:4">
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2326,7 +2259,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58E59886-CDD6-B745-BD2E-15FB5F2CF4D1}">
-  <dimension ref="A1:Z52"/>
+  <dimension ref="A1:Z54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
@@ -2376,152 +2309,133 @@
     <row r="4" spans="1:26" ht="19">
       <c r="B4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="24">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:26" ht="39" customHeight="1">
+      <c r="B5" s="71" t="s">
+        <v>298</v>
+      </c>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+    </row>
+    <row r="6" spans="1:26" ht="19">
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:26" ht="24">
+      <c r="B7" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="19">
-      <c r="B6" s="26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26">
-      <c r="B7" s="14" t="s">
+    <row r="8" spans="1:26" ht="19">
+      <c r="B8" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="B9" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C9" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="16" t="s">
+      <c r="D9" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26">
-      <c r="B8" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8">
-        <v>483000</v>
-      </c>
-      <c r="E8" s="20">
-        <v>0.58945569929216501</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26">
-      <c r="B9" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9">
-        <v>103500</v>
-      </c>
-      <c r="E9" s="20">
-        <v>0.12631193556260678</v>
       </c>
     </row>
     <row r="10" spans="1:26">
       <c r="B10" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="64">
+        <v>483000</v>
+      </c>
+      <c r="E10" s="20">
+        <v>0.58945569929216501</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
+      <c r="B11" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="64">
+        <v>103500</v>
+      </c>
+      <c r="E11" s="20">
+        <v>0.12631193556260678</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
+      <c r="B12" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C12" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="D10">
+      <c r="D12" s="64">
         <v>86300</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E12" s="20">
         <v>0.10532096656089822</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="17">
-      <c r="B11" s="21" t="s">
+    <row r="13" spans="1:26" ht="17">
+      <c r="B13" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C13" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D11">
+      <c r="D13" s="64">
         <v>77600</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E13" s="20">
         <v>9.4703441542592137E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="17">
-      <c r="B12" s="23" t="s">
+    <row r="14" spans="1:26" ht="17">
+      <c r="B14" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C14" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D14" s="65">
         <v>69000</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E14" s="25">
         <v>8.4207957041737863E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
-      <c r="B13" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" ht="19">
-      <c r="B15" s="26" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26">
-      <c r="B16" s="14" t="s">
+    <row r="15" spans="1:26">
+      <c r="B15" s="11" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" ht="19">
+      <c r="B17" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26">
+      <c r="B18" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C18" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26">
-      <c r="B17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17">
-        <v>7.9</v>
-      </c>
-      <c r="E17" s="7">
-        <f>D17/SUM($D$17:$D$27)</f>
-        <v>8.9752329016132698E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26">
-      <c r="B18" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18">
-        <v>369</v>
-      </c>
-      <c r="E18" s="7">
-        <f t="shared" ref="E18:E27" si="0">D18/SUM($D$17:$D$27)</f>
-        <v>0.41922290388548056</v>
+      <c r="D18" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="19" spans="1:26">
@@ -2529,44 +2443,44 @@
         <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D19">
+        <v>7.9</v>
+      </c>
+      <c r="E19" s="7">
+        <f>D19/SUM($D$19:$D$29)</f>
+        <v>8.9752329016132698E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26">
+      <c r="B20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20">
+        <v>369</v>
+      </c>
+      <c r="E20" s="7">
+        <f t="shared" ref="E20:E29" si="0">D20/SUM($D$19:$D$29)</f>
+        <v>0.41922290388548056</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26">
+      <c r="B21" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21">
         <v>25.1</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E21" s="7">
         <f t="shared" si="0"/>
         <v>2.851624630765735E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26">
-      <c r="B20" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="E20" s="7">
-        <f t="shared" si="0"/>
-        <v>3.8400363553737785E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26">
-      <c r="B21" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21">
-        <v>250.2</v>
-      </c>
-      <c r="E21" s="7">
-        <f t="shared" si="0"/>
-        <v>0.28425357873210633</v>
       </c>
     </row>
     <row r="22" spans="1:26">
@@ -2574,29 +2488,29 @@
         <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D22">
-        <v>9</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="E22" s="7">
         <f t="shared" si="0"/>
-        <v>1.0224948875255623E-2</v>
+        <v>3.8400363553737785E-2</v>
       </c>
     </row>
     <row r="23" spans="1:26">
       <c r="B23" s="5" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D23">
-        <v>25.5</v>
+        <v>250.2</v>
       </c>
       <c r="E23" s="7">
         <f t="shared" si="0"/>
-        <v>2.8970688479890934E-2</v>
+        <v>0.28425357873210633</v>
       </c>
     </row>
     <row r="24" spans="1:26">
@@ -2604,14 +2518,14 @@
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D24">
-        <v>17.2</v>
+        <v>9</v>
       </c>
       <c r="E24" s="7">
         <f t="shared" si="0"/>
-        <v>1.954101340604408E-2</v>
+        <v>1.0224948875255623E-2</v>
       </c>
     </row>
     <row r="25" spans="1:26">
@@ -2619,327 +2533,360 @@
         <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D25">
-        <v>12.5</v>
+        <v>25.5</v>
       </c>
       <c r="E25" s="7">
         <f t="shared" si="0"/>
-        <v>1.4201317882299476E-2</v>
+        <v>2.8970688479890934E-2</v>
       </c>
     </row>
     <row r="26" spans="1:26">
       <c r="B26" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D26">
-        <v>80.7</v>
+        <v>17.2</v>
       </c>
       <c r="E26" s="7">
         <f t="shared" si="0"/>
+        <v>1.954101340604408E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26">
+      <c r="B27" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27">
+        <v>12.5</v>
+      </c>
+      <c r="E27" s="7">
+        <f t="shared" si="0"/>
+        <v>1.4201317882299476E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26">
+      <c r="B28" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28">
+        <v>80.7</v>
+      </c>
+      <c r="E28" s="7">
+        <f t="shared" si="0"/>
         <v>9.1683708248125426E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:26">
-      <c r="B27" s="8" t="s">
+    <row r="29" spans="1:26">
+      <c r="B29" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" s="9">
+      <c r="C29" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="9">
         <v>49.3</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E29" s="10">
         <f t="shared" si="0"/>
         <v>5.6009997727789133E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:26">
-      <c r="B28" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
     <row r="30" spans="1:26">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
-    </row>
-    <row r="32" spans="1:26" ht="24">
-      <c r="B32" s="3" t="s">
+      <c r="B30" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+    </row>
+    <row r="34" spans="2:5" ht="24">
+      <c r="B34" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="19">
+      <c r="B35" s="26" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="2:5" ht="19">
-      <c r="B33" s="26" t="s">
+    <row r="36" spans="2:5">
+      <c r="B36" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5">
+      <c r="B37" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="59" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="34" spans="2:5">
-      <c r="B34" s="14" t="s">
+      <c r="D37" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" s="60">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5">
+      <c r="B38" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="60">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5">
+      <c r="B39" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="59" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="60">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5">
+      <c r="B40" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="59" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" s="60">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" ht="17">
+      <c r="B41" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" ht="17">
+      <c r="B42" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5">
+      <c r="B43" s="27" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" ht="19">
+      <c r="B45" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5">
+      <c r="B46" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C46" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D34" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5">
-      <c r="B35" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" t="s">
-        <v>6</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.56000000000000005</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5">
-      <c r="B36" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" t="s">
-        <v>6</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.18333333333333332</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5">
-      <c r="B37" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" t="s">
-        <v>46</v>
-      </c>
-      <c r="D37" t="s">
-        <v>6</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.11388888888888889</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5">
-      <c r="B38" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" t="s">
-        <v>48</v>
-      </c>
-      <c r="D38" t="s">
-        <v>6</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5">
-      <c r="B39" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5">
-      <c r="B40" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E40" s="10">
-        <v>4.7222222222222221E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5">
-      <c r="B41" s="27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" ht="19">
-      <c r="B43" s="26" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5">
-      <c r="B44" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5">
-      <c r="B45" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45" t="s">
-        <v>51</v>
-      </c>
-      <c r="D45">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="E45" s="7">
-        <f>D45/SUM($D$45:$D$51)</f>
-        <v>5.086114101184068E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5">
-      <c r="B46" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46">
-        <v>52.1</v>
-      </c>
-      <c r="E46" s="7">
-        <f t="shared" ref="E46:E51" si="1">D46/SUM($D$45:$D$51)</f>
-        <v>7.0102260495156082E-2</v>
+      <c r="D46" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="47" spans="2:5">
       <c r="B47" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D47">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="E47" s="7">
+        <f>D47/SUM($D$47:$D$53)</f>
+        <v>5.086114101184068E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5">
+      <c r="B48" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48">
+        <v>52.1</v>
+      </c>
+      <c r="E48" s="7">
+        <f t="shared" ref="E48:E53" si="1">D48/SUM($D$47:$D$53)</f>
+        <v>7.0102260495156082E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5">
+      <c r="B49" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C47" t="s">
-        <v>53</v>
-      </c>
-      <c r="D47">
+      <c r="C49" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49">
         <v>33.700000000000003</v>
       </c>
-      <c r="E47" s="7">
+      <c r="E49" s="7">
         <f t="shared" si="1"/>
         <v>4.5344456404736277E-2</v>
       </c>
     </row>
-    <row r="48" spans="2:5">
-      <c r="B48" s="5" t="s">
+    <row r="50" spans="2:5">
+      <c r="B50" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C48" t="s">
-        <v>31</v>
-      </c>
-      <c r="D48">
+      <c r="C50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50">
         <v>18.7</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E50" s="7">
         <f t="shared" si="1"/>
         <v>2.5161463939720127E-2</v>
       </c>
     </row>
-    <row r="49" spans="2:5">
-      <c r="B49" s="5" t="s">
+    <row r="51" spans="2:5">
+      <c r="B51" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C49" t="s">
-        <v>54</v>
-      </c>
-      <c r="D49">
+      <c r="C51" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51">
         <v>140.19999999999999</v>
       </c>
-      <c r="E49" s="7">
+      <c r="E51" s="7">
         <f t="shared" si="1"/>
         <v>0.18864370290635088</v>
       </c>
     </row>
-    <row r="50" spans="2:5">
-      <c r="B50" s="5" t="s">
+    <row r="52" spans="2:5">
+      <c r="B52" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C50" t="s">
-        <v>55</v>
-      </c>
-      <c r="D50">
+      <c r="C52" t="s">
+        <v>54</v>
+      </c>
+      <c r="D52">
         <v>437.7</v>
       </c>
-      <c r="E50" s="7">
+      <c r="E52" s="7">
         <f t="shared" si="1"/>
         <v>0.58893972012917106</v>
       </c>
     </row>
-    <row r="51" spans="2:5">
-      <c r="B51" s="8" t="s">
+    <row r="53" spans="2:5">
+      <c r="B53" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D51" s="9">
+      <c r="C53" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D53" s="9">
         <v>23</v>
       </c>
-      <c r="E51" s="10">
+      <c r="E53" s="10">
         <f t="shared" si="1"/>
         <v>3.0947255113024756E-2</v>
       </c>
     </row>
-    <row r="52" spans="2:5">
-      <c r="B52" s="11" t="s">
-        <v>57</v>
+    <row r="54" spans="2:5">
+      <c r="B54" s="11" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:E5"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B13" r:id="rId1" xr:uid="{B3E237F5-6201-7241-BE4E-24DDE6575418}"/>
-    <hyperlink ref="B28" r:id="rId2" xr:uid="{31F48FA3-21AE-4844-A943-EB532ED8BC85}"/>
-    <hyperlink ref="B41" r:id="rId3" display="(1) Source: EPA Water Treatment Chemical Supply Chain Profile, Hydrochloric Acid" xr:uid="{D1141142-C843-D047-9C82-4356DA0C904F}"/>
-    <hyperlink ref="B52" r:id="rId4" xr:uid="{35C6CEE8-C097-9948-BBC1-E2956CF4FB20}"/>
+    <hyperlink ref="B15" r:id="rId1" display="(1) Source: Ullmann's Encyclopedia for Industrial Chemistry, Bromine" xr:uid="{B3E237F5-6201-7241-BE4E-24DDE6575418}"/>
+    <hyperlink ref="B30" r:id="rId2" xr:uid="{31F48FA3-21AE-4844-A943-EB532ED8BC85}"/>
+    <hyperlink ref="B43" r:id="rId3" display="(1) Source: EPA Water Treatment Chemical Supply Chain Profile, Hydrochloric Acid" xr:uid="{D1141142-C843-D047-9C82-4356DA0C904F}"/>
+    <hyperlink ref="B54" r:id="rId4" xr:uid="{35C6CEE8-C097-9948-BBC1-E2956CF4FB20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2963,8 +2910,8 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -2987,37 +2934,37 @@
     </row>
     <row r="2" spans="1:25" ht="27">
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="19">
       <c r="B3" s="4" t="s">
-        <v>15</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="19">
       <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:25" ht="17">
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="D5" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="54" t="s">
         <v>65</v>
-      </c>
-      <c r="D5" s="61" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="62" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="62" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="34">
       <c r="B6" t="s">
-        <v>69</v>
+        <v>310</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -3026,15 +2973,15 @@
         <v>580</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>99</v>
+        <v>305</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="51">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="68">
       <c r="B7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -3043,15 +2990,15 @@
         <v>2000</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>79</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="34">
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -3060,15 +3007,15 @@
         <v>275</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="34">
       <c r="B9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -3077,15 +3024,15 @@
         <v>2470</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="34">
       <c r="B10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -3094,15 +3041,15 @@
         <v>1458</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="51">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="119">
       <c r="B11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -3111,15 +3058,15 @@
         <v>320</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>86</v>
+        <v>300</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>87</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="34">
       <c r="B12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -3128,15 +3075,15 @@
         <v>3.75</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="34">
       <c r="B13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -3145,15 +3092,15 @@
         <v>190</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="34">
       <c r="B14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -3162,15 +3109,15 @@
         <v>72.900000000000006</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="34">
       <c r="B15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -3179,15 +3126,15 @@
         <v>6000</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="34">
       <c r="B16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -3196,25 +3143,25 @@
         <v>5700</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>95</v>
+        <v>301</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F6" r:id="rId1" xr:uid="{E0A61302-E760-3F42-9070-A7C6289A59F8}"/>
-    <hyperlink ref="F7" r:id="rId2" xr:uid="{B657757A-F86C-5E4E-B760-9142C52901E0}"/>
+    <hyperlink ref="F7" r:id="rId2" display="Market Reports World, Barite Products Market Size, Share, Growth, and Industry Analysis, By Type (Up to Grade 3.9, Grade 4.0, Grade 4.1, Grade 4.2, Grade 4.3, Grade above 4.3), By Application (Drilling Industry (Rig), Medical Industry, Rubber &amp; Plastics, " xr:uid="{B657757A-F86C-5E4E-B760-9142C52901E0}"/>
     <hyperlink ref="F8" r:id="rId3" xr:uid="{8E42E622-5EC4-3242-99B7-032940B684AD}"/>
     <hyperlink ref="F9" r:id="rId4" xr:uid="{75D43406-2C82-AD49-BEEE-61E46F610A2B}"/>
     <hyperlink ref="F10" r:id="rId5" xr:uid="{A365FA2F-6174-6D47-A0C3-8946FE61D0E4}"/>
-    <hyperlink ref="F11" r:id="rId6" xr:uid="{3B90BDB8-757A-7646-82F8-ACC474D47BB8}"/>
-    <hyperlink ref="F12" r:id="rId7" xr:uid="{10A9827D-262C-4E43-A982-BA50AD78A15B}"/>
-    <hyperlink ref="F13" r:id="rId8" xr:uid="{98C4BBC5-E91F-C544-8FEC-CDDF72115AC3}"/>
-    <hyperlink ref="F14" r:id="rId9" xr:uid="{BB7B0332-8F56-6B47-82A2-75A844B4E0CF}"/>
-    <hyperlink ref="F15" r:id="rId10" xr:uid="{7E11D623-5E2F-D64E-ACCC-B095B776AF85}"/>
-    <hyperlink ref="F16" r:id="rId11" xr:uid="{46572126-4DF4-4A45-8D05-07D875C33994}"/>
+    <hyperlink ref="F12" r:id="rId6" xr:uid="{10A9827D-262C-4E43-A982-BA50AD78A15B}"/>
+    <hyperlink ref="F13" r:id="rId7" xr:uid="{98C4BBC5-E91F-C544-8FEC-CDDF72115AC3}"/>
+    <hyperlink ref="F14" r:id="rId8" xr:uid="{BB7B0332-8F56-6B47-82A2-75A844B4E0CF}"/>
+    <hyperlink ref="F15" r:id="rId9" xr:uid="{7E11D623-5E2F-D64E-ACCC-B095B776AF85}"/>
+    <hyperlink ref="F16" r:id="rId10" xr:uid="{46572126-4DF4-4A45-8D05-07D875C33994}"/>
+    <hyperlink ref="F11" r:id="rId11" display="https://www.marketgrowthreports.com/market-reports/liquid-anhydrous-hydrogen-fluoride-market-108451" xr:uid="{96F79528-E4FF-094A-8616-51A031ACBA0C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3255,7 +3202,7 @@
     </row>
     <row r="2" spans="1:19" ht="27">
       <c r="B2" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="19">
@@ -3267,29 +3214,29 @@
       <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:19" ht="37" customHeight="1">
-      <c r="B5" s="41" t="s">
-        <v>174</v>
-      </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
+      <c r="B5" s="72" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
     </row>
     <row r="6" spans="1:19">
       <c r="B6" s="17"/>
     </row>
     <row r="7" spans="1:19" ht="19">
       <c r="B7" s="26" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:19">
-      <c r="B8" s="37" t="s">
-        <v>104</v>
+      <c r="B8" s="35" t="s">
+        <v>97</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>12</v>
@@ -3301,28 +3248,28 @@
         <v>14</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="B9" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C9" s="38">
+        <v>159</v>
+      </c>
+      <c r="C9" s="36">
         <f t="shared" ref="C9:C27" si="0">IF(ISERROR(_xlfn.XLOOKUP(B9,$H$36:$H$54,$J$36:$J$54)/$J$55), "", (_xlfn.XLOOKUP(B9,$H$36:$H$54,$J$36:$J$54)/$J$55))</f>
         <v>2.3127272727272729E-2</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="36">
         <f>_xlfn.XLOOKUP(B9,$H$92:$H$110,$I$92:$I$110)/$I$111</f>
         <v>2.2233913580529313E-2</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="36">
         <f>_xlfn.XLOOKUP(B9,$H$121:$H$139,$I$121:$I$139)/$I$140</f>
         <v>2.1295163541192035E-2</v>
       </c>
-      <c r="F9" s="38">
-        <f>_xlfn.XLOOKUP(B9,$H$121:$H$139,$I$121:$I$139)/$I$140</f>
-        <v>2.1295163541192035E-2</v>
+      <c r="F9" s="36">
+        <f>_xlfn.XLOOKUP(B9,$H$218:$H$237,$I$218:$I$237)/$I$237</f>
+        <v>2.7143440335252313E-2</v>
       </c>
       <c r="G9" s="7">
         <f>_xlfn.XLOOKUP(B9,$H$247:$H$265,$I$247:$I$265)/$I$266</f>
@@ -3331,23 +3278,23 @@
     </row>
     <row r="10" spans="1:19">
       <c r="B10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C10" s="38">
+        <v>135</v>
+      </c>
+      <c r="C10" s="36">
         <f t="shared" si="0"/>
         <v>4.7181818181818179E-2</v>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="36">
         <f t="shared" ref="D10:D27" si="1">_xlfn.XLOOKUP(B10,$H$92:$H$110,$I$92:$I$110)/$I$111</f>
         <v>3.9458334286433194E-2</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="36">
         <f t="shared" ref="E10:E27" si="2">_xlfn.XLOOKUP(B10,$H$121:$H$139,$I$121:$I$139)/$I$140</f>
         <v>4.4032605681508151E-2</v>
       </c>
-      <c r="F10" s="38">
-        <f t="shared" ref="F10:F27" si="3">_xlfn.XLOOKUP(B10,$H$121:$H$139,$I$121:$I$139)/$I$140</f>
-        <v>4.4032605681508151E-2</v>
+      <c r="F10" s="36">
+        <f t="shared" ref="F10:F27" si="3">_xlfn.XLOOKUP(B10,$H$218:$H$237,$I$218:$I$237)/$I$237</f>
+        <v>4.8238342400586526E-2</v>
       </c>
       <c r="G10" s="7">
         <f t="shared" ref="G10:G27" si="4">_xlfn.XLOOKUP(B10,$H$247:$H$265,$I$247:$I$265)/$I$266</f>
@@ -3356,23 +3303,23 @@
     </row>
     <row r="11" spans="1:19">
       <c r="B11" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="38" t="str">
+        <v>110</v>
+      </c>
+      <c r="C11" s="36" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D11" s="38">
+      <c r="D11" s="36">
         <f t="shared" si="1"/>
         <v>1.52000365990347E-2</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="36">
         <f t="shared" si="2"/>
         <v>1.7139801078028306E-2</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="36">
         <f t="shared" si="3"/>
-        <v>1.7139801078028306E-2</v>
+        <v>2.1086570745403193E-2</v>
       </c>
       <c r="G11" s="7">
         <f t="shared" si="4"/>
@@ -3381,23 +3328,23 @@
     </row>
     <row r="12" spans="1:19">
       <c r="B12" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C12" s="38">
+        <v>157</v>
+      </c>
+      <c r="C12" s="36">
         <f t="shared" si="0"/>
         <v>4.236363636363636E-2</v>
       </c>
-      <c r="D12" s="38">
+      <c r="D12" s="36">
         <f t="shared" si="1"/>
         <v>4.3941716037239516E-2</v>
       </c>
-      <c r="E12" s="38">
+      <c r="E12" s="36">
         <f t="shared" si="2"/>
         <v>4.9296062800893277E-2</v>
       </c>
-      <c r="F12" s="38">
+      <c r="F12" s="36">
         <f t="shared" si="3"/>
-        <v>4.9296062800893277E-2</v>
+        <v>4.7313565888243675E-2</v>
       </c>
       <c r="G12" s="7">
         <f t="shared" si="4"/>
@@ -3406,23 +3353,23 @@
     </row>
     <row r="13" spans="1:19">
       <c r="B13" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C13" s="38" t="str">
+        <v>119</v>
+      </c>
+      <c r="C13" s="36" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D13" s="38">
+      <c r="D13" s="36">
         <f t="shared" si="1"/>
         <v>5.4646933687124005E-2</v>
       </c>
-      <c r="E13" s="38">
+      <c r="E13" s="36">
         <f t="shared" si="2"/>
         <v>4.7991301974609671E-2</v>
       </c>
-      <c r="F13" s="38">
+      <c r="F13" s="36">
         <f t="shared" si="3"/>
-        <v>4.7991301974609671E-2</v>
+        <v>4.7805113764173658E-2</v>
       </c>
       <c r="G13" s="7">
         <f t="shared" si="4"/>
@@ -3431,23 +3378,23 @@
     </row>
     <row r="14" spans="1:19">
       <c r="B14" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C14" s="38" t="str">
+        <v>158</v>
+      </c>
+      <c r="C14" s="36" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="36">
         <f t="shared" si="1"/>
         <v>4.1036667657890526E-2</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="36">
         <f t="shared" si="2"/>
         <v>4.1990455501326858E-2</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="36">
         <f t="shared" si="3"/>
-        <v>4.1990455501326858E-2</v>
+        <v>3.5699705904406437E-2</v>
       </c>
       <c r="G14" s="7">
         <f t="shared" si="4"/>
@@ -3456,48 +3403,48 @@
     </row>
     <row r="15" spans="1:19">
       <c r="B15" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C15" s="38" t="str">
+        <v>113</v>
+      </c>
+      <c r="C15" s="36" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D15" s="38">
+      <c r="D15" s="36">
         <f t="shared" si="1"/>
-        <v>5.7323238099595122E-2</v>
-      </c>
-      <c r="E15" s="38">
+        <v>3.1772536999336645E-2</v>
+      </c>
+      <c r="E15" s="36">
         <f t="shared" si="2"/>
         <v>3.3605517492133169E-2</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="36">
         <f t="shared" si="3"/>
-        <v>3.3605517492133169E-2</v>
+        <v>2.642694682118488E-2</v>
       </c>
       <c r="G15" s="7">
         <f t="shared" si="4"/>
-        <v>6.0606060606060608E-2</v>
+        <v>2.0202020202020204E-2</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="B16" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C16" s="38">
+        <v>122</v>
+      </c>
+      <c r="C16" s="36">
         <f t="shared" si="0"/>
         <v>0.10818181818181818</v>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="36">
         <f t="shared" si="1"/>
         <v>0.11277077567079169</v>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="36">
         <f t="shared" si="2"/>
         <v>0.10300249238021748</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="36">
         <f t="shared" si="3"/>
-        <v>0.10300249238021748</v>
+        <v>9.3535728865524165E-2</v>
       </c>
       <c r="G16" s="7">
         <f t="shared" si="4"/>
@@ -3506,23 +3453,23 @@
     </row>
     <row r="17" spans="1:19">
       <c r="B17" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C17" s="38">
+        <v>107</v>
+      </c>
+      <c r="C17" s="36">
         <f t="shared" si="0"/>
         <v>4.8818181818181816E-2</v>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="36">
         <f t="shared" si="1"/>
         <v>7.2866390648946636E-2</v>
       </c>
-      <c r="E17" s="38">
+      <c r="E17" s="36">
         <f t="shared" si="2"/>
         <v>6.336830976222689E-2</v>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="36">
         <f t="shared" si="3"/>
-        <v>6.336830976222689E-2</v>
+        <v>8.7812112072915713E-2</v>
       </c>
       <c r="G17" s="7">
         <f t="shared" si="4"/>
@@ -3531,23 +3478,23 @@
     </row>
     <row r="18" spans="1:19">
       <c r="B18" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C18" s="38" t="str">
+        <v>156</v>
+      </c>
+      <c r="C18" s="36" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="36">
         <f t="shared" si="1"/>
         <v>6.862319006336208E-2</v>
       </c>
-      <c r="E18" s="38">
+      <c r="E18" s="36">
         <f t="shared" si="2"/>
         <v>6.5548172775919358E-2</v>
       </c>
-      <c r="F18" s="38">
+      <c r="F18" s="36">
         <f t="shared" si="3"/>
-        <v>6.5548172775919358E-2</v>
+        <v>6.6067367052962206E-2</v>
       </c>
       <c r="G18" s="7">
         <f t="shared" si="4"/>
@@ -3556,23 +3503,23 @@
     </row>
     <row r="19" spans="1:19">
       <c r="B19" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C19" s="38">
+        <v>137</v>
+      </c>
+      <c r="C19" s="36">
         <f t="shared" si="0"/>
         <v>1.8727272727272728E-2</v>
       </c>
-      <c r="D19" s="38">
+      <c r="D19" s="36">
         <f t="shared" si="1"/>
         <v>3.3522428345952378E-2</v>
       </c>
-      <c r="E19" s="38">
+      <c r="E19" s="36">
         <f t="shared" si="2"/>
         <v>3.4855166176611739E-2</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F19" s="36">
         <f t="shared" si="3"/>
-        <v>3.4855166176611739E-2</v>
+        <v>4.7205258729140456E-2</v>
       </c>
       <c r="G19" s="7">
         <f t="shared" si="4"/>
@@ -3581,23 +3528,23 @@
     </row>
     <row r="20" spans="1:19">
       <c r="B20" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C20" s="38" t="str">
+        <v>152</v>
+      </c>
+      <c r="C20" s="36" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D20" s="38">
+      <c r="D20" s="36">
         <f t="shared" si="1"/>
         <v>9.0273806528352818E-2</v>
       </c>
-      <c r="E20" s="38">
+      <c r="E20" s="36">
         <f t="shared" si="2"/>
         <v>9.3484702014291016E-2</v>
       </c>
-      <c r="F20" s="38">
+      <c r="F20" s="36">
         <f t="shared" si="3"/>
-        <v>9.3484702014291016E-2</v>
+        <v>8.4346282981612772E-2</v>
       </c>
       <c r="G20" s="7">
         <f t="shared" si="4"/>
@@ -3606,23 +3553,23 @@
     </row>
     <row r="21" spans="1:19">
       <c r="B21" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="38" t="str">
+        <v>154</v>
+      </c>
+      <c r="C21" s="36" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D21" s="38">
+      <c r="D21" s="36">
         <f t="shared" si="1"/>
         <v>2.5550701100258481E-2</v>
       </c>
-      <c r="E21" s="38">
+      <c r="E21" s="36">
         <f t="shared" si="2"/>
         <v>3.0991779528145538E-2</v>
       </c>
-      <c r="F21" s="38">
+      <c r="F21" s="36">
         <f t="shared" si="3"/>
-        <v>3.0991779528145538E-2</v>
+        <v>3.0117721550625264E-2</v>
       </c>
       <c r="G21" s="7">
         <f t="shared" si="4"/>
@@ -3631,23 +3578,23 @@
     </row>
     <row r="22" spans="1:19">
       <c r="B22" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C22" s="38">
+        <v>140</v>
+      </c>
+      <c r="C22" s="36">
         <f t="shared" si="0"/>
         <v>0.18454545454545454</v>
       </c>
-      <c r="D22" s="38">
+      <c r="D22" s="36">
         <f t="shared" si="1"/>
         <v>0.1342727085573118</v>
       </c>
-      <c r="E22" s="38">
+      <c r="E22" s="36">
         <f t="shared" si="2"/>
         <v>0.13128517928573913</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="36">
         <f t="shared" si="3"/>
-        <v>0.13128517928573913</v>
+        <v>0.13130160211282274</v>
       </c>
       <c r="G22" s="7">
         <f t="shared" si="4"/>
@@ -3656,23 +3603,23 @@
     </row>
     <row r="23" spans="1:19">
       <c r="B23" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C23" s="38" t="str">
+        <v>153</v>
+      </c>
+      <c r="C23" s="36" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D23" s="38">
+      <c r="D23" s="36">
         <f t="shared" si="1"/>
         <v>3.4734771370405107E-2</v>
       </c>
-      <c r="E23" s="38">
+      <c r="E23" s="36">
         <f t="shared" si="2"/>
         <v>3.5189335114847446E-2</v>
       </c>
-      <c r="F23" s="38">
+      <c r="F23" s="36">
         <f t="shared" si="3"/>
-        <v>3.5189335114847446E-2</v>
+        <v>2.8118204767181264E-2</v>
       </c>
       <c r="G23" s="7">
         <f t="shared" si="4"/>
@@ -3681,23 +3628,23 @@
     </row>
     <row r="24" spans="1:19">
       <c r="B24" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C24" s="38" t="str">
+        <v>155</v>
+      </c>
+      <c r="C24" s="36" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D24" s="38">
+      <c r="D24" s="36">
         <f t="shared" si="1"/>
         <v>3.2149964544685133E-2</v>
       </c>
-      <c r="E24" s="38">
+      <c r="E24" s="36">
         <f t="shared" si="2"/>
         <v>3.1911430571807904E-2</v>
       </c>
-      <c r="F24" s="38">
+      <c r="F24" s="36">
         <f t="shared" si="3"/>
-        <v>3.1911430571807904E-2</v>
+        <v>3.561639270509627E-2</v>
       </c>
       <c r="G24" s="7">
         <f t="shared" si="4"/>
@@ -3706,23 +3653,23 @@
     </row>
     <row r="25" spans="1:19">
       <c r="B25" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C25" s="38" t="str">
+        <v>161</v>
+      </c>
+      <c r="C25" s="36" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D25" s="38">
+      <c r="D25" s="36">
         <f t="shared" si="1"/>
         <v>2.8021135942539514E-2</v>
       </c>
-      <c r="E25" s="38">
+      <c r="E25" s="36">
         <f t="shared" si="2"/>
         <v>3.1325348279702174E-2</v>
       </c>
-      <c r="F25" s="38">
+      <c r="F25" s="36">
         <f t="shared" si="3"/>
-        <v>3.1325348279702174E-2</v>
+        <v>2.6668555099184362E-2</v>
       </c>
       <c r="G25" s="7">
         <f t="shared" si="4"/>
@@ -3731,23 +3678,23 @@
     </row>
     <row r="26" spans="1:19">
       <c r="B26" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C26" s="38">
+        <v>103</v>
+      </c>
+      <c r="C26" s="36">
         <f t="shared" si="0"/>
         <v>0.11181818181818182</v>
       </c>
-      <c r="D26" s="38">
+      <c r="D26" s="36">
         <f t="shared" si="1"/>
         <v>0.10224855319440949</v>
       </c>
-      <c r="E26" s="38">
+      <c r="E26" s="36">
         <f t="shared" si="2"/>
         <v>0.10946350198033845</v>
       </c>
-      <c r="F26" s="38">
+      <c r="F26" s="36">
         <f t="shared" si="3"/>
-        <v>0.10946350198033845</v>
+        <v>9.4143915220488386E-2</v>
       </c>
       <c r="G26" s="7">
         <f t="shared" si="4"/>
@@ -3756,23 +3703,23 @@
     </row>
     <row r="27" spans="1:19">
       <c r="B27" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C27" s="39" t="str">
+        <v>162</v>
+      </c>
+      <c r="C27" s="37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D27" s="39">
+      <c r="D27" s="37">
         <f t="shared" si="1"/>
         <v>1.6675435185396985E-2</v>
       </c>
-      <c r="E27" s="39">
+      <c r="E27" s="37">
         <f t="shared" si="2"/>
         <v>1.4223674060461395E-2</v>
       </c>
-      <c r="F27" s="39">
+      <c r="F27" s="37">
         <f t="shared" si="3"/>
-        <v>1.4223674060461395E-2</v>
+        <v>2.1353172983195726E-2</v>
       </c>
       <c r="G27" s="10">
         <f t="shared" si="4"/>
@@ -3781,13 +3728,17 @@
     </row>
     <row r="28" spans="1:19">
       <c r="B28" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:19">
       <c r="B29" t="s">
-        <v>277</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
     </row>
     <row r="31" spans="1:19">
       <c r="A31" s="1"/>
@@ -3812,43 +3763,43 @@
     </row>
     <row r="33" spans="2:10" ht="24">
       <c r="B33" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="2:10" ht="19">
       <c r="B34" s="26" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="2:10" ht="19">
       <c r="B35" s="14" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H35" s="14" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J35" s="16" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="2:10">
       <c r="B36" s="5" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C36" s="29">
         <v>4660</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="I36" t="b" cm="1">
         <f t="array" ref="I36">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H36," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -3861,13 +3812,13 @@
     </row>
     <row r="37" spans="2:10">
       <c r="B37" s="5" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="I37" t="b" cm="1">
         <f t="array" ref="I37">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H37," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -3880,13 +3831,13 @@
     </row>
     <row r="38" spans="2:10">
       <c r="B38" s="5" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I38" t="b" cm="1">
         <f t="array" ref="I38">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H38," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -3899,13 +3850,13 @@
     </row>
     <row r="39" spans="2:10">
       <c r="B39" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C39" s="29">
         <v>12300</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="I39" t="b" cm="1">
         <f t="array" ref="I39">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H39," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -3918,13 +3869,13 @@
     </row>
     <row r="40" spans="2:10">
       <c r="B40" s="5" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C40" s="29">
         <v>3140</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I40" t="b" cm="1">
         <f t="array" ref="I40">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H40," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -3937,13 +3888,13 @@
     </row>
     <row r="41" spans="2:10">
       <c r="B41" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C41" s="29">
         <v>0</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I41" t="b" cm="1">
         <f t="array" ref="I41">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H41," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -3956,13 +3907,13 @@
     </row>
     <row r="42" spans="2:10">
       <c r="B42" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C42" s="29">
         <v>0</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I42" t="b" cm="1">
         <f t="array" ref="I42">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H42," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -3975,13 +3926,13 @@
     </row>
     <row r="43" spans="2:10">
       <c r="B43" s="5" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C43" s="29">
         <v>5370</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="I43" t="b" cm="1">
         <f t="array" ref="I43">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H43," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -3994,13 +3945,13 @@
     </row>
     <row r="44" spans="2:10">
       <c r="B44" s="5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C44" s="29">
         <v>530</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="I44" t="b" cm="1">
         <f t="array" ref="I44">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H44," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -4013,13 +3964,13 @@
     </row>
     <row r="45" spans="2:10">
       <c r="B45" s="5" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C45" s="29">
         <v>0</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="I45" t="b" cm="1">
         <f t="array" ref="I45">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H45," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -4032,13 +3983,13 @@
     </row>
     <row r="46" spans="2:10">
       <c r="B46" s="5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="I46" t="b" cm="1">
         <f t="array" ref="I46">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H46," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -4051,13 +4002,13 @@
     </row>
     <row r="47" spans="2:10">
       <c r="B47" s="5" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C47" s="29">
         <v>3520</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I47" t="b" cm="1">
         <f t="array" ref="I47">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H47," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -4070,13 +4021,13 @@
     </row>
     <row r="48" spans="2:10">
       <c r="B48" s="5" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C48" s="29">
         <v>2150</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="I48" t="b" cm="1">
         <f t="array" ref="I48">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H48," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -4089,13 +4040,13 @@
     </row>
     <row r="49" spans="2:10">
       <c r="B49" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="I49" t="b" cm="1">
         <f t="array" ref="I49">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H49," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -4108,13 +4059,13 @@
     </row>
     <row r="50" spans="2:10">
       <c r="B50" s="5" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C50" s="29">
         <v>1770</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="I50" t="b" cm="1">
         <f t="array" ref="I50">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H50," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -4127,13 +4078,13 @@
     </row>
     <row r="51" spans="2:10">
       <c r="B51" s="5" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C51" s="29">
         <v>0</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="I51" t="b" cm="1">
         <f t="array" ref="I51">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H51," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -4146,13 +4097,13 @@
     </row>
     <row r="52" spans="2:10">
       <c r="B52" s="5" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C52" s="29">
         <v>394</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="I52" t="b" cm="1">
         <f t="array" ref="I52">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H52," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -4165,13 +4116,13 @@
     </row>
     <row r="53" spans="2:10">
       <c r="B53" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C53" s="29">
         <v>3660</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I53" t="b" cm="1">
         <f t="array" ref="I53">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H53," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -4184,13 +4135,13 @@
     </row>
     <row r="54" spans="2:10">
       <c r="B54" s="5" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C54" s="29">
         <v>0</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="I54" t="b" cm="1">
         <f t="array" ref="I54">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H54," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
@@ -4203,13 +4154,13 @@
     </row>
     <row r="55" spans="2:10">
       <c r="B55" s="5" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C55" s="29" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="I55" s="31" t="s">
         <v>6</v>
@@ -4221,18 +4172,18 @@
     </row>
     <row r="56" spans="2:10">
       <c r="B56" s="5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C56" s="29">
         <v>0</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
     </row>
     <row r="57" spans="2:10">
       <c r="B57" s="5" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C57" s="29">
         <v>0</v>
@@ -4240,7 +4191,7 @@
     </row>
     <row r="58" spans="2:10">
       <c r="B58" s="5" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C58" s="29">
         <v>11900</v>
@@ -4248,7 +4199,7 @@
     </row>
     <row r="59" spans="2:10">
       <c r="B59" s="5" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C59" s="29">
         <v>718</v>
@@ -4256,15 +4207,15 @@
     </row>
     <row r="60" spans="2:10">
       <c r="B60" s="5" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C60" s="29" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="61" spans="2:10">
       <c r="B61" s="5" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C61" s="29">
         <v>599</v>
@@ -4272,7 +4223,7 @@
     </row>
     <row r="62" spans="2:10">
       <c r="B62" s="5" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C62" s="29">
         <v>0</v>
@@ -4280,7 +4231,7 @@
     </row>
     <row r="63" spans="2:10">
       <c r="B63" s="5" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C63" s="29">
         <v>0</v>
@@ -4288,7 +4239,7 @@
     </row>
     <row r="64" spans="2:10">
       <c r="B64" s="5" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C64" s="29">
         <v>514</v>
@@ -4296,7 +4247,7 @@
     </row>
     <row r="65" spans="2:3">
       <c r="B65" s="5" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C65" s="29">
         <v>2150</v>
@@ -4304,7 +4255,7 @@
     </row>
     <row r="66" spans="2:3">
       <c r="B66" s="5" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C66" s="29">
         <v>0</v>
@@ -4312,7 +4263,7 @@
     </row>
     <row r="67" spans="2:3">
       <c r="B67" s="5" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C67" s="29">
         <v>0</v>
@@ -4320,7 +4271,7 @@
     </row>
     <row r="68" spans="2:3">
       <c r="B68" s="5" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C68" s="29">
         <v>1140</v>
@@ -4328,7 +4279,7 @@
     </row>
     <row r="69" spans="2:3">
       <c r="B69" s="5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C69" s="29">
         <v>1890</v>
@@ -4336,15 +4287,15 @@
     </row>
     <row r="70" spans="2:3">
       <c r="B70" s="5" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C70" s="29" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="71" spans="2:3">
       <c r="B71" s="5" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C71" s="29">
         <v>5190</v>
@@ -4352,7 +4303,7 @@
     </row>
     <row r="72" spans="2:3">
       <c r="B72" s="5" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C72" s="29">
         <v>0</v>
@@ -4360,7 +4311,7 @@
     </row>
     <row r="73" spans="2:3">
       <c r="B73" s="5" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C73" s="29">
         <v>2060</v>
@@ -4368,23 +4319,23 @@
     </row>
     <row r="74" spans="2:3">
       <c r="B74" s="5" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C74" s="29" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="75" spans="2:3">
       <c r="B75" s="5" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C75" s="29" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="76" spans="2:3">
       <c r="B76" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C76" s="29">
         <v>20300</v>
@@ -4392,15 +4343,15 @@
     </row>
     <row r="77" spans="2:3">
       <c r="B77" s="5" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C77" s="29" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="78" spans="2:3">
       <c r="B78" s="5" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C78" s="29">
         <v>0</v>
@@ -4408,7 +4359,7 @@
     </row>
     <row r="79" spans="2:3">
       <c r="B79" s="5" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C79" s="29">
         <v>1460</v>
@@ -4416,7 +4367,7 @@
     </row>
     <row r="80" spans="2:3">
       <c r="B80" s="5" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C80" s="29">
         <v>637</v>
@@ -4424,15 +4375,15 @@
     </row>
     <row r="81" spans="1:19">
       <c r="B81" s="5" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C81" s="29" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="82" spans="1:19">
       <c r="B82" s="5" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C82" s="29">
         <v>0</v>
@@ -4440,23 +4391,23 @@
     </row>
     <row r="83" spans="1:19">
       <c r="B83" s="5" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C83" s="29" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="84" spans="1:19">
       <c r="B84" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C84" s="40">
+        <v>148</v>
+      </c>
+      <c r="C84" s="38">
         <v>110000</v>
       </c>
     </row>
     <row r="85" spans="1:19">
       <c r="B85" s="12" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="87" spans="1:19">
@@ -4482,334 +4433,334 @@
     </row>
     <row r="89" spans="1:19" ht="24">
       <c r="B89" s="3" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:19" ht="19">
       <c r="B90" s="26" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="H90" s="26" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
     </row>
     <row r="91" spans="1:19">
       <c r="B91" s="14" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C91" s="16" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H91" s="14" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="I91" s="16" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="92" spans="1:19">
       <c r="B92" s="18" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C92" s="32">
         <v>1944</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="I92" s="29" cm="1">
-        <f t="array" ref="I92">SUMPRODUCT(ISNUMBER(SEARCH(H92,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>159</v>
+      </c>
+      <c r="I92" s="66">
+        <f>SUMIF($B$92:$B$113,H92,$C$92:$C$113)</f>
         <v>1944</v>
       </c>
     </row>
     <row r="93" spans="1:19">
       <c r="B93" s="18" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C93" s="32">
         <v>3450</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="I93" s="29" cm="1">
-        <f t="array" ref="I93">SUMPRODUCT(ISNUMBER(SEARCH(H93,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>135</v>
+      </c>
+      <c r="I93" s="66">
+        <f t="shared" ref="I93:I110" si="5">SUMIF($B$92:$B$113,H93,$C$92:$C$113)</f>
         <v>3450</v>
       </c>
     </row>
     <row r="94" spans="1:19">
       <c r="B94" s="18" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C94" s="32">
         <v>1329</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="I94" s="29" cm="1">
-        <f t="array" ref="I94">SUMPRODUCT(ISNUMBER(SEARCH(H94,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>110</v>
+      </c>
+      <c r="I94" s="66">
+        <f t="shared" si="5"/>
         <v>1329</v>
       </c>
     </row>
     <row r="95" spans="1:19">
       <c r="B95" s="18" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C95" s="32">
         <v>3842</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="I95" s="29" cm="1">
-        <f t="array" ref="I95">SUMPRODUCT(ISNUMBER(SEARCH(H95,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>157</v>
+      </c>
+      <c r="I95" s="66">
+        <f t="shared" si="5"/>
         <v>3842</v>
       </c>
     </row>
     <row r="96" spans="1:19">
       <c r="B96" s="18" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="C96" s="32">
         <v>4778</v>
       </c>
-      <c r="H96" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="I96" s="29" cm="1">
-        <f t="array" ref="I96">SUMPRODUCT(ISNUMBER(SEARCH(H96,$B$92:$B$113))*$C$92:$C$113)</f>
+      <c r="H96" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="I96" s="66">
+        <f t="shared" si="5"/>
         <v>4778</v>
       </c>
     </row>
     <row r="97" spans="2:9">
       <c r="B97" s="18" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C97" s="32">
         <v>3588</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="I97" s="29" cm="1">
-        <f t="array" ref="I97">SUMPRODUCT(ISNUMBER(SEARCH(H97,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>158</v>
+      </c>
+      <c r="I97" s="66">
+        <f t="shared" si="5"/>
         <v>3588</v>
       </c>
     </row>
     <row r="98" spans="2:9">
       <c r="B98" s="18" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C98" s="32">
         <v>2778</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="I98" s="29" cm="1">
-        <f t="array" ref="I98">SUMPRODUCT(ISNUMBER(SEARCH(H98,$B$92:$B$113))*$C$92:$C$113)</f>
-        <v>5012</v>
+        <v>113</v>
+      </c>
+      <c r="I98" s="66">
+        <f t="shared" si="5"/>
+        <v>2778</v>
       </c>
     </row>
     <row r="99" spans="2:9">
       <c r="B99" s="18" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C99" s="32">
         <v>9860</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="I99" s="29" cm="1">
-        <f t="array" ref="I99">SUMPRODUCT(ISNUMBER(SEARCH(H99,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>122</v>
+      </c>
+      <c r="I99" s="66">
+        <f t="shared" si="5"/>
         <v>9860</v>
       </c>
     </row>
     <row r="100" spans="2:9">
       <c r="B100" s="18" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C100" s="32">
         <v>6371</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I100" s="29" cm="1">
-        <f t="array" ref="I100">SUMPRODUCT(ISNUMBER(SEARCH(H100,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>107</v>
+      </c>
+      <c r="I100" s="66">
+        <f t="shared" si="5"/>
         <v>6371</v>
       </c>
     </row>
     <row r="101" spans="2:9">
       <c r="B101" s="18" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C101" s="32">
         <v>6000</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="I101" s="29" cm="1">
-        <f t="array" ref="I101">SUMPRODUCT(ISNUMBER(SEARCH(H101,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>156</v>
+      </c>
+      <c r="I101" s="66">
+        <f t="shared" si="5"/>
         <v>6000</v>
       </c>
     </row>
     <row r="102" spans="2:9">
       <c r="B102" s="18" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C102" s="32">
         <v>2931</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I102" s="29" cm="1">
-        <f t="array" ref="I102">SUMPRODUCT(ISNUMBER(SEARCH(H102,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>137</v>
+      </c>
+      <c r="I102" s="66">
+        <f t="shared" si="5"/>
         <v>2931</v>
       </c>
     </row>
     <row r="103" spans="2:9">
       <c r="B103" s="18" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C103" s="32">
         <v>7893</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I103" s="29" cm="1">
-        <f t="array" ref="I103">SUMPRODUCT(ISNUMBER(SEARCH(H103,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>152</v>
+      </c>
+      <c r="I103" s="66">
+        <f t="shared" si="5"/>
         <v>7893</v>
       </c>
     </row>
     <row r="104" spans="2:9">
       <c r="B104" s="18" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C104" s="32">
         <v>2234</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I104" s="29" cm="1">
-        <f t="array" ref="I104">SUMPRODUCT(ISNUMBER(SEARCH(H104,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>154</v>
+      </c>
+      <c r="I104" s="66">
+        <f t="shared" si="5"/>
         <v>2234</v>
       </c>
     </row>
     <row r="105" spans="2:9">
       <c r="B105" s="18" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C105" s="32">
         <v>6150</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="I105" s="29" cm="1">
-        <f t="array" ref="I105">SUMPRODUCT(ISNUMBER(SEARCH(H105,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>140</v>
+      </c>
+      <c r="I105" s="66">
+        <f>SUM(C105:C106)</f>
         <v>11740</v>
       </c>
     </row>
     <row r="106" spans="2:9">
       <c r="B106" s="18" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C106" s="32">
         <v>5590</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="I106" s="29" cm="1">
-        <f t="array" ref="I106">SUMPRODUCT(ISNUMBER(SEARCH(H106,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>153</v>
+      </c>
+      <c r="I106" s="66">
+        <f t="shared" si="5"/>
         <v>3037</v>
       </c>
     </row>
     <row r="107" spans="2:9">
       <c r="B107" s="18" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C107" s="32">
         <v>3037</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="I107" s="29" cm="1">
-        <f t="array" ref="I107">SUMPRODUCT(ISNUMBER(SEARCH(H107,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>155</v>
+      </c>
+      <c r="I107" s="66">
+        <f t="shared" si="5"/>
         <v>2811</v>
       </c>
     </row>
     <row r="108" spans="2:9">
       <c r="B108" s="18" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C108" s="32">
         <v>2811</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="I108" s="29" cm="1">
-        <f t="array" ref="I108">SUMPRODUCT(ISNUMBER(SEARCH(H108,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>161</v>
+      </c>
+      <c r="I108" s="66">
+        <f t="shared" si="5"/>
         <v>2450</v>
       </c>
     </row>
     <row r="109" spans="2:9">
       <c r="B109" s="18" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C109" s="32">
         <v>2450</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="I109" s="29" cm="1">
-        <f t="array" ref="I109">SUMPRODUCT(ISNUMBER(SEARCH(H109,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>103</v>
+      </c>
+      <c r="I109" s="66">
+        <f t="shared" si="5"/>
         <v>8940</v>
       </c>
     </row>
     <row r="110" spans="2:9">
       <c r="B110" s="18" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C110" s="32">
         <v>0</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I110" s="29" cm="1">
-        <f t="array" ref="I110">SUMPRODUCT(ISNUMBER(SEARCH(H110,$B$92:$B$113))*$C$92:$C$113)</f>
+        <v>162</v>
+      </c>
+      <c r="I110" s="66">
+        <f t="shared" si="5"/>
         <v>1458</v>
       </c>
     </row>
     <row r="111" spans="2:9">
       <c r="B111" s="18" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C111" s="32">
         <v>8940</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="I111" s="30">
-        <f>C113</f>
+        <v>148</v>
+      </c>
+      <c r="I111" s="38">
+        <f>SUM(I92:I110)</f>
         <v>87434</v>
       </c>
     </row>
     <row r="112" spans="2:9">
       <c r="B112" s="18" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C112" s="32">
         <v>1458</v>
@@ -4817,7 +4768,7 @@
     </row>
     <row r="113" spans="1:19">
       <c r="B113" s="33" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C113" s="34">
         <f>SUM(C92:C112)</f>
@@ -4826,7 +4777,7 @@
     </row>
     <row r="114" spans="1:19">
       <c r="B114" s="13" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="115" spans="1:19">
@@ -4855,1167 +4806,1167 @@
     </row>
     <row r="118" spans="1:19" ht="24">
       <c r="B118" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="119" spans="1:19" ht="19">
       <c r="B119" s="26" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="H119" s="26" t="s">
-        <v>275</v>
+        <v>309</v>
       </c>
     </row>
     <row r="120" spans="1:19" ht="18">
       <c r="B120" s="14" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="H120" s="14" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="I120" s="16" t="s">
-        <v>285</v>
+        <v>175</v>
       </c>
     </row>
     <row r="121" spans="1:19">
       <c r="B121" s="5" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C121" t="s">
-        <v>147</v>
-      </c>
-      <c r="D121" s="29">
+        <v>140</v>
+      </c>
+      <c r="D121" s="66">
         <v>787292</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="I121" s="29" cm="1">
+        <v>159</v>
+      </c>
+      <c r="I121" s="66" cm="1">
         <f t="array" ref="I121">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H121," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>1419236</v>
       </c>
     </row>
     <row r="122" spans="1:19">
       <c r="B122" s="5" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C122" t="s">
-        <v>114</v>
-      </c>
-      <c r="D122" s="29">
+        <v>107</v>
+      </c>
+      <c r="D122" s="66">
         <v>873429</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="I122" s="29" cm="1">
+        <v>135</v>
+      </c>
+      <c r="I122" s="66" cm="1">
         <f t="array" ref="I122">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H122," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2934594</v>
       </c>
     </row>
     <row r="123" spans="1:19">
       <c r="B123" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C123" t="s">
-        <v>144</v>
-      </c>
-      <c r="D123" s="29">
+        <v>137</v>
+      </c>
+      <c r="D123" s="66">
         <v>617861</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="I123" s="29" cm="1">
+        <v>110</v>
+      </c>
+      <c r="I123" s="66" cm="1">
         <f t="array" ref="I123">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H123," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>1142298</v>
       </c>
     </row>
     <row r="124" spans="1:19">
       <c r="B124" s="5" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C124" t="s">
-        <v>107</v>
-      </c>
-      <c r="D124" s="29">
+        <v>100</v>
+      </c>
+      <c r="D124" s="66">
         <v>1058822</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="I124" s="29" cm="1">
+        <v>157</v>
+      </c>
+      <c r="I124" s="66" cm="1">
         <f t="array" ref="I124">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H124," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>3285382</v>
       </c>
     </row>
     <row r="125" spans="1:19">
       <c r="B125" s="5" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C125" t="s">
-        <v>152</v>
-      </c>
-      <c r="D125" s="29">
+        <v>145</v>
+      </c>
+      <c r="D125" s="66">
         <v>846192</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="I125" s="29" cm="1">
+        <v>119</v>
+      </c>
+      <c r="I125" s="66" cm="1">
         <f t="array" ref="I125">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H125," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>3198425</v>
       </c>
     </row>
     <row r="126" spans="1:19">
       <c r="B126" s="5" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C126" t="s">
-        <v>142</v>
-      </c>
-      <c r="D126" s="29">
+        <v>135</v>
+      </c>
+      <c r="D126" s="66">
         <v>184561</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="I126" s="29" cm="1">
+        <v>158</v>
+      </c>
+      <c r="I126" s="66" cm="1">
         <f t="array" ref="I126">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H126," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2798493</v>
       </c>
     </row>
     <row r="127" spans="1:19">
       <c r="B127" s="5" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C127" t="s">
-        <v>120</v>
-      </c>
-      <c r="D127" s="29">
+        <v>113</v>
+      </c>
+      <c r="D127" s="66">
         <v>1299990</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="I127" s="29" cm="1">
+        <v>113</v>
+      </c>
+      <c r="I127" s="66" cm="1">
         <f t="array" ref="I127">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H127," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2239671</v>
       </c>
     </row>
     <row r="128" spans="1:19">
       <c r="B128" s="5" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C128" t="s">
-        <v>147</v>
-      </c>
-      <c r="D128" s="29">
+        <v>140</v>
+      </c>
+      <c r="D128" s="66">
         <v>642168</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="I128" s="29" cm="1">
+        <v>122</v>
+      </c>
+      <c r="I128" s="66" cm="1">
         <f t="array" ref="I128">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H128," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>6864697</v>
       </c>
     </row>
     <row r="129" spans="2:9">
       <c r="B129" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C129" t="s">
-        <v>141</v>
-      </c>
-      <c r="D129" s="29">
+        <v>134</v>
+      </c>
+      <c r="D129" s="66">
         <v>580299</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I129" s="29" cm="1">
+        <v>107</v>
+      </c>
+      <c r="I129" s="66" cm="1">
         <f t="array" ref="I129">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H129," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>4223240</v>
       </c>
     </row>
     <row r="130" spans="2:9">
       <c r="B130" s="5" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C130" t="s">
-        <v>148</v>
-      </c>
-      <c r="D130" s="29">
+        <v>141</v>
+      </c>
+      <c r="D130" s="66">
         <v>548943</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="I130" s="29" cm="1">
+        <v>156</v>
+      </c>
+      <c r="I130" s="66" cm="1">
         <f t="array" ref="I130">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H130," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>4368519</v>
       </c>
     </row>
     <row r="131" spans="2:9">
       <c r="B131" s="5" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C131" t="s">
-        <v>131</v>
-      </c>
-      <c r="D131" s="29">
+        <v>124</v>
+      </c>
+      <c r="D131" s="66">
         <v>612375</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I131" s="29" cm="1">
+        <v>137</v>
+      </c>
+      <c r="I131" s="66" cm="1">
         <f t="array" ref="I131">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H131," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2322955</v>
       </c>
     </row>
     <row r="132" spans="2:9">
       <c r="B132" s="5" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C132" t="s">
-        <v>130</v>
-      </c>
-      <c r="D132" s="29">
+        <v>123</v>
+      </c>
+      <c r="D132" s="66">
         <v>323958</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I132" s="29" cm="1">
+        <v>152</v>
+      </c>
+      <c r="I132" s="66" cm="1">
         <f t="array" ref="I132">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H132," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>6230375</v>
       </c>
     </row>
     <row r="133" spans="2:9">
       <c r="B133" s="5" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C133" t="s">
-        <v>151</v>
-      </c>
-      <c r="D133" s="29">
+        <v>144</v>
+      </c>
+      <c r="D133" s="66">
         <v>367651</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I133" s="29" cm="1">
+        <v>154</v>
+      </c>
+      <c r="I133" s="66" cm="1">
         <f t="array" ref="I133">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H133," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2065476</v>
       </c>
     </row>
     <row r="134" spans="2:9">
       <c r="B134" s="5" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C134" t="s">
-        <v>109</v>
-      </c>
-      <c r="D134" s="29">
+        <v>102</v>
+      </c>
+      <c r="D134" s="66">
         <v>884375</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="I134" s="29" cm="1">
+        <v>140</v>
+      </c>
+      <c r="I134" s="66" cm="1">
         <f t="array" ref="I134">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H134," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>8749623</v>
       </c>
     </row>
     <row r="135" spans="2:9">
       <c r="B135" s="5" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C135" t="s">
-        <v>114</v>
-      </c>
-      <c r="D135" s="29">
+        <v>107</v>
+      </c>
+      <c r="D135" s="66">
         <v>746907</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="I135" s="29" cm="1">
+        <v>153</v>
+      </c>
+      <c r="I135" s="66" cm="1">
         <f t="array" ref="I135">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H135," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2345226</v>
       </c>
     </row>
     <row r="136" spans="2:9">
       <c r="B136" s="5" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C136" t="s">
-        <v>110</v>
-      </c>
-      <c r="D136" s="29">
+        <v>103</v>
+      </c>
+      <c r="D136" s="66">
         <v>991489</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="I136" s="29" cm="1">
+        <v>155</v>
+      </c>
+      <c r="I136" s="66" cm="1">
         <f t="array" ref="I136">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H136," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2126767</v>
       </c>
     </row>
     <row r="137" spans="2:9">
       <c r="B137" s="5" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C137" t="s">
-        <v>110</v>
-      </c>
-      <c r="D137" s="29">
+        <v>103</v>
+      </c>
+      <c r="D137" s="66">
         <v>1424150</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="I137" s="29" cm="1">
+        <v>161</v>
+      </c>
+      <c r="I137" s="66" cm="1">
         <f t="array" ref="I137">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H137," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2087707</v>
       </c>
     </row>
     <row r="138" spans="2:9">
       <c r="B138" s="5" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C138" t="s">
-        <v>108</v>
-      </c>
-      <c r="D138" s="29">
+        <v>101</v>
+      </c>
+      <c r="D138" s="66">
         <v>789422</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="I138" s="29" cm="1">
+        <v>103</v>
+      </c>
+      <c r="I138" s="66" cm="1">
         <f t="array" ref="I138">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H138," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>7295297</v>
       </c>
     </row>
     <row r="139" spans="2:9">
       <c r="B139" s="5" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C139" t="s">
-        <v>110</v>
-      </c>
-      <c r="D139" s="29">
+        <v>103</v>
+      </c>
+      <c r="D139" s="66">
         <v>372759</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I139" s="29" cm="1">
+        <v>162</v>
+      </c>
+      <c r="I139" s="66" cm="1">
         <f t="array" ref="I139">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H139," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>947950</v>
       </c>
     </row>
     <row r="140" spans="2:9">
       <c r="B140" s="5" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C140" t="s">
-        <v>147</v>
-      </c>
-      <c r="D140" s="29">
+        <v>140</v>
+      </c>
+      <c r="D140" s="66">
         <v>492032</v>
       </c>
       <c r="H140" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="I140" s="30">
+        <v>148</v>
+      </c>
+      <c r="I140" s="38">
         <f>SUM(D121:D210)</f>
         <v>66645931</v>
       </c>
     </row>
     <row r="141" spans="2:9">
       <c r="B141" s="5" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C141" t="s">
-        <v>146</v>
-      </c>
-      <c r="D141" s="29">
+        <v>139</v>
+      </c>
+      <c r="D141" s="66">
         <v>441463</v>
       </c>
     </row>
     <row r="142" spans="2:9">
       <c r="B142" s="5" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C142" t="s">
-        <v>110</v>
-      </c>
-      <c r="D142" s="29">
+        <v>103</v>
+      </c>
+      <c r="D142" s="66">
         <v>1951045</v>
       </c>
     </row>
     <row r="143" spans="2:9">
       <c r="B143" s="5" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C143" t="s">
-        <v>111</v>
-      </c>
-      <c r="D143" s="29">
+        <v>104</v>
+      </c>
+      <c r="D143" s="66">
         <v>243722</v>
       </c>
     </row>
     <row r="144" spans="2:9">
       <c r="B144" s="5" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C144" t="s">
-        <v>147</v>
-      </c>
-      <c r="D144" s="29">
+        <v>140</v>
+      </c>
+      <c r="D144" s="66">
         <v>1122560</v>
       </c>
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="5" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C145" t="s">
-        <v>114</v>
-      </c>
-      <c r="D145" s="29">
+        <v>107</v>
+      </c>
+      <c r="D145" s="66">
         <v>581354</v>
       </c>
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="5" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C146" t="s">
-        <v>115</v>
-      </c>
-      <c r="D146" s="29">
+        <v>108</v>
+      </c>
+      <c r="D146" s="66">
         <v>405369</v>
       </c>
     </row>
     <row r="147" spans="2:4">
       <c r="B147" s="5" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C147" t="s">
-        <v>107</v>
-      </c>
-      <c r="D147" s="29">
+        <v>100</v>
+      </c>
+      <c r="D147" s="66">
         <v>520546</v>
       </c>
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="5" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C148" t="s">
-        <v>140</v>
-      </c>
-      <c r="D148" s="29">
+        <v>133</v>
+      </c>
+      <c r="D148" s="66">
         <v>494937</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="5" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C149" t="s">
-        <v>129</v>
-      </c>
-      <c r="D149" s="29">
+        <v>122</v>
+      </c>
+      <c r="D149" s="66">
         <v>780363</v>
       </c>
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="5" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C150" t="s">
-        <v>129</v>
-      </c>
-      <c r="D150" s="29">
+        <v>122</v>
+      </c>
+      <c r="D150" s="66">
         <v>548811</v>
       </c>
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="5" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C151" t="s">
-        <v>119</v>
-      </c>
-      <c r="D151" s="29">
+        <v>112</v>
+      </c>
+      <c r="D151" s="66">
         <v>841277</v>
       </c>
     </row>
     <row r="152" spans="2:4">
       <c r="B152" s="5" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C152" t="s">
-        <v>123</v>
-      </c>
-      <c r="D152" s="29">
+        <v>116</v>
+      </c>
+      <c r="D152" s="66">
         <v>236953</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="5" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C153" t="s">
-        <v>108</v>
-      </c>
-      <c r="D153" s="29">
+        <v>101</v>
+      </c>
+      <c r="D153" s="66">
         <v>483450</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="5" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C154" t="s">
-        <v>139</v>
-      </c>
-      <c r="D154" s="29">
+        <v>132</v>
+      </c>
+      <c r="D154" s="66">
         <v>478200</v>
       </c>
     </row>
     <row r="155" spans="2:4">
       <c r="B155" s="5" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C155" t="s">
-        <v>145</v>
-      </c>
-      <c r="D155" s="29">
+        <v>138</v>
+      </c>
+      <c r="D155" s="66">
         <v>825771</v>
       </c>
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="5" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C156" t="s">
-        <v>147</v>
-      </c>
-      <c r="D156" s="29">
+        <v>140</v>
+      </c>
+      <c r="D156" s="66">
         <v>309171</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="5" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C157" t="s">
-        <v>111</v>
-      </c>
-      <c r="D157" s="29">
+        <v>104</v>
+      </c>
+      <c r="D157" s="66">
         <v>623704</v>
       </c>
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="5" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C158" t="s">
-        <v>135</v>
-      </c>
-      <c r="D158" s="29">
+        <v>128</v>
+      </c>
+      <c r="D158" s="66">
         <v>304227</v>
       </c>
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="5" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C159" t="s">
-        <v>144</v>
-      </c>
-      <c r="D159" s="29">
+        <v>137</v>
+      </c>
+      <c r="D159" s="66">
         <v>499783</v>
       </c>
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C160" t="s">
-        <v>118</v>
-      </c>
-      <c r="D160" s="29">
+        <v>111</v>
+      </c>
+      <c r="D160" s="66">
         <v>444881</v>
       </c>
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="5" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C161" t="s">
-        <v>142</v>
-      </c>
-      <c r="D161" s="29">
+        <v>135</v>
+      </c>
+      <c r="D161" s="66">
         <v>583943</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C162" t="s">
-        <v>136</v>
-      </c>
-      <c r="D162" s="29">
+        <v>129</v>
+      </c>
+      <c r="D162" s="66">
         <v>61388</v>
       </c>
     </row>
     <row r="163" spans="2:4">
       <c r="B163" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C163" t="s">
-        <v>118</v>
-      </c>
-      <c r="D163" s="29">
+        <v>111</v>
+      </c>
+      <c r="D163" s="66">
         <v>67822</v>
       </c>
     </row>
     <row r="164" spans="2:4">
       <c r="B164" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C164" t="s">
-        <v>124</v>
-      </c>
-      <c r="D164" s="29">
+        <v>117</v>
+      </c>
+      <c r="D164" s="66">
         <v>1857878</v>
       </c>
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C165" t="s">
-        <v>118</v>
-      </c>
-      <c r="D165" s="29">
+        <v>111</v>
+      </c>
+      <c r="D165" s="66">
         <v>833267</v>
       </c>
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C166" t="s">
-        <v>142</v>
-      </c>
-      <c r="D166" s="29">
+        <v>135</v>
+      </c>
+      <c r="D166" s="66">
         <v>646387</v>
       </c>
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="5" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C167" t="s">
-        <v>142</v>
-      </c>
-      <c r="D167" s="29">
+        <v>135</v>
+      </c>
+      <c r="D167" s="66">
         <v>456577</v>
       </c>
     </row>
     <row r="168" spans="2:4">
       <c r="B168" s="5" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C168" t="s">
-        <v>107</v>
-      </c>
-      <c r="D168" s="29">
+        <v>100</v>
+      </c>
+      <c r="D168" s="66">
         <v>522543</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="5" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C169" t="s">
-        <v>140</v>
-      </c>
-      <c r="D169" s="29">
+        <v>133</v>
+      </c>
+      <c r="D169" s="66">
         <v>429907</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="5" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C170" t="s">
-        <v>147</v>
-      </c>
-      <c r="D170" s="29">
+        <v>140</v>
+      </c>
+      <c r="D170" s="66">
         <v>1253349</v>
       </c>
     </row>
     <row r="171" spans="2:4">
       <c r="B171" s="5" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C171" t="s">
-        <v>107</v>
-      </c>
-      <c r="D171" s="29">
+        <v>100</v>
+      </c>
+      <c r="D171" s="66">
         <v>615636</v>
       </c>
     </row>
     <row r="172" spans="2:4">
       <c r="B172" s="5" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C172" t="s">
-        <v>144</v>
-      </c>
-      <c r="D172" s="29">
+        <v>137</v>
+      </c>
+      <c r="D172" s="66">
         <v>1205311</v>
       </c>
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="5" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C173" t="s">
-        <v>124</v>
-      </c>
-      <c r="D173" s="29">
+        <v>117</v>
+      </c>
+      <c r="D173" s="66">
         <v>451527</v>
       </c>
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="5" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="C174" t="s">
-        <v>126</v>
-      </c>
-      <c r="D174" s="29">
+        <v>119</v>
+      </c>
+      <c r="D174" s="66">
         <v>1769013</v>
       </c>
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="5" t="s">
-        <v>233</v>
+        <v>306</v>
       </c>
       <c r="C175" t="s">
-        <v>148</v>
-      </c>
-      <c r="D175" s="29">
+        <v>141</v>
+      </c>
+      <c r="D175" s="66">
         <v>579152</v>
       </c>
     </row>
     <row r="176" spans="2:4">
       <c r="B176" s="5" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C176" t="s">
-        <v>117</v>
-      </c>
-      <c r="D176" s="29">
+        <v>110</v>
+      </c>
+      <c r="D176" s="66">
         <v>380737</v>
       </c>
     </row>
     <row r="177" spans="2:4">
       <c r="B177" s="5" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C177" t="s">
-        <v>111</v>
-      </c>
-      <c r="D177" s="29">
+        <v>104</v>
+      </c>
+      <c r="D177" s="66">
         <v>737083</v>
       </c>
     </row>
     <row r="178" spans="2:4">
       <c r="B178" s="5" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C178" t="s">
-        <v>129</v>
-      </c>
-      <c r="D178" s="29">
+        <v>122</v>
+      </c>
+      <c r="D178" s="66">
         <v>2967851</v>
       </c>
     </row>
     <row r="179" spans="2:4">
       <c r="B179" s="5" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C179" t="s">
-        <v>139</v>
-      </c>
-      <c r="D179" s="29">
+        <v>132</v>
+      </c>
+      <c r="D179" s="66">
         <v>358128</v>
       </c>
     </row>
     <row r="180" spans="2:4">
       <c r="B180" s="5" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C180" t="s">
-        <v>117</v>
-      </c>
-      <c r="D180" s="29">
+        <v>110</v>
+      </c>
+      <c r="D180" s="66">
         <v>761561</v>
       </c>
     </row>
     <row r="181" spans="2:4">
       <c r="B181" s="5" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C181" t="s">
-        <v>142</v>
-      </c>
-      <c r="D181" s="29">
+        <v>135</v>
+      </c>
+      <c r="D181" s="66">
         <v>684874</v>
       </c>
     </row>
     <row r="182" spans="2:4">
       <c r="B182" s="5" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C182" t="s">
-        <v>121</v>
-      </c>
-      <c r="D182" s="29">
+        <v>114</v>
+      </c>
+      <c r="D182" s="66">
         <v>1333431</v>
       </c>
     </row>
     <row r="183" spans="2:4">
       <c r="B183" s="5" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C183" t="s">
-        <v>142</v>
-      </c>
-      <c r="D183" s="29">
+        <v>135</v>
+      </c>
+      <c r="D183" s="66">
         <v>295726</v>
       </c>
     </row>
     <row r="184" spans="2:4">
       <c r="B184" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C184" t="s">
-        <v>136</v>
-      </c>
-      <c r="D184" s="29">
+        <v>129</v>
+      </c>
+      <c r="D184" s="66">
         <v>1120895</v>
       </c>
     </row>
     <row r="185" spans="2:4">
       <c r="B185" s="5" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C185" t="s">
-        <v>119</v>
-      </c>
-      <c r="D185" s="29">
+        <v>112</v>
+      </c>
+      <c r="D185" s="66">
         <v>519070</v>
       </c>
     </row>
     <row r="186" spans="2:4">
       <c r="B186" s="5" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C186" t="s">
-        <v>147</v>
-      </c>
-      <c r="D186" s="29">
+        <v>140</v>
+      </c>
+      <c r="D186" s="66">
         <v>80285</v>
       </c>
     </row>
     <row r="187" spans="2:4">
       <c r="B187" s="5" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C187" t="s">
-        <v>142</v>
-      </c>
-      <c r="D187" s="29">
+        <v>135</v>
+      </c>
+      <c r="D187" s="66">
         <v>82526</v>
       </c>
     </row>
     <row r="188" spans="2:4">
       <c r="B188" s="5" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C188" t="s">
-        <v>140</v>
-      </c>
-      <c r="D188" s="29">
+        <v>133</v>
+      </c>
+      <c r="D188" s="66">
         <v>256257</v>
       </c>
     </row>
     <row r="189" spans="2:4">
       <c r="B189" s="5" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C189" t="s">
-        <v>129</v>
-      </c>
-      <c r="D189" s="29">
+        <v>122</v>
+      </c>
+      <c r="D189" s="66">
         <v>1010547</v>
       </c>
     </row>
     <row r="190" spans="2:4">
       <c r="B190" s="5" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C190" t="s">
-        <v>118</v>
-      </c>
-      <c r="D190" s="29">
+        <v>111</v>
+      </c>
+      <c r="D190" s="66">
         <v>1103084</v>
       </c>
     </row>
     <row r="191" spans="2:4">
       <c r="B191" s="5" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C191" t="s">
-        <v>147</v>
-      </c>
-      <c r="D191" s="29">
+        <v>140</v>
+      </c>
+      <c r="D191" s="66">
         <v>632181</v>
       </c>
     </row>
     <row r="192" spans="2:4">
       <c r="B192" s="5" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C192" t="s">
-        <v>147</v>
-      </c>
-      <c r="D192" s="29">
+        <v>140</v>
+      </c>
+      <c r="D192" s="66">
         <v>1323231</v>
       </c>
     </row>
     <row r="193" spans="2:4">
       <c r="B193" s="5" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C193" t="s">
-        <v>147</v>
-      </c>
-      <c r="D193" s="29">
+        <v>140</v>
+      </c>
+      <c r="D193" s="66">
         <v>1289116</v>
       </c>
     </row>
     <row r="194" spans="2:4">
       <c r="B194" s="5" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C194" t="s">
-        <v>110</v>
-      </c>
-      <c r="D194" s="29">
+        <v>103</v>
+      </c>
+      <c r="D194" s="66">
         <v>1221243</v>
       </c>
     </row>
     <row r="195" spans="2:4">
       <c r="B195" s="5" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C195" t="s">
-        <v>120</v>
-      </c>
-      <c r="D195" s="29">
+        <v>113</v>
+      </c>
+      <c r="D195" s="66">
         <v>939681</v>
       </c>
     </row>
     <row r="196" spans="2:4">
       <c r="B196" s="5" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C196" t="s">
-        <v>154</v>
-      </c>
-      <c r="D196" s="29">
+        <v>147</v>
+      </c>
+      <c r="D196" s="66">
         <v>522258</v>
       </c>
     </row>
     <row r="197" spans="2:4">
       <c r="B197" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C197" t="s">
-        <v>107</v>
-      </c>
-      <c r="D197" s="29">
+        <v>100</v>
+      </c>
+      <c r="D197" s="66">
         <v>923191</v>
       </c>
     </row>
     <row r="198" spans="2:4">
       <c r="B198" s="5" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C198" t="s">
-        <v>110</v>
-      </c>
-      <c r="D198" s="29">
+        <v>103</v>
+      </c>
+      <c r="D198" s="66">
         <v>807598</v>
       </c>
     </row>
     <row r="199" spans="2:4">
       <c r="B199" s="5" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C199" t="s">
-        <v>132</v>
-      </c>
-      <c r="D199" s="29">
+        <v>125</v>
+      </c>
+      <c r="D199" s="66">
         <v>385165</v>
       </c>
     </row>
     <row r="200" spans="2:4">
       <c r="B200" s="5" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="C200" t="s">
-        <v>108</v>
-      </c>
-      <c r="D200" s="29">
+        <v>101</v>
+      </c>
+      <c r="D200" s="66">
         <v>768127</v>
       </c>
     </row>
     <row r="201" spans="2:4">
       <c r="B201" s="5" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C201" t="s">
-        <v>129</v>
-      </c>
-      <c r="D201" s="29">
+        <v>122</v>
+      </c>
+      <c r="D201" s="66">
         <v>1557125</v>
       </c>
     </row>
     <row r="202" spans="2:4">
       <c r="B202" s="5" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="C202" t="s">
-        <v>150</v>
-      </c>
-      <c r="D202" s="29">
+        <v>143</v>
+      </c>
+      <c r="D202" s="66">
         <v>807553</v>
       </c>
     </row>
     <row r="203" spans="2:4">
       <c r="B203" s="5" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="C203" t="s">
-        <v>146</v>
-      </c>
-      <c r="D203" s="29">
+        <v>139</v>
+      </c>
+      <c r="D203" s="66">
         <v>814743</v>
       </c>
     </row>
     <row r="204" spans="2:4">
       <c r="B204" s="5" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C204" t="s">
-        <v>126</v>
-      </c>
-      <c r="D204" s="29">
+        <v>119</v>
+      </c>
+      <c r="D204" s="66">
         <v>1429412</v>
       </c>
     </row>
     <row r="205" spans="2:4">
       <c r="B205" s="5" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C205" t="s">
-        <v>114</v>
-      </c>
-      <c r="D205" s="29">
+        <v>107</v>
+      </c>
+      <c r="D205" s="66">
         <v>361182</v>
       </c>
     </row>
     <row r="206" spans="2:4">
       <c r="B206" s="5" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="C206" t="s">
-        <v>114</v>
-      </c>
-      <c r="D206" s="29">
+        <v>107</v>
+      </c>
+      <c r="D206" s="66">
         <v>567263</v>
       </c>
     </row>
     <row r="207" spans="2:4">
       <c r="B207" s="5" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="C207" t="s">
-        <v>114</v>
-      </c>
-      <c r="D207" s="29">
+        <v>107</v>
+      </c>
+      <c r="D207" s="66">
         <v>1093105</v>
       </c>
     </row>
     <row r="208" spans="2:4">
       <c r="B208" s="5" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="C208" t="s">
-        <v>110</v>
-      </c>
-      <c r="D208" s="29">
+        <v>103</v>
+      </c>
+      <c r="D208" s="66">
         <v>527013</v>
       </c>
     </row>
     <row r="209" spans="1:19">
       <c r="B209" s="5" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C209" t="s">
-        <v>147</v>
-      </c>
-      <c r="D209" s="29">
+        <v>140</v>
+      </c>
+      <c r="D209" s="66">
         <v>818238</v>
       </c>
     </row>
     <row r="210" spans="1:19">
       <c r="B210" s="8" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C210" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="D210" s="30">
+        <v>123</v>
+      </c>
+      <c r="D210" s="38">
         <v>250489</v>
       </c>
     </row>
     <row r="211" spans="1:19">
       <c r="B211" s="12" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
     </row>
     <row r="213" spans="1:19">
@@ -6041,334 +5992,334 @@
     </row>
     <row r="215" spans="1:19" ht="24">
       <c r="B215" s="3" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
     </row>
     <row r="216" spans="1:19" ht="19">
       <c r="B216" s="26" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="H216" s="26" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="217" spans="1:19">
       <c r="B217" s="14" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C217" s="16" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="H217" s="14" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="I217" s="16" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="218" spans="1:19">
       <c r="B218" s="18" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C218" s="32">
         <v>3258</v>
       </c>
-      <c r="H218" s="35" t="s">
-        <v>166</v>
-      </c>
-      <c r="I218" s="36" cm="1">
-        <f t="array" ref="I218">SUMPRODUCT(ISNUMBER(SEARCH(H218,$B$218:$B$238))*$C$218:$C$238)</f>
+      <c r="H218" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="I218" s="66">
+        <f>SUMIF($B$218:$B$238,H218,$C$218:$C$238)</f>
         <v>3258</v>
       </c>
     </row>
     <row r="219" spans="1:19">
       <c r="B219" s="18" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C219" s="32">
         <v>5790</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="I219" s="29" cm="1">
-        <f t="array" ref="I219">SUMPRODUCT(ISNUMBER(SEARCH(H219,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>135</v>
+      </c>
+      <c r="I219" s="66">
+        <f t="shared" ref="I219:I236" si="6">SUMIF($B$218:$B$238,H219,$C$218:$C$238)</f>
         <v>5790</v>
       </c>
     </row>
     <row r="220" spans="1:19">
       <c r="B220" s="18" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C220" s="32">
         <v>2531</v>
       </c>
       <c r="H220" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="I220" s="29" cm="1">
-        <f t="array" ref="I220">SUMPRODUCT(ISNUMBER(SEARCH(H220,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>110</v>
+      </c>
+      <c r="I220" s="66">
+        <f t="shared" si="6"/>
         <v>2531</v>
       </c>
     </row>
     <row r="221" spans="1:19">
       <c r="B221" s="18" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C221" s="32">
         <v>5679</v>
       </c>
       <c r="H221" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="I221" s="29" cm="1">
-        <f t="array" ref="I221">SUMPRODUCT(ISNUMBER(SEARCH(H221,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>157</v>
+      </c>
+      <c r="I221" s="66">
+        <f t="shared" si="6"/>
         <v>5679</v>
       </c>
     </row>
     <row r="222" spans="1:19">
       <c r="B222" s="18" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="C222" s="32">
         <v>5738</v>
       </c>
       <c r="H222" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="I222" s="29" cm="1">
-        <f t="array" ref="I222">SUMPRODUCT(ISNUMBER(SEARCH(H222,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>119</v>
+      </c>
+      <c r="I222" s="66">
+        <f t="shared" si="6"/>
         <v>5738</v>
       </c>
     </row>
     <row r="223" spans="1:19">
       <c r="B223" s="18" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C223" s="32">
         <v>4285</v>
       </c>
       <c r="H223" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="I223" s="29" cm="1">
-        <f t="array" ref="I223">SUMPRODUCT(ISNUMBER(SEARCH(H223,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>158</v>
+      </c>
+      <c r="I223" s="66">
+        <f t="shared" si="6"/>
         <v>4285</v>
       </c>
     </row>
     <row r="224" spans="1:19">
       <c r="B224" s="18" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C224" s="32">
         <v>3172</v>
       </c>
       <c r="H224" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="I224" s="29" cm="1">
-        <f t="array" ref="I224">SUMPRODUCT(ISNUMBER(SEARCH(H224,$B$218:$B$238))*$C$218:$C$238)</f>
-        <v>6787</v>
+        <v>113</v>
+      </c>
+      <c r="I224" s="66">
+        <f t="shared" si="6"/>
+        <v>3172</v>
       </c>
     </row>
     <row r="225" spans="2:9">
       <c r="B225" s="18" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C225" s="32">
         <v>11227</v>
       </c>
       <c r="H225" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="I225" s="29" cm="1">
-        <f t="array" ref="I225">SUMPRODUCT(ISNUMBER(SEARCH(H225,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>122</v>
+      </c>
+      <c r="I225" s="66">
+        <f t="shared" si="6"/>
         <v>11227</v>
       </c>
     </row>
     <row r="226" spans="2:9">
       <c r="B226" s="18" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C226" s="32">
         <v>10540</v>
       </c>
       <c r="H226" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I226" s="29" cm="1">
-        <f t="array" ref="I226">SUMPRODUCT(ISNUMBER(SEARCH(H226,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>107</v>
+      </c>
+      <c r="I226" s="66">
+        <f t="shared" si="6"/>
         <v>10540</v>
       </c>
     </row>
     <row r="227" spans="2:9">
       <c r="B227" s="18" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C227" s="32">
         <v>7930</v>
       </c>
       <c r="H227" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="I227" s="29" cm="1">
-        <f t="array" ref="I227">SUMPRODUCT(ISNUMBER(SEARCH(H227,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>156</v>
+      </c>
+      <c r="I227" s="66">
+        <f t="shared" si="6"/>
         <v>7930</v>
       </c>
     </row>
     <row r="228" spans="2:9">
       <c r="B228" s="18" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C228" s="32">
         <v>5666</v>
       </c>
       <c r="H228" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I228" s="29" cm="1">
-        <f t="array" ref="I228">SUMPRODUCT(ISNUMBER(SEARCH(H228,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>137</v>
+      </c>
+      <c r="I228" s="66">
+        <f t="shared" si="6"/>
         <v>5666</v>
       </c>
     </row>
     <row r="229" spans="2:9">
       <c r="B229" s="18" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C229" s="32">
         <v>10124</v>
       </c>
       <c r="H229" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I229" s="29" cm="1">
-        <f t="array" ref="I229">SUMPRODUCT(ISNUMBER(SEARCH(H229,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>152</v>
+      </c>
+      <c r="I229" s="66">
+        <f t="shared" si="6"/>
         <v>10124</v>
       </c>
     </row>
     <row r="230" spans="2:9">
       <c r="B230" s="18" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C230" s="32">
         <v>3615</v>
       </c>
       <c r="H230" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I230" s="29" cm="1">
-        <f t="array" ref="I230">SUMPRODUCT(ISNUMBER(SEARCH(H230,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>154</v>
+      </c>
+      <c r="I230" s="66">
+        <f t="shared" si="6"/>
         <v>3615</v>
       </c>
     </row>
     <row r="231" spans="2:9">
       <c r="B231" s="18" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C231" s="32">
         <v>8140</v>
       </c>
       <c r="H231" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="I231" s="29" cm="1">
-        <f t="array" ref="I231">SUMPRODUCT(ISNUMBER(SEARCH(H231,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>140</v>
+      </c>
+      <c r="I231" s="66">
+        <f>SUM(C231+C232)</f>
         <v>15760</v>
       </c>
     </row>
     <row r="232" spans="2:9">
       <c r="B232" s="18" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C232" s="32">
         <v>7620</v>
       </c>
       <c r="H232" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="I232" s="29" cm="1">
-        <f t="array" ref="I232">SUMPRODUCT(ISNUMBER(SEARCH(H232,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>153</v>
+      </c>
+      <c r="I232" s="66">
+        <f t="shared" si="6"/>
         <v>3375</v>
       </c>
     </row>
     <row r="233" spans="2:9">
       <c r="B233" s="18" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C233" s="32">
         <v>3375</v>
       </c>
       <c r="H233" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="I233" s="29" cm="1">
-        <f t="array" ref="I233">SUMPRODUCT(ISNUMBER(SEARCH(H233,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>155</v>
+      </c>
+      <c r="I233" s="66">
+        <f t="shared" si="6"/>
         <v>4275</v>
       </c>
     </row>
     <row r="234" spans="2:9">
       <c r="B234" s="18" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C234" s="32">
         <v>4275</v>
       </c>
       <c r="H234" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="I234" s="29" cm="1">
-        <f t="array" ref="I234">SUMPRODUCT(ISNUMBER(SEARCH(H234,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>161</v>
+      </c>
+      <c r="I234" s="66">
+        <f t="shared" si="6"/>
         <v>3201</v>
       </c>
     </row>
     <row r="235" spans="2:9">
       <c r="B235" s="18" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C235" s="32">
         <v>3201</v>
       </c>
       <c r="H235" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="I235" s="29" cm="1">
-        <f t="array" ref="I235">SUMPRODUCT(ISNUMBER(SEARCH(H235,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>103</v>
+      </c>
+      <c r="I235" s="66">
+        <f t="shared" si="6"/>
         <v>11300</v>
       </c>
     </row>
     <row r="236" spans="2:9">
       <c r="B236" s="18" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C236" s="32">
         <v>0</v>
       </c>
       <c r="H236" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I236" s="29" cm="1">
-        <f t="array" ref="I236">SUMPRODUCT(ISNUMBER(SEARCH(H236,$B$218:$B$238))*$C$218:$C$238)</f>
+        <v>162</v>
+      </c>
+      <c r="I236" s="66">
+        <f t="shared" si="6"/>
         <v>2563</v>
       </c>
     </row>
     <row r="237" spans="2:9">
       <c r="B237" s="18" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C237" s="32">
         <v>11300</v>
       </c>
       <c r="H237" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="I237" s="30">
-        <f>C239</f>
+        <v>148</v>
+      </c>
+      <c r="I237" s="38">
+        <f>SUM(I218:I236)</f>
         <v>120029</v>
       </c>
     </row>
     <row r="238" spans="2:9">
       <c r="B238" s="18" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C238" s="32">
         <v>2563</v>
@@ -6376,7 +6327,7 @@
     </row>
     <row r="239" spans="2:9">
       <c r="B239" s="33" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C239" s="34">
         <f>SUM(C218:C238)</f>
@@ -6385,7 +6336,7 @@
     </row>
     <row r="240" spans="2:9">
       <c r="B240" s="13" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="242" spans="1:19">
@@ -6411,334 +6362,334 @@
     </row>
     <row r="244" spans="1:19" ht="24">
       <c r="B244" s="3" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
     </row>
     <row r="245" spans="1:19" ht="19">
       <c r="B245" s="26" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="H245" s="26" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="246" spans="1:19">
       <c r="B246" s="14" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C246" s="16" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="H246" s="14" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="I246" s="16" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
     </row>
     <row r="247" spans="1:19">
       <c r="B247" s="18" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C247" s="32">
         <v>4</v>
       </c>
       <c r="H247" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="I247" s="29" cm="1">
-        <f t="array" ref="I247">SUMPRODUCT(ISNUMBER(SEARCH(H247,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>159</v>
+      </c>
+      <c r="I247" s="29">
+        <f>SUMIF($B$247:$B$267,H247,$C$247:$C$267)</f>
         <v>4</v>
       </c>
     </row>
     <row r="248" spans="1:19">
       <c r="B248" s="18" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C248" s="32">
         <v>7</v>
       </c>
       <c r="H248" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="I248" s="29" cm="1">
-        <f t="array" ref="I248">SUMPRODUCT(ISNUMBER(SEARCH(H248,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>135</v>
+      </c>
+      <c r="I248" s="29">
+        <f t="shared" ref="I248:I265" si="7">SUMIF($B$247:$B$267,H248,$C$247:$C$267)</f>
         <v>7</v>
       </c>
     </row>
     <row r="249" spans="1:19">
       <c r="B249" s="18" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C249" s="32">
         <v>3</v>
       </c>
       <c r="H249" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="I249" s="29" cm="1">
-        <f t="array" ref="I249">SUMPRODUCT(ISNUMBER(SEARCH(H249,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>110</v>
+      </c>
+      <c r="I249" s="29">
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
     <row r="250" spans="1:19">
       <c r="B250" s="18" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C250" s="32">
         <v>6</v>
       </c>
       <c r="H250" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="I250" s="29" cm="1">
-        <f t="array" ref="I250">SUMPRODUCT(ISNUMBER(SEARCH(H250,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>157</v>
+      </c>
+      <c r="I250" s="29">
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
     <row r="251" spans="1:19">
       <c r="B251" s="18" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="C251" s="32">
         <v>3</v>
       </c>
-      <c r="H251" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="I251" s="29" cm="1">
-        <f t="array" ref="I251">SUMPRODUCT(ISNUMBER(SEARCH(H251,$B$247:$B$267))*$C$247:$C$267)</f>
+      <c r="H251" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="I251" s="29">
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
     <row r="252" spans="1:19">
       <c r="B252" s="18" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C252" s="32">
         <v>4</v>
       </c>
       <c r="H252" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="I252" s="29" cm="1">
-        <f t="array" ref="I252">SUMPRODUCT(ISNUMBER(SEARCH(H252,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>158</v>
+      </c>
+      <c r="I252" s="29">
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
     <row r="253" spans="1:19">
       <c r="B253" s="18" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C253" s="32">
         <v>2</v>
       </c>
       <c r="H253" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="I253" s="29" cm="1">
-        <f t="array" ref="I253">SUMPRODUCT(ISNUMBER(SEARCH(H253,$B$247:$B$267))*$C$247:$C$267)</f>
-        <v>6</v>
+        <v>113</v>
+      </c>
+      <c r="I253" s="29">
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
     </row>
     <row r="254" spans="1:19">
       <c r="B254" s="18" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C254" s="32">
         <v>5</v>
       </c>
       <c r="H254" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="I254" s="29" cm="1">
-        <f t="array" ref="I254">SUMPRODUCT(ISNUMBER(SEARCH(H254,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>122</v>
+      </c>
+      <c r="I254" s="29">
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:19">
       <c r="B255" s="18" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C255" s="32">
         <v>8</v>
       </c>
       <c r="H255" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I255" s="29" cm="1">
-        <f t="array" ref="I255">SUMPRODUCT(ISNUMBER(SEARCH(H255,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>107</v>
+      </c>
+      <c r="I255" s="29">
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:19">
       <c r="B256" s="18" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C256" s="32">
         <v>6</v>
       </c>
       <c r="H256" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="I256" s="29" cm="1">
-        <f t="array" ref="I256">SUMPRODUCT(ISNUMBER(SEARCH(H256,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>156</v>
+      </c>
+      <c r="I256" s="29">
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
     <row r="257" spans="2:9">
       <c r="B257" s="18" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C257" s="32">
         <v>3</v>
       </c>
       <c r="H257" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I257" s="29" cm="1">
-        <f t="array" ref="I257">SUMPRODUCT(ISNUMBER(SEARCH(H257,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>137</v>
+      </c>
+      <c r="I257" s="29">
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
     <row r="258" spans="2:9">
       <c r="B258" s="18" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C258" s="32">
         <v>8</v>
       </c>
       <c r="H258" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I258" s="29" cm="1">
-        <f t="array" ref="I258">SUMPRODUCT(ISNUMBER(SEARCH(H258,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>152</v>
+      </c>
+      <c r="I258" s="29">
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
     <row r="259" spans="2:9">
       <c r="B259" s="18" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C259" s="32">
         <v>4</v>
       </c>
       <c r="H259" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I259" s="29" cm="1">
-        <f t="array" ref="I259">SUMPRODUCT(ISNUMBER(SEARCH(H259,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>154</v>
+      </c>
+      <c r="I259" s="29">
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
     <row r="260" spans="2:9">
       <c r="B260" s="18" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C260" s="32">
         <v>6</v>
       </c>
       <c r="H260" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="I260" s="29" cm="1">
-        <f t="array" ref="I260">SUMPRODUCT(ISNUMBER(SEARCH(H260,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>140</v>
+      </c>
+      <c r="I260" s="29">
+        <f>SUM(C260:C261)</f>
         <v>12</v>
       </c>
     </row>
     <row r="261" spans="2:9">
       <c r="B261" s="18" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C261" s="32">
         <v>6</v>
       </c>
       <c r="H261" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="I261" s="29" cm="1">
-        <f t="array" ref="I261">SUMPRODUCT(ISNUMBER(SEARCH(H261,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>153</v>
+      </c>
+      <c r="I261" s="29">
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
     <row r="262" spans="2:9">
       <c r="B262" s="18" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C262" s="32">
         <v>4</v>
       </c>
       <c r="H262" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="I262" s="29" cm="1">
-        <f t="array" ref="I262">SUMPRODUCT(ISNUMBER(SEARCH(H262,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>155</v>
+      </c>
+      <c r="I262" s="29">
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
     <row r="263" spans="2:9">
       <c r="B263" s="18" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C263" s="32">
         <v>4</v>
       </c>
       <c r="H263" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="I263" s="29" cm="1">
-        <f t="array" ref="I263">SUMPRODUCT(ISNUMBER(SEARCH(H263,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>161</v>
+      </c>
+      <c r="I263" s="29">
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
     <row r="264" spans="2:9">
       <c r="B264" s="18" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C264" s="32">
         <v>5</v>
       </c>
       <c r="H264" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="I264" s="29" cm="1">
-        <f t="array" ref="I264">SUMPRODUCT(ISNUMBER(SEARCH(H264,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>103</v>
+      </c>
+      <c r="I264" s="29">
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
     <row r="265" spans="2:9">
       <c r="B265" s="18" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C265" s="32">
         <v>0</v>
       </c>
       <c r="H265" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I265" s="29" cm="1">
-        <f t="array" ref="I265">SUMPRODUCT(ISNUMBER(SEARCH(H265,$B$247:$B$267))*$C$247:$C$267)</f>
+        <v>162</v>
+      </c>
+      <c r="I265" s="29">
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
     <row r="266" spans="2:9">
       <c r="B266" s="18" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C266" s="32">
         <v>7</v>
       </c>
       <c r="H266" s="8" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="I266" s="30">
-        <f>C268</f>
+        <f>SUM(I247:I265)</f>
         <v>99</v>
       </c>
     </row>
     <row r="267" spans="2:9">
       <c r="B267" s="18" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C267" s="32">
         <v>4</v>
@@ -6746,7 +6697,7 @@
     </row>
     <row r="268" spans="2:9">
       <c r="B268" s="33" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C268" s="34">
         <f>SUM(C247:C267)</f>
@@ -6755,7 +6706,7 @@
     </row>
     <row r="269" spans="2:9">
       <c r="B269" s="12" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -6784,177 +6735,177 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
         <v>11</v>
       </c>
       <c r="C1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" t="s">
         <v>59</v>
-      </c>
-      <c r="D1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:B7">_xlfn.UNIQUE(_xlfn.VSTACK('V1. Markets'!B8:B12,'V1. Markets'!B17:B27))</f>
+        <f t="array" ref="B2:B7">_xlfn.UNIQUE(_xlfn.VSTACK('V1. Markets'!B10:B14,'V1. Markets'!B19:B29))</f>
         <v>Miscellaneous Chemical Manufacturing</v>
       </c>
       <c r="C2">
-        <f>SUMIF('V1. Markets'!$B$8:$B$12,'X1. Markets'!B2,'V1. Markets'!$E$8:$E$12)</f>
+        <f>SUMIF('V1. Markets'!$B$10:$B$14,'X1. Markets'!B2,'V1. Markets'!$E$10:$E$14)</f>
         <v>0.58945569929216501</v>
       </c>
       <c r="D2">
-        <f>SUMIF('V1. Markets'!$B$17:$B$27,'X1. Markets'!B2,'V1. Markets'!$E$17:$E$27)</f>
+        <f>SUMIF('V1. Markets'!$B$19:$B$29,'X1. Markets'!B2,'V1. Markets'!$E$19:$E$29)</f>
         <v>0.510906612133606</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B3" t="str">
         <v>Oil and Gas Drilling</v>
       </c>
       <c r="C3">
-        <f>SUMIF('V1. Markets'!$B$8:$B$12,'X1. Markets'!B3,'V1. Markets'!$E$8:$E$12)</f>
+        <f>SUMIF('V1. Markets'!$B$10:$B$14,'X1. Markets'!B3,'V1. Markets'!$E$10:$E$14)</f>
         <v>0.12631193556260678</v>
       </c>
       <c r="D3">
-        <f>SUMIF('V1. Markets'!$B$17:$B$27,'X1. Markets'!B3,'V1. Markets'!$E$17:$E$27)</f>
+        <f>SUMIF('V1. Markets'!$B$19:$B$29,'X1. Markets'!B3,'V1. Markets'!$E$19:$E$29)</f>
         <v>0.28425357873210633</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" t="str">
         <v>Organic Chemical Manufacturing</v>
       </c>
       <c r="C4">
-        <f>SUMIF('V1. Markets'!$B$8:$B$12,'X1. Markets'!B4,'V1. Markets'!$E$8:$E$12)</f>
+        <f>SUMIF('V1. Markets'!$B$10:$B$14,'X1. Markets'!B4,'V1. Markets'!$E$10:$E$14)</f>
         <v>0.10532096656089822</v>
       </c>
       <c r="D4">
-        <f>SUMIF('V1. Markets'!$B$17:$B$27,'X1. Markets'!B4,'V1. Markets'!$E$17:$E$27)</f>
+        <f>SUMIF('V1. Markets'!$B$19:$B$29,'X1. Markets'!B4,'V1. Markets'!$E$19:$E$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B5" t="str">
         <v>Pharmaceutical Manufacturing</v>
       </c>
       <c r="C5">
-        <f>SUMIF('V1. Markets'!$B$8:$B$12,'X1. Markets'!B5,'V1. Markets'!$E$8:$E$12)</f>
+        <f>SUMIF('V1. Markets'!$B$10:$B$14,'X1. Markets'!B5,'V1. Markets'!$E$10:$E$14)</f>
         <v>9.4703441542592137E-2</v>
       </c>
       <c r="D5">
-        <f>SUMIF('V1. Markets'!$B$17:$B$27,'X1. Markets'!B5,'V1. Markets'!$E$17:$E$27)</f>
+        <f>SUMIF('V1. Markets'!$B$19:$B$29,'X1. Markets'!B5,'V1. Markets'!$E$19:$E$29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" t="str">
         <v>Industrial Water Treatment</v>
       </c>
       <c r="C6">
-        <f>SUMIF('V1. Markets'!$B$8:$B$12,'X1. Markets'!B6,'V1. Markets'!$E$8:$E$12)</f>
+        <f>SUMIF('V1. Markets'!$B$10:$B$14,'X1. Markets'!B6,'V1. Markets'!$E$10:$E$14)</f>
         <v>8.4207957041737863E-2</v>
       </c>
       <c r="D6">
-        <f>SUMIF('V1. Markets'!$B$17:$B$27,'X1. Markets'!B6,'V1. Markets'!$E$17:$E$27)</f>
+        <f>SUMIF('V1. Markets'!$B$19:$B$29,'X1. Markets'!B6,'V1. Markets'!$E$19:$E$29)</f>
         <v>5.6009997727789133E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" t="str">
         <v>Other</v>
       </c>
       <c r="C7">
-        <f>SUMIF('V1. Markets'!$B$8:$B$12,'X1. Markets'!B7,'V1. Markets'!$E$8:$E$12)</f>
+        <f>SUMIF('V1. Markets'!$B$10:$B$14,'X1. Markets'!B7,'V1. Markets'!$E$10:$E$14)</f>
         <v>0</v>
       </c>
       <c r="D7">
-        <f>SUMIF('V1. Markets'!$B$17:$B$27,'X1. Markets'!B7,'V1. Markets'!$E$17:$E$27)</f>
+        <f>SUMIF('V1. Markets'!$B$19:$B$29,'X1. Markets'!B7,'V1. Markets'!$E$19:$E$29)</f>
         <v>0.14882981140649851</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B8" t="str" cm="1">
-        <f t="array" ref="B8:B11">_xlfn.UNIQUE(_xlfn.VSTACK('V1. Markets'!B35:B40,'V1. Markets'!B45:B51))</f>
+        <f t="array" ref="B8:B11">_xlfn.UNIQUE(_xlfn.VSTACK('V1. Markets'!B37:B42,'V1. Markets'!B47:B53))</f>
         <v>Organic Chemical Manufacturing</v>
       </c>
       <c r="C8">
-        <f>SUMIF('V1. Markets'!$B$35:$B$40,'X1. Markets'!B8,'V1. Markets'!$E$35:$E$40)</f>
-        <v>0.7433333333333334</v>
+        <f>SUMIF('V1. Markets'!$B$37:$B$42,'X1. Markets'!B8,'V1. Markets'!$E$37:$E$42)</f>
+        <v>0.74</v>
       </c>
       <c r="D8">
-        <f>SUMIF('V1. Markets'!$B$45:$B$51,'X1. Markets'!B8,'V1. Markets'!$E$45:$E$51)</f>
+        <f>SUMIF('V1. Markets'!$B$47:$B$53,'X1. Markets'!B8,'V1. Markets'!$E$47:$E$53)</f>
         <v>0.77758342303552197</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B9" t="str">
         <v>Steel Pickling</v>
       </c>
       <c r="C9">
-        <f>SUMIF('V1. Markets'!$B$35:$B$40,'X1. Markets'!B9,'V1. Markets'!$E$35:$E$40)</f>
-        <v>0.11388888888888889</v>
+        <f>SUMIF('V1. Markets'!$B$37:$B$42,'X1. Markets'!B9,'V1. Markets'!$E$37:$E$42)</f>
+        <v>0.11</v>
       </c>
       <c r="D9">
-        <f>SUMIF('V1. Markets'!$B$45:$B$51,'X1. Markets'!B9,'V1. Markets'!$E$45:$E$51)</f>
+        <f>SUMIF('V1. Markets'!$B$47:$B$53,'X1. Markets'!B9,'V1. Markets'!$E$47:$E$53)</f>
         <v>7.0102260495156082E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B10" t="str">
         <v>Semiconductor Manufacturing</v>
       </c>
       <c r="C10">
-        <f>SUMIF('V1. Markets'!$B$35:$B$40,'X1. Markets'!B10,'V1. Markets'!$E$35:$E$40)</f>
+        <f>SUMIF('V1. Markets'!$B$37:$B$42,'X1. Markets'!B10,'V1. Markets'!$E$37:$E$42)</f>
         <v>0.06</v>
       </c>
       <c r="D10">
-        <f>SUMIF('V1. Markets'!$B$45:$B$51,'X1. Markets'!B10,'V1. Markets'!$E$45:$E$51)</f>
+        <f>SUMIF('V1. Markets'!$B$47:$B$53,'X1. Markets'!B10,'V1. Markets'!$E$47:$E$53)</f>
         <v>5.086114101184068E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" t="str">
         <v>Other</v>
       </c>
       <c r="C11">
-        <f>SUMIF('V1. Markets'!$B$35:$B$40,'X1. Markets'!B11,'V1. Markets'!$E$35:$E$40)</f>
-        <v>8.7222222222222229E-2</v>
+        <f>SUMIF('V1. Markets'!$B$37:$B$42,'X1. Markets'!B11,'V1. Markets'!$E$37:$E$42)</f>
+        <v>0.09</v>
       </c>
       <c r="D11">
-        <f>SUMIF('V1. Markets'!$B$45:$B$51,'X1. Markets'!B11,'V1. Markets'!$E$45:$E$51)</f>
+        <f>SUMIF('V1. Markets'!$B$47:$B$53,'X1. Markets'!B11,'V1. Markets'!$E$47:$E$53)</f>
         <v>0.10145317545748117</v>
       </c>
     </row>
@@ -6974,16 +6925,16 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="str" cm="1">
         <f t="array" ref="A2:A12">_xlfn.UNIQUE('V2. Demand'!B6:B16)</f>
-        <v>B</v>
+        <v>B2O3</v>
       </c>
       <c r="B2">
         <f>_xlfn.XLOOKUP($A2,'V2. Demand'!$B:$B,'V2. Demand'!D:D)</f>
@@ -7129,7 +7080,7 @@
         <v>2.1295163541192035E-2</v>
       </c>
       <c r="E2">
-        <v>2.1295163541192035E-2</v>
+        <v>2.7143440335252313E-2</v>
       </c>
       <c r="F2">
         <v>4.0404040404040407E-2</v>
@@ -7149,7 +7100,7 @@
         <v>4.4032605681508151E-2</v>
       </c>
       <c r="E3">
-        <v>4.4032605681508151E-2</v>
+        <v>4.8238342400586526E-2</v>
       </c>
       <c r="F3">
         <v>7.0707070707070704E-2</v>
@@ -7169,7 +7120,7 @@
         <v>1.7139801078028306E-2</v>
       </c>
       <c r="E4">
-        <v>1.7139801078028306E-2</v>
+        <v>2.1086570745403193E-2</v>
       </c>
       <c r="F4">
         <v>3.0303030303030304E-2</v>
@@ -7189,7 +7140,7 @@
         <v>4.9296062800893277E-2</v>
       </c>
       <c r="E5">
-        <v>4.9296062800893277E-2</v>
+        <v>4.7313565888243675E-2</v>
       </c>
       <c r="F5">
         <v>6.0606060606060608E-2</v>
@@ -7197,7 +7148,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="str">
-        <v xml:space="preserve">Michigan </v>
+        <v>Michigan</v>
       </c>
       <c r="B6" t="str">
         <v/>
@@ -7209,7 +7160,7 @@
         <v>4.7991301974609671E-2</v>
       </c>
       <c r="E6">
-        <v>4.7991301974609671E-2</v>
+        <v>4.7805113764173658E-2</v>
       </c>
       <c r="F6">
         <v>3.0303030303030304E-2</v>
@@ -7229,7 +7180,7 @@
         <v>4.1990455501326858E-2</v>
       </c>
       <c r="E7">
-        <v>4.1990455501326858E-2</v>
+        <v>3.5699705904406437E-2</v>
       </c>
       <c r="F7">
         <v>4.0404040404040407E-2</v>
@@ -7243,16 +7194,16 @@
         <v/>
       </c>
       <c r="C8">
-        <v>5.7323238099595122E-2</v>
+        <v>3.1772536999336645E-2</v>
       </c>
       <c r="D8">
         <v>3.3605517492133169E-2</v>
       </c>
       <c r="E8">
-        <v>3.3605517492133169E-2</v>
+        <v>2.642694682118488E-2</v>
       </c>
       <c r="F8">
-        <v>6.0606060606060608E-2</v>
+        <v>2.0202020202020204E-2</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7269,7 +7220,7 @@
         <v>0.10300249238021748</v>
       </c>
       <c r="E9">
-        <v>0.10300249238021748</v>
+        <v>9.3535728865524165E-2</v>
       </c>
       <c r="F9">
         <v>5.0505050505050504E-2</v>
@@ -7289,7 +7240,7 @@
         <v>6.336830976222689E-2</v>
       </c>
       <c r="E10">
-        <v>6.336830976222689E-2</v>
+        <v>8.7812112072915713E-2</v>
       </c>
       <c r="F10">
         <v>8.0808080808080815E-2</v>
@@ -7309,7 +7260,7 @@
         <v>6.5548172775919358E-2</v>
       </c>
       <c r="E11">
-        <v>6.5548172775919358E-2</v>
+        <v>6.6067367052962206E-2</v>
       </c>
       <c r="F11">
         <v>6.0606060606060608E-2</v>
@@ -7329,7 +7280,7 @@
         <v>3.4855166176611739E-2</v>
       </c>
       <c r="E12">
-        <v>3.4855166176611739E-2</v>
+        <v>4.7205258729140456E-2</v>
       </c>
       <c r="F12">
         <v>3.0303030303030304E-2</v>
@@ -7349,7 +7300,7 @@
         <v>9.3484702014291016E-2</v>
       </c>
       <c r="E13">
-        <v>9.3484702014291016E-2</v>
+        <v>8.4346282981612772E-2</v>
       </c>
       <c r="F13">
         <v>8.0808080808080815E-2</v>
@@ -7369,7 +7320,7 @@
         <v>3.0991779528145538E-2</v>
       </c>
       <c r="E14">
-        <v>3.0991779528145538E-2</v>
+        <v>3.0117721550625264E-2</v>
       </c>
       <c r="F14">
         <v>4.0404040404040407E-2</v>
@@ -7389,7 +7340,7 @@
         <v>0.13128517928573913</v>
       </c>
       <c r="E15">
-        <v>0.13128517928573913</v>
+        <v>0.13130160211282274</v>
       </c>
       <c r="F15">
         <v>0.12121212121212122</v>
@@ -7409,7 +7360,7 @@
         <v>3.5189335114847446E-2</v>
       </c>
       <c r="E16">
-        <v>3.5189335114847446E-2</v>
+        <v>2.8118204767181264E-2</v>
       </c>
       <c r="F16">
         <v>4.0404040404040407E-2</v>
@@ -7429,7 +7380,7 @@
         <v>3.1911430571807904E-2</v>
       </c>
       <c r="E17">
-        <v>3.1911430571807904E-2</v>
+        <v>3.561639270509627E-2</v>
       </c>
       <c r="F17">
         <v>4.0404040404040407E-2</v>
@@ -7449,7 +7400,7 @@
         <v>3.1325348279702174E-2</v>
       </c>
       <c r="E18">
-        <v>3.1325348279702174E-2</v>
+        <v>2.6668555099184362E-2</v>
       </c>
       <c r="F18">
         <v>5.0505050505050504E-2</v>
@@ -7469,7 +7420,7 @@
         <v>0.10946350198033845</v>
       </c>
       <c r="E19">
-        <v>0.10946350198033845</v>
+        <v>9.4143915220488386E-2</v>
       </c>
       <c r="F19">
         <v>7.0707070707070704E-2</v>
@@ -7489,7 +7440,7 @@
         <v>1.4223674060461395E-2</v>
       </c>
       <c r="E20">
-        <v>1.4223674060461395E-2</v>
+        <v>2.1353172983195726E-2</v>
       </c>
       <c r="F20">
         <v>4.0404040404040407E-2</v>

--- a/data/inputs/sw3_validation.xlsx
+++ b/data/inputs/sw3_validation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carolineadkins/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2D10A4-0E66-004A-9C3A-74BACDB6917A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA10794F-870B-5242-8A25-AB5A38420F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17800" yWindow="-26680" windowWidth="28400" windowHeight="21000" activeTab="6" xr2:uid="{DD733A40-C352-434B-90DD-0C52971768EC}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="286">
   <si>
     <t>Major End-Use Markets</t>
   </si>
@@ -81,9 +81,6 @@
     <t>End-Use</t>
   </si>
   <si>
-    <t>Demand (kt)</t>
-  </si>
-  <si>
     <t>% of Demand</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
   </si>
   <si>
     <t>Other</t>
-  </si>
-  <si>
-    <t>Others</t>
   </si>
   <si>
     <t>end_use_category</t>
@@ -213,69 +207,6 @@
     </r>
   </si>
   <si>
-    <t>Hydrofluoric Acid</t>
-  </si>
-  <si>
-    <r>
-      <t>Assigned Major End-Use Categories (Tier 3)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow (Body)"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <t>Fluorocarbon</t>
-  </si>
-  <si>
-    <t>Fluorinated derivatives</t>
-  </si>
-  <si>
-    <t>Steel Pickling</t>
-  </si>
-  <si>
-    <t>Metal pickling</t>
-  </si>
-  <si>
-    <t>Semiconductor Manufacturing</t>
-  </si>
-  <si>
-    <t>Glass etching</t>
-  </si>
-  <si>
-    <t>Oil refining</t>
-  </si>
-  <si>
-    <t>(1) Source: Grand View Research, Hydrofluoric Acid Market 2022-2030</t>
-  </si>
-  <si>
-    <t>Glass Etching &amp; Cleaning</t>
-  </si>
-  <si>
-    <t>Metal Pickling</t>
-  </si>
-  <si>
-    <t>Oil Refining</t>
-  </si>
-  <si>
-    <t>Production of Fluorinated Derivatives</t>
-  </si>
-  <si>
-    <t>Production of Fluorocarbons</t>
-  </si>
-  <si>
-    <t>Production of Uranium Fuel</t>
-  </si>
-  <si>
-    <t>(1) Source: Markets and Markets, US Hydrofluoric Acid Market (2025-2030)</t>
-  </si>
-  <si>
     <t>byproduct</t>
   </si>
   <si>
@@ -288,9 +219,6 @@
     <t>Br</t>
   </si>
   <si>
-    <t>HF</t>
-  </si>
-  <si>
     <t>Domestic Byproduct Demand</t>
   </si>
   <si>
@@ -331,9 +259,6 @@
   </si>
   <si>
     <t>P2O5</t>
-  </si>
-  <si>
-    <t>Market Reports World, Borates Market Size, Share, Growth, and Industry Analysis, By Type (Borax, Boric Acid, Ulexite), By Application (Glass &amp; Ceramics, Agriculture, Detergents), Regional Insights and Forecast to 2033</t>
   </si>
   <si>
     <t>represents US consumption of bromine when it was last reported in 2006</t>
@@ -1116,24 +1041,13 @@
     <t>% of Revenue</t>
   </si>
   <si>
-    <t>represents US consumption of liquid anhydrous hydrogen fluoride (2024)</t>
-  </si>
-  <si>
     <t>represents P2O5 content of phosphate rock sold or used by producers (2023)</t>
   </si>
   <si>
     <t>Barite Products Market Size, Share, Growth, and Industry Analysis, By Type (Up to Grade 3.9, Grade 4.0, Grade 4.1, Grade 4.2, Grade 4.3, Grade above 4.3), By Application (Drilling Industry (Rig), Medical Industry, Rubber &amp; Plastics, Pulps and Papers, Paints and Coatings, Cosmetic Industry, Others), Regional Insights and Forecast From 2026 To 2035</t>
   </si>
   <si>
-    <t xml:space="preserve">
-Liquid Anhydrous Hydrogen Fluoride Market Report is Segmented by Types (99.99 AHF, 99.90 AHF, 99.70 AHF), Application (Chemical Industry, Mining &amp; Metallurgical, Etching, Pharmaceuticals, Others), and Geography (North America, Europe, Asia-Pacific, South America, and Middle East and Africa).
-Liquid Anhydrous Hydrogen Fluoride Market Report is Segmented by Types (?99.99 AHF, ?99.90 AHF, ?99.70 AHF), Application (Chemical Industry, Mining &amp; Metallurgical, Etching, Pharmaceuticals, Others), and Geography (North America, Europe, Asia-Pacific, South America, and Middle East and Africa).</t>
-  </si>
-  <si>
     <t>External Benchmark Validation</t>
-  </si>
-  <si>
-    <t>represents gross weight borate consumption in North America (2024)</t>
   </si>
   <si>
     <t>HOLCIM (US) INC. DEVIL'S SLIDE PLANT</t>
@@ -1158,9 +1072,6 @@
   </si>
   <si>
     <t>Greenhouse Gas Emissions from Cement Production Facilities in 2023, by District</t>
-  </si>
-  <si>
-    <t>B2O3</t>
   </si>
 </sst>
 </file>
@@ -1411,7 +1322,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1451,7 +1362,6 @@
     </xf>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1507,17 +1417,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1890,353 +1789,353 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" s="39"/>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
+      <c r="A1" s="38"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+      <c r="Z1" s="38"/>
     </row>
     <row r="2" spans="1:26" ht="27">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42" t="s">
-        <v>279</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
+      <c r="A2" s="40"/>
+      <c r="B2" s="41" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
+      <c r="U2" s="40"/>
+      <c r="V2" s="40"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="40"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
     </row>
     <row r="3" spans="1:26" ht="19">
-      <c r="A3" s="41"/>
-      <c r="B3" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="41"/>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="41"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="C3" s="42"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
+      <c r="X3" s="40"/>
+      <c r="Y3" s="40"/>
+      <c r="Z3" s="40"/>
     </row>
     <row r="4" spans="1:26">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="41"/>
-      <c r="Y4" s="41"/>
-      <c r="Z4" s="41"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="40"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40"/>
+      <c r="X4" s="40"/>
+      <c r="Y4" s="40"/>
+      <c r="Z4" s="40"/>
     </row>
     <row r="5" spans="1:26" ht="42" customHeight="1">
-      <c r="A5" s="41"/>
-      <c r="B5" s="67" t="s">
-        <v>281</v>
-      </c>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="41"/>
-      <c r="R5" s="41"/>
-      <c r="S5" s="41"/>
-      <c r="T5" s="41"/>
-      <c r="U5" s="41"/>
-      <c r="V5" s="41"/>
-      <c r="W5" s="41"/>
-      <c r="X5" s="41"/>
-      <c r="Y5" s="41"/>
-      <c r="Z5" s="41"/>
+      <c r="A5" s="40"/>
+      <c r="B5" s="61" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="40"/>
+      <c r="U5" s="40"/>
+      <c r="V5" s="40"/>
+      <c r="W5" s="40"/>
+      <c r="X5" s="40"/>
+      <c r="Y5" s="40"/>
+      <c r="Z5" s="40"/>
     </row>
     <row r="6" spans="1:26">
-      <c r="A6" s="41"/>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="41"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="41"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="41"/>
-      <c r="Z6" s="41"/>
+      <c r="A6" s="40"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="40"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="40"/>
+      <c r="W6" s="40"/>
+      <c r="X6" s="40"/>
+      <c r="Y6" s="40"/>
+      <c r="Z6" s="40"/>
     </row>
     <row r="7" spans="1:26">
-      <c r="A7" s="39"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="39"/>
-      <c r="U7" s="39"/>
-      <c r="V7" s="39"/>
-      <c r="W7" s="39"/>
-      <c r="X7" s="39"/>
-      <c r="Y7" s="39"/>
-      <c r="Z7" s="39"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="38"/>
+      <c r="V7" s="38"/>
+      <c r="W7" s="38"/>
+      <c r="X7" s="38"/>
+      <c r="Y7" s="38"/>
+      <c r="Z7" s="38"/>
     </row>
     <row r="8" spans="1:26">
-      <c r="A8" s="41"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="41"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="41"/>
-      <c r="Q8" s="41"/>
-      <c r="R8" s="41"/>
-      <c r="S8" s="41"/>
-      <c r="T8" s="41"/>
-      <c r="U8" s="41"/>
-      <c r="V8" s="41"/>
-      <c r="W8" s="41"/>
-      <c r="X8" s="41"/>
-      <c r="Y8" s="41"/>
-      <c r="Z8" s="41"/>
+      <c r="A8" s="40"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="40"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="40"/>
+      <c r="U8" s="40"/>
+      <c r="V8" s="40"/>
+      <c r="W8" s="40"/>
+      <c r="X8" s="40"/>
+      <c r="Y8" s="40"/>
+      <c r="Z8" s="40"/>
     </row>
     <row r="9" spans="1:26" ht="27">
-      <c r="A9" s="41"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="41"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="41"/>
-      <c r="Y9" s="41"/>
-      <c r="Z9" s="41"/>
+        <v>254</v>
+      </c>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="40"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="40"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="40"/>
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="40"/>
     </row>
     <row r="10" spans="1:26" ht="17">
-      <c r="A10" s="41"/>
-      <c r="B10" s="46" t="s">
-        <v>278</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>276</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>277</v>
-      </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="41"/>
-      <c r="S10" s="41"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="41"/>
-      <c r="W10" s="41"/>
-      <c r="X10" s="41"/>
-      <c r="Y10" s="41"/>
-      <c r="Z10" s="41"/>
+      <c r="A10" s="40"/>
+      <c r="B10" s="45" t="s">
+        <v>257</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>255</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="40"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="40"/>
+      <c r="S10" s="40"/>
+      <c r="T10" s="40"/>
+      <c r="U10" s="40"/>
+      <c r="V10" s="40"/>
+      <c r="W10" s="40"/>
+      <c r="X10" s="40"/>
+      <c r="Y10" s="40"/>
+      <c r="Z10" s="40"/>
     </row>
     <row r="11" spans="1:26" ht="50" customHeight="1">
-      <c r="B11" s="68" t="s">
-        <v>282</v>
-      </c>
-      <c r="C11" s="55" t="s">
-        <v>283</v>
-      </c>
-      <c r="D11" s="50" t="s">
-        <v>290</v>
+      <c r="B11" s="62" t="s">
+        <v>261</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>262</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="50" customHeight="1">
-      <c r="B12" s="68"/>
-      <c r="C12" s="55" t="s">
-        <v>284</v>
-      </c>
-      <c r="D12" s="50" t="s">
-        <v>291</v>
+      <c r="B12" s="62"/>
+      <c r="C12" s="54" t="s">
+        <v>263</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="50" customHeight="1">
-      <c r="B13" s="68"/>
+      <c r="B13" s="62"/>
       <c r="C13" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="D13" s="50" t="s">
-        <v>292</v>
+        <v>264</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="50" customHeight="1">
-      <c r="B14" s="69" t="s">
-        <v>289</v>
+      <c r="B14" s="63" t="s">
+        <v>268</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="D14" s="50" t="s">
-        <v>293</v>
+        <v>265</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="50" customHeight="1">
-      <c r="B15" s="69"/>
+      <c r="B15" s="63"/>
       <c r="C15" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="D15" s="50" t="s">
-        <v>294</v>
+        <v>266</v>
+      </c>
+      <c r="D15" s="49" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="50" customHeight="1">
-      <c r="B16" s="70"/>
-      <c r="C16" s="56" t="s">
-        <v>288</v>
-      </c>
-      <c r="D16" s="51" t="s">
-        <v>295</v>
+      <c r="B16" s="64"/>
+      <c r="C16" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -2259,7 +2158,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58E59886-CDD6-B745-BD2E-15FB5F2CF4D1}">
-  <dimension ref="A1:Z54"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
@@ -2303,31 +2202,31 @@
     </row>
     <row r="3" spans="1:26" ht="19">
       <c r="B3" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="19">
       <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:26" ht="39" customHeight="1">
-      <c r="B5" s="71" t="s">
-        <v>298</v>
-      </c>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
+      <c r="B5" s="65" t="s">
+        <v>277</v>
+      </c>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
     </row>
     <row r="6" spans="1:26" ht="19">
       <c r="B6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="24">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="19">
       <c r="B8" s="26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:26">
@@ -2338,20 +2237,20 @@
         <v>3</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:26">
       <c r="B10" s="18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="64">
+        <v>15</v>
+      </c>
+      <c r="D10" s="58">
         <v>483000</v>
       </c>
       <c r="E10" s="20">
@@ -2360,12 +2259,12 @@
     </row>
     <row r="11" spans="1:26">
       <c r="B11" s="18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="64">
+        <v>17</v>
+      </c>
+      <c r="D11" s="58">
         <v>103500</v>
       </c>
       <c r="E11" s="20">
@@ -2374,12 +2273,12 @@
     </row>
     <row r="12" spans="1:26">
       <c r="B12" s="18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="64">
+        <v>19</v>
+      </c>
+      <c r="D12" s="58">
         <v>86300</v>
       </c>
       <c r="E12" s="20">
@@ -2388,12 +2287,12 @@
     </row>
     <row r="13" spans="1:26" ht="17">
       <c r="B13" s="21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="64">
+        <v>20</v>
+      </c>
+      <c r="D13" s="58">
         <v>77600</v>
       </c>
       <c r="E13" s="20">
@@ -2402,12 +2301,12 @@
     </row>
     <row r="14" spans="1:26" ht="17">
       <c r="B14" s="23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="65">
+        <v>22</v>
+      </c>
+      <c r="D14" s="59">
         <v>69000</v>
       </c>
       <c r="E14" s="25">
@@ -2416,15 +2315,15 @@
     </row>
     <row r="15" spans="1:26">
       <c r="B15" s="11" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" ht="19">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="19">
       <c r="B17" s="26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
       <c r="B18" s="14" t="s">
         <v>2</v>
       </c>
@@ -2432,18 +2331,18 @@
         <v>3</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
       <c r="B19" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19">
         <v>7.9</v>
@@ -2453,12 +2352,12 @@
         <v>8.9752329016132698E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="2:5">
       <c r="B20" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D20">
         <v>369</v>
@@ -2468,12 +2367,12 @@
         <v>0.41922290388548056</v>
       </c>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" spans="2:5">
       <c r="B21" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D21">
         <v>25.1</v>
@@ -2483,12 +2382,12 @@
         <v>2.851624630765735E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" spans="2:5">
       <c r="B22" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D22">
         <v>33.799999999999997</v>
@@ -2498,12 +2397,12 @@
         <v>3.8400363553737785E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" spans="2:5">
       <c r="B23" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D23">
         <v>250.2</v>
@@ -2513,12 +2412,12 @@
         <v>0.28425357873210633</v>
       </c>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" spans="2:5">
       <c r="B24" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>9</v>
@@ -2528,12 +2427,12 @@
         <v>1.0224948875255623E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" spans="2:5">
       <c r="B25" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D25">
         <v>25.5</v>
@@ -2543,12 +2442,12 @@
         <v>2.8970688479890934E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" spans="2:5">
       <c r="B26" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D26">
         <v>17.2</v>
@@ -2558,12 +2457,12 @@
         <v>1.954101340604408E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" spans="2:5">
       <c r="B27" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D27">
         <v>12.5</v>
@@ -2573,12 +2472,12 @@
         <v>1.4201317882299476E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:26">
+    <row r="28" spans="2:5">
       <c r="B28" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D28">
         <v>80.7</v>
@@ -2588,12 +2487,12 @@
         <v>9.1683708248125426E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" spans="2:5">
       <c r="B29" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D29" s="9">
         <v>49.3</v>
@@ -2603,279 +2502,9 @@
         <v>5.6009997727789133E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:26">
+    <row r="30" spans="2:5">
       <c r="B30" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
-    </row>
-    <row r="34" spans="2:5" ht="24">
-      <c r="B34" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" ht="19">
-      <c r="B35" s="26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5">
-      <c r="B36" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5">
-      <c r="B37" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="D37" s="59" t="s">
-        <v>6</v>
-      </c>
-      <c r="E37" s="60">
-        <v>0.56000000000000005</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5">
-      <c r="B38" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="D38" s="59" t="s">
-        <v>6</v>
-      </c>
-      <c r="E38" s="60">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5">
-      <c r="B39" s="58" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" s="59" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" s="59" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" s="60">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5">
-      <c r="B40" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="59" t="s">
-        <v>47</v>
-      </c>
-      <c r="D40" s="59" t="s">
-        <v>6</v>
-      </c>
-      <c r="E40" s="60">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" ht="17">
-      <c r="B41" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" ht="17">
-      <c r="B42" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="63" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="E42" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5">
-      <c r="B43" s="27" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" ht="19">
-      <c r="B45" s="26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5">
-      <c r="B46" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5">
-      <c r="B47" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C47" t="s">
-        <v>50</v>
-      </c>
-      <c r="D47">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="E47" s="7">
-        <f>D47/SUM($D$47:$D$53)</f>
-        <v>5.086114101184068E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5">
-      <c r="B48" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D48">
-        <v>52.1</v>
-      </c>
-      <c r="E48" s="7">
-        <f t="shared" ref="E48:E53" si="1">D48/SUM($D$47:$D$53)</f>
-        <v>7.0102260495156082E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5">
-      <c r="B49" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C49" t="s">
-        <v>52</v>
-      </c>
-      <c r="D49">
-        <v>33.700000000000003</v>
-      </c>
-      <c r="E49" s="7">
-        <f t="shared" si="1"/>
-        <v>4.5344456404736277E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5">
-      <c r="B50" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" t="s">
-        <v>30</v>
-      </c>
-      <c r="D50">
-        <v>18.7</v>
-      </c>
-      <c r="E50" s="7">
-        <f t="shared" si="1"/>
-        <v>2.5161463939720127E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5">
-      <c r="B51" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C51" t="s">
-        <v>53</v>
-      </c>
-      <c r="D51">
-        <v>140.19999999999999</v>
-      </c>
-      <c r="E51" s="7">
-        <f t="shared" si="1"/>
-        <v>0.18864370290635088</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5">
-      <c r="B52" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52" t="s">
-        <v>54</v>
-      </c>
-      <c r="D52">
-        <v>437.7</v>
-      </c>
-      <c r="E52" s="7">
-        <f t="shared" si="1"/>
-        <v>0.58893972012917106</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5">
-      <c r="B53" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D53" s="9">
-        <v>23</v>
-      </c>
-      <c r="E53" s="10">
-        <f t="shared" si="1"/>
-        <v>3.0947255113024756E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5">
-      <c r="B54" s="11" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2885,8 +2514,6 @@
   <hyperlinks>
     <hyperlink ref="B15" r:id="rId1" display="(1) Source: Ullmann's Encyclopedia for Industrial Chemistry, Bromine" xr:uid="{B3E237F5-6201-7241-BE4E-24DDE6575418}"/>
     <hyperlink ref="B30" r:id="rId2" xr:uid="{31F48FA3-21AE-4844-A943-EB532ED8BC85}"/>
-    <hyperlink ref="B43" r:id="rId3" display="(1) Source: EPA Water Treatment Chemical Supply Chain Profile, Hydrochloric Acid" xr:uid="{D1141142-C843-D047-9C82-4356DA0C904F}"/>
-    <hyperlink ref="B54" r:id="rId4" xr:uid="{35C6CEE8-C097-9948-BBC1-E2956CF4FB20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2894,7 +2521,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58735F91-BAA8-C14F-9F13-EFB6B20863AE}">
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
@@ -2910,8 +2537,8 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -2934,234 +2561,198 @@
     </row>
     <row r="2" spans="1:25" ht="27">
       <c r="B2" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="19">
       <c r="B3" s="4" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="19">
       <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:25" ht="17">
-      <c r="B5" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="53" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="54" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="34">
+      <c r="B5" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="68">
       <c r="B6" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
-        <v>580</v>
+        <v>2000</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="68">
+        <v>71</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="34">
       <c r="B7" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7">
-        <v>2000</v>
+        <v>275</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>302</v>
+        <v>56</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="34">
       <c r="B8" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>275</v>
+        <v>2470</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>78</v>
+        <v>59</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="34">
       <c r="B9" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>2470</v>
+        <v>1458</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>79</v>
+        <v>60</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="34">
       <c r="B10" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10">
-        <v>1458</v>
+        <v>3.75</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="119">
+        <v>62</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="34">
       <c r="B11" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11">
-        <v>320</v>
+        <v>190</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>303</v>
+        <v>64</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="34">
       <c r="B12" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12">
-        <v>3.75</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>84</v>
+        <v>66</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="34">
       <c r="B13" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13">
-        <v>190</v>
+        <v>6000</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>86</v>
+        <v>67</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="34">
       <c r="B14" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>72.900000000000006</v>
+        <v>5700</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="34">
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15">
-        <v>6000</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="34">
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>5700</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>90</v>
+        <v>279</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F6" r:id="rId1" xr:uid="{E0A61302-E760-3F42-9070-A7C6289A59F8}"/>
-    <hyperlink ref="F7" r:id="rId2" display="Market Reports World, Barite Products Market Size, Share, Growth, and Industry Analysis, By Type (Up to Grade 3.9, Grade 4.0, Grade 4.1, Grade 4.2, Grade 4.3, Grade above 4.3), By Application (Drilling Industry (Rig), Medical Industry, Rubber &amp; Plastics, " xr:uid="{B657757A-F86C-5E4E-B760-9142C52901E0}"/>
-    <hyperlink ref="F8" r:id="rId3" xr:uid="{8E42E622-5EC4-3242-99B7-032940B684AD}"/>
-    <hyperlink ref="F9" r:id="rId4" xr:uid="{75D43406-2C82-AD49-BEEE-61E46F610A2B}"/>
-    <hyperlink ref="F10" r:id="rId5" xr:uid="{A365FA2F-6174-6D47-A0C3-8946FE61D0E4}"/>
-    <hyperlink ref="F12" r:id="rId6" xr:uid="{10A9827D-262C-4E43-A982-BA50AD78A15B}"/>
-    <hyperlink ref="F13" r:id="rId7" xr:uid="{98C4BBC5-E91F-C544-8FEC-CDDF72115AC3}"/>
-    <hyperlink ref="F14" r:id="rId8" xr:uid="{BB7B0332-8F56-6B47-82A2-75A844B4E0CF}"/>
-    <hyperlink ref="F15" r:id="rId9" xr:uid="{7E11D623-5E2F-D64E-ACCC-B095B776AF85}"/>
-    <hyperlink ref="F16" r:id="rId10" xr:uid="{46572126-4DF4-4A45-8D05-07D875C33994}"/>
-    <hyperlink ref="F11" r:id="rId11" display="https://www.marketgrowthreports.com/market-reports/liquid-anhydrous-hydrogen-fluoride-market-108451" xr:uid="{96F79528-E4FF-094A-8616-51A031ACBA0C}"/>
+    <hyperlink ref="F6" r:id="rId1" display="Market Reports World, Barite Products Market Size, Share, Growth, and Industry Analysis, By Type (Up to Grade 3.9, Grade 4.0, Grade 4.1, Grade 4.2, Grade 4.3, Grade above 4.3), By Application (Drilling Industry (Rig), Medical Industry, Rubber &amp; Plastics, " xr:uid="{B657757A-F86C-5E4E-B760-9142C52901E0}"/>
+    <hyperlink ref="F7" r:id="rId2" xr:uid="{8E42E622-5EC4-3242-99B7-032940B684AD}"/>
+    <hyperlink ref="F8" r:id="rId3" xr:uid="{75D43406-2C82-AD49-BEEE-61E46F610A2B}"/>
+    <hyperlink ref="F9" r:id="rId4" xr:uid="{A365FA2F-6174-6D47-A0C3-8946FE61D0E4}"/>
+    <hyperlink ref="F10" r:id="rId5" xr:uid="{10A9827D-262C-4E43-A982-BA50AD78A15B}"/>
+    <hyperlink ref="F11" r:id="rId6" xr:uid="{98C4BBC5-E91F-C544-8FEC-CDDF72115AC3}"/>
+    <hyperlink ref="F12" r:id="rId7" xr:uid="{BB7B0332-8F56-6B47-82A2-75A844B4E0CF}"/>
+    <hyperlink ref="F13" r:id="rId8" xr:uid="{7E11D623-5E2F-D64E-ACCC-B095B776AF85}"/>
+    <hyperlink ref="F14" r:id="rId9" xr:uid="{46572126-4DF4-4A45-8D05-07D875C33994}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3202,7 +2793,7 @@
     </row>
     <row r="2" spans="1:19" ht="27">
       <c r="B2" s="2" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="19">
@@ -3214,60 +2805,60 @@
       <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:19" ht="37" customHeight="1">
-      <c r="B5" s="72" t="s">
-        <v>167</v>
-      </c>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
+      <c r="B5" s="66" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:19">
       <c r="B6" s="17"/>
     </row>
     <row r="7" spans="1:19" ht="19">
       <c r="B7" s="26" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:19">
-      <c r="B8" s="35" t="s">
-        <v>97</v>
+      <c r="B8" s="34" t="s">
+        <v>76</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D8" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>14</v>
-      </c>
       <c r="G8" s="16" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="B9" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C9" s="36">
+        <v>138</v>
+      </c>
+      <c r="C9" s="35">
         <f t="shared" ref="C9:C27" si="0">IF(ISERROR(_xlfn.XLOOKUP(B9,$H$36:$H$54,$J$36:$J$54)/$J$55), "", (_xlfn.XLOOKUP(B9,$H$36:$H$54,$J$36:$J$54)/$J$55))</f>
         <v>2.3127272727272729E-2</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="35">
         <f>_xlfn.XLOOKUP(B9,$H$92:$H$110,$I$92:$I$110)/$I$111</f>
         <v>2.2233913580529313E-2</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="35">
         <f>_xlfn.XLOOKUP(B9,$H$121:$H$139,$I$121:$I$139)/$I$140</f>
         <v>2.1295163541192035E-2</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="35">
         <f>_xlfn.XLOOKUP(B9,$H$218:$H$237,$I$218:$I$237)/$I$237</f>
         <v>2.7143440335252313E-2</v>
       </c>
@@ -3278,21 +2869,21 @@
     </row>
     <row r="10" spans="1:19">
       <c r="B10" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C10" s="36">
+        <v>114</v>
+      </c>
+      <c r="C10" s="35">
         <f t="shared" si="0"/>
         <v>4.7181818181818179E-2</v>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="35">
         <f t="shared" ref="D10:D27" si="1">_xlfn.XLOOKUP(B10,$H$92:$H$110,$I$92:$I$110)/$I$111</f>
         <v>3.9458334286433194E-2</v>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="35">
         <f t="shared" ref="E10:E27" si="2">_xlfn.XLOOKUP(B10,$H$121:$H$139,$I$121:$I$139)/$I$140</f>
         <v>4.4032605681508151E-2</v>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="35">
         <f t="shared" ref="F10:F27" si="3">_xlfn.XLOOKUP(B10,$H$218:$H$237,$I$218:$I$237)/$I$237</f>
         <v>4.8238342400586526E-2</v>
       </c>
@@ -3303,21 +2894,21 @@
     </row>
     <row r="11" spans="1:19">
       <c r="B11" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C11" s="36" t="str">
+        <v>89</v>
+      </c>
+      <c r="C11" s="35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="35">
         <f t="shared" si="1"/>
         <v>1.52000365990347E-2</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="35">
         <f t="shared" si="2"/>
         <v>1.7139801078028306E-2</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="35">
         <f t="shared" si="3"/>
         <v>2.1086570745403193E-2</v>
       </c>
@@ -3328,21 +2919,21 @@
     </row>
     <row r="12" spans="1:19">
       <c r="B12" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C12" s="36">
+        <v>136</v>
+      </c>
+      <c r="C12" s="35">
         <f t="shared" si="0"/>
         <v>4.236363636363636E-2</v>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="35">
         <f t="shared" si="1"/>
         <v>4.3941716037239516E-2</v>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="35">
         <f t="shared" si="2"/>
         <v>4.9296062800893277E-2</v>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="35">
         <f t="shared" si="3"/>
         <v>4.7313565888243675E-2</v>
       </c>
@@ -3353,21 +2944,21 @@
     </row>
     <row r="13" spans="1:19">
       <c r="B13" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C13" s="36" t="str">
+        <v>98</v>
+      </c>
+      <c r="C13" s="35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="35">
         <f t="shared" si="1"/>
         <v>5.4646933687124005E-2</v>
       </c>
-      <c r="E13" s="36">
+      <c r="E13" s="35">
         <f t="shared" si="2"/>
         <v>4.7991301974609671E-2</v>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="35">
         <f t="shared" si="3"/>
         <v>4.7805113764173658E-2</v>
       </c>
@@ -3378,21 +2969,21 @@
     </row>
     <row r="14" spans="1:19">
       <c r="B14" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C14" s="36" t="str">
+        <v>137</v>
+      </c>
+      <c r="C14" s="35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="35">
         <f t="shared" si="1"/>
         <v>4.1036667657890526E-2</v>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="35">
         <f t="shared" si="2"/>
         <v>4.1990455501326858E-2</v>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="35">
         <f t="shared" si="3"/>
         <v>3.5699705904406437E-2</v>
       </c>
@@ -3403,21 +2994,21 @@
     </row>
     <row r="15" spans="1:19">
       <c r="B15" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" s="36" t="str">
+        <v>92</v>
+      </c>
+      <c r="C15" s="35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="35">
         <f t="shared" si="1"/>
         <v>3.1772536999336645E-2</v>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="35">
         <f t="shared" si="2"/>
         <v>3.3605517492133169E-2</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="35">
         <f t="shared" si="3"/>
         <v>2.642694682118488E-2</v>
       </c>
@@ -3428,21 +3019,21 @@
     </row>
     <row r="16" spans="1:19">
       <c r="B16" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="36">
+        <v>101</v>
+      </c>
+      <c r="C16" s="35">
         <f t="shared" si="0"/>
         <v>0.10818181818181818</v>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="35">
         <f t="shared" si="1"/>
         <v>0.11277077567079169</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="35">
         <f t="shared" si="2"/>
         <v>0.10300249238021748</v>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="35">
         <f t="shared" si="3"/>
         <v>9.3535728865524165E-2</v>
       </c>
@@ -3453,21 +3044,21 @@
     </row>
     <row r="17" spans="1:19">
       <c r="B17" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" s="36">
+        <v>86</v>
+      </c>
+      <c r="C17" s="35">
         <f t="shared" si="0"/>
         <v>4.8818181818181816E-2</v>
       </c>
-      <c r="D17" s="36">
+      <c r="D17" s="35">
         <f t="shared" si="1"/>
         <v>7.2866390648946636E-2</v>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="35">
         <f t="shared" si="2"/>
         <v>6.336830976222689E-2</v>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="35">
         <f t="shared" si="3"/>
         <v>8.7812112072915713E-2</v>
       </c>
@@ -3478,21 +3069,21 @@
     </row>
     <row r="18" spans="1:19">
       <c r="B18" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C18" s="36" t="str">
+        <v>135</v>
+      </c>
+      <c r="C18" s="35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="35">
         <f t="shared" si="1"/>
         <v>6.862319006336208E-2</v>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="35">
         <f t="shared" si="2"/>
         <v>6.5548172775919358E-2</v>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="35">
         <f t="shared" si="3"/>
         <v>6.6067367052962206E-2</v>
       </c>
@@ -3503,21 +3094,21 @@
     </row>
     <row r="19" spans="1:19">
       <c r="B19" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C19" s="36">
+        <v>116</v>
+      </c>
+      <c r="C19" s="35">
         <f t="shared" si="0"/>
         <v>1.8727272727272728E-2</v>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="35">
         <f t="shared" si="1"/>
         <v>3.3522428345952378E-2</v>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="35">
         <f t="shared" si="2"/>
         <v>3.4855166176611739E-2</v>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="35">
         <f t="shared" si="3"/>
         <v>4.7205258729140456E-2</v>
       </c>
@@ -3528,21 +3119,21 @@
     </row>
     <row r="20" spans="1:19">
       <c r="B20" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C20" s="36" t="str">
+        <v>131</v>
+      </c>
+      <c r="C20" s="35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="35">
         <f t="shared" si="1"/>
         <v>9.0273806528352818E-2</v>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="35">
         <f t="shared" si="2"/>
         <v>9.3484702014291016E-2</v>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="35">
         <f t="shared" si="3"/>
         <v>8.4346282981612772E-2</v>
       </c>
@@ -3553,21 +3144,21 @@
     </row>
     <row r="21" spans="1:19">
       <c r="B21" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C21" s="36" t="str">
+        <v>133</v>
+      </c>
+      <c r="C21" s="35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="35">
         <f t="shared" si="1"/>
         <v>2.5550701100258481E-2</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="35">
         <f t="shared" si="2"/>
         <v>3.0991779528145538E-2</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="35">
         <f t="shared" si="3"/>
         <v>3.0117721550625264E-2</v>
       </c>
@@ -3578,21 +3169,21 @@
     </row>
     <row r="22" spans="1:19">
       <c r="B22" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C22" s="36">
+        <v>119</v>
+      </c>
+      <c r="C22" s="35">
         <f t="shared" si="0"/>
         <v>0.18454545454545454</v>
       </c>
-      <c r="D22" s="36">
+      <c r="D22" s="35">
         <f t="shared" si="1"/>
         <v>0.1342727085573118</v>
       </c>
-      <c r="E22" s="36">
+      <c r="E22" s="35">
         <f t="shared" si="2"/>
         <v>0.13128517928573913</v>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="35">
         <f t="shared" si="3"/>
         <v>0.13130160211282274</v>
       </c>
@@ -3603,21 +3194,21 @@
     </row>
     <row r="23" spans="1:19">
       <c r="B23" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C23" s="36" t="str">
+        <v>132</v>
+      </c>
+      <c r="C23" s="35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D23" s="36">
+      <c r="D23" s="35">
         <f t="shared" si="1"/>
         <v>3.4734771370405107E-2</v>
       </c>
-      <c r="E23" s="36">
+      <c r="E23" s="35">
         <f t="shared" si="2"/>
         <v>3.5189335114847446E-2</v>
       </c>
-      <c r="F23" s="36">
+      <c r="F23" s="35">
         <f t="shared" si="3"/>
         <v>2.8118204767181264E-2</v>
       </c>
@@ -3628,21 +3219,21 @@
     </row>
     <row r="24" spans="1:19">
       <c r="B24" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C24" s="36" t="str">
+        <v>134</v>
+      </c>
+      <c r="C24" s="35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D24" s="36">
+      <c r="D24" s="35">
         <f t="shared" si="1"/>
         <v>3.2149964544685133E-2</v>
       </c>
-      <c r="E24" s="36">
+      <c r="E24" s="35">
         <f t="shared" si="2"/>
         <v>3.1911430571807904E-2</v>
       </c>
-      <c r="F24" s="36">
+      <c r="F24" s="35">
         <f t="shared" si="3"/>
         <v>3.561639270509627E-2</v>
       </c>
@@ -3653,21 +3244,21 @@
     </row>
     <row r="25" spans="1:19">
       <c r="B25" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C25" s="36" t="str">
+        <v>140</v>
+      </c>
+      <c r="C25" s="35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D25" s="36">
+      <c r="D25" s="35">
         <f t="shared" si="1"/>
         <v>2.8021135942539514E-2</v>
       </c>
-      <c r="E25" s="36">
+      <c r="E25" s="35">
         <f t="shared" si="2"/>
         <v>3.1325348279702174E-2</v>
       </c>
-      <c r="F25" s="36">
+      <c r="F25" s="35">
         <f t="shared" si="3"/>
         <v>2.6668555099184362E-2</v>
       </c>
@@ -3678,21 +3269,21 @@
     </row>
     <row r="26" spans="1:19">
       <c r="B26" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C26" s="36">
+        <v>82</v>
+      </c>
+      <c r="C26" s="35">
         <f t="shared" si="0"/>
         <v>0.11181818181818182</v>
       </c>
-      <c r="D26" s="36">
+      <c r="D26" s="35">
         <f t="shared" si="1"/>
         <v>0.10224855319440949</v>
       </c>
-      <c r="E26" s="36">
+      <c r="E26" s="35">
         <f t="shared" si="2"/>
         <v>0.10946350198033845</v>
       </c>
-      <c r="F26" s="36">
+      <c r="F26" s="35">
         <f t="shared" si="3"/>
         <v>9.4143915220488386E-2</v>
       </c>
@@ -3703,21 +3294,21 @@
     </row>
     <row r="27" spans="1:19">
       <c r="B27" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="C27" s="37" t="str">
+        <v>141</v>
+      </c>
+      <c r="C27" s="36" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D27" s="37">
+      <c r="D27" s="36">
         <f t="shared" si="1"/>
         <v>1.6675435185396985E-2</v>
       </c>
-      <c r="E27" s="37">
+      <c r="E27" s="36">
         <f t="shared" si="2"/>
         <v>1.4223674060461395E-2</v>
       </c>
-      <c r="F27" s="37">
+      <c r="F27" s="36">
         <f t="shared" si="3"/>
         <v>2.1353172983195726E-2</v>
       </c>
@@ -3728,17 +3319,17 @@
     </row>
     <row r="28" spans="1:19">
       <c r="B28" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:19">
       <c r="B29" t="s">
-        <v>266</v>
-      </c>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
+        <v>245</v>
+      </c>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
     </row>
     <row r="31" spans="1:19">
       <c r="A31" s="1"/>
@@ -3763,651 +3354,651 @@
     </row>
     <row r="33" spans="2:10" ht="24">
       <c r="B33" s="3" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="2:10" ht="19">
       <c r="B34" s="26" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="2:10" ht="19">
       <c r="B35" s="14" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="H35" s="14" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="J35" s="16" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="2:10">
       <c r="B36" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C36" s="29">
+        <v>79</v>
+      </c>
+      <c r="C36" s="28">
         <v>4660</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="I36" t="b" cm="1">
         <f t="array" ref="I36">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H36," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>1</v>
       </c>
-      <c r="J36" s="29" cm="1">
+      <c r="J36" s="28" cm="1">
         <f t="array" ref="J36">IF(I36,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H36," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v>2544</v>
       </c>
     </row>
     <row r="37" spans="2:10">
       <c r="B37" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" s="29" t="s">
-        <v>149</v>
+        <v>80</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>128</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="I37" t="b" cm="1">
         <f t="array" ref="I37">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H37," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>1</v>
       </c>
-      <c r="J37" s="29" cm="1">
+      <c r="J37" s="28" cm="1">
         <f t="array" ref="J37">IF(I37,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H37," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v>5190</v>
       </c>
     </row>
     <row r="38" spans="2:10">
       <c r="B38" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C38" s="29" t="s">
-        <v>149</v>
+        <v>81</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>128</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="I38" t="b" cm="1">
         <f t="array" ref="I38">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H38," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>0</v>
       </c>
-      <c r="J38" s="29" t="str" cm="1">
+      <c r="J38" s="28" t="str" cm="1">
         <f t="array" ref="J38">IF(I38,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H38," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v/>
       </c>
     </row>
     <row r="39" spans="2:10">
       <c r="B39" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C39" s="29">
+        <v>82</v>
+      </c>
+      <c r="C39" s="28">
         <v>12300</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="I39" t="b" cm="1">
         <f t="array" ref="I39">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H39," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>1</v>
       </c>
-      <c r="J39" s="29" cm="1">
+      <c r="J39" s="28" cm="1">
         <f t="array" ref="J39">IF(I39,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H39," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v>4660</v>
       </c>
     </row>
     <row r="40" spans="2:10">
       <c r="B40" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C40" s="29">
+        <v>83</v>
+      </c>
+      <c r="C40" s="28">
         <v>3140</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="I40" t="b" cm="1">
         <f t="array" ref="I40">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H40," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>0</v>
       </c>
-      <c r="J40" s="29" t="str" cm="1">
+      <c r="J40" s="28" t="str" cm="1">
         <f t="array" ref="J40">IF(I40,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H40," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v/>
       </c>
     </row>
     <row r="41" spans="2:10">
       <c r="B41" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C41" s="29">
+        <v>84</v>
+      </c>
+      <c r="C41" s="28">
         <v>0</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="I41" t="b" cm="1">
         <f t="array" ref="I41">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H41," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>0</v>
       </c>
-      <c r="J41" s="29" t="str" cm="1">
+      <c r="J41" s="28" t="str" cm="1">
         <f t="array" ref="J41">IF(I41,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H41," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" spans="2:10">
       <c r="B42" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C42" s="29">
+        <v>85</v>
+      </c>
+      <c r="C42" s="28">
         <v>0</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="I42" t="b" cm="1">
         <f t="array" ref="I42">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H42," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>0</v>
       </c>
-      <c r="J42" s="29" t="str" cm="1">
+      <c r="J42" s="28" t="str" cm="1">
         <f t="array" ref="J42">IF(I42,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H42," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" spans="2:10">
       <c r="B43" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C43" s="29">
+        <v>86</v>
+      </c>
+      <c r="C43" s="28">
         <v>5370</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="I43" t="b" cm="1">
         <f t="array" ref="I43">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H43," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>1</v>
       </c>
-      <c r="J43" s="29" cm="1">
+      <c r="J43" s="28" cm="1">
         <f t="array" ref="J43">IF(I43,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H43," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v>11900</v>
       </c>
     </row>
     <row r="44" spans="2:10">
       <c r="B44" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C44" s="29">
+        <v>87</v>
+      </c>
+      <c r="C44" s="28">
         <v>530</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="I44" t="b" cm="1">
         <f t="array" ref="I44">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H44," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>1</v>
       </c>
-      <c r="J44" s="29" cm="1">
+      <c r="J44" s="28" cm="1">
         <f t="array" ref="J44">IF(I44,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H44," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v>5370</v>
       </c>
     </row>
     <row r="45" spans="2:10">
       <c r="B45" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C45" s="29">
+        <v>88</v>
+      </c>
+      <c r="C45" s="28">
         <v>0</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="I45" t="b" cm="1">
         <f t="array" ref="I45">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H45," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>0</v>
       </c>
-      <c r="J45" s="29" t="str" cm="1">
+      <c r="J45" s="28" t="str" cm="1">
         <f t="array" ref="J45">IF(I45,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H45," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" spans="2:10">
       <c r="B46" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C46" s="29" t="s">
-        <v>149</v>
+        <v>89</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>128</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="I46" t="b" cm="1">
         <f t="array" ref="I46">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H46," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>1</v>
       </c>
-      <c r="J46" s="29" cm="1">
+      <c r="J46" s="28" cm="1">
         <f t="array" ref="J46">IF(I46,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H46," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v>2060</v>
       </c>
     </row>
     <row r="47" spans="2:10">
       <c r="B47" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C47" s="29">
+        <v>90</v>
+      </c>
+      <c r="C47" s="28">
         <v>3520</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="I47" t="b" cm="1">
         <f t="array" ref="I47">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H47," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>0</v>
       </c>
-      <c r="J47" s="29" t="str" cm="1">
+      <c r="J47" s="28" t="str" cm="1">
         <f t="array" ref="J47">IF(I47,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H47," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48" spans="2:10">
       <c r="B48" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C48" s="29">
+        <v>91</v>
+      </c>
+      <c r="C48" s="28">
         <v>2150</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="I48" t="b" cm="1">
         <f t="array" ref="I48">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H48," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>0</v>
       </c>
-      <c r="J48" s="29" t="str" cm="1">
+      <c r="J48" s="28" t="str" cm="1">
         <f t="array" ref="J48">IF(I48,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H48," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v/>
       </c>
     </row>
     <row r="49" spans="2:10">
       <c r="B49" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C49" s="29" t="s">
-        <v>149</v>
+        <v>92</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>128</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="I49" t="b" cm="1">
         <f t="array" ref="I49">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H49," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>1</v>
       </c>
-      <c r="J49" s="29" cm="1">
+      <c r="J49" s="28" cm="1">
         <f t="array" ref="J49">IF(I49,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H49," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v>20300</v>
       </c>
     </row>
     <row r="50" spans="2:10">
       <c r="B50" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C50" s="29">
+        <v>93</v>
+      </c>
+      <c r="C50" s="28">
         <v>1770</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="I50" t="b" cm="1">
         <f t="array" ref="I50">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H50," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>0</v>
       </c>
-      <c r="J50" s="29" t="str" cm="1">
+      <c r="J50" s="28" t="str" cm="1">
         <f t="array" ref="J50">IF(I50,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H50," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v/>
       </c>
     </row>
     <row r="51" spans="2:10">
       <c r="B51" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C51" s="29">
+        <v>94</v>
+      </c>
+      <c r="C51" s="28">
         <v>0</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="I51" t="b" cm="1">
         <f t="array" ref="I51">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H51," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>0</v>
       </c>
-      <c r="J51" s="29" t="str" cm="1">
+      <c r="J51" s="28" t="str" cm="1">
         <f t="array" ref="J51">IF(I51,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H51," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v/>
       </c>
     </row>
     <row r="52" spans="2:10">
       <c r="B52" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C52" s="29">
+        <v>95</v>
+      </c>
+      <c r="C52" s="28">
         <v>394</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="I52" t="b" cm="1">
         <f t="array" ref="I52">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H52," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>0</v>
       </c>
-      <c r="J52" s="29" t="str" cm="1">
+      <c r="J52" s="28" t="str" cm="1">
         <f t="array" ref="J52">IF(I52,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H52," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v/>
       </c>
     </row>
     <row r="53" spans="2:10">
       <c r="B53" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C53" s="29">
+        <v>96</v>
+      </c>
+      <c r="C53" s="28">
         <v>3660</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="I53" t="b" cm="1">
         <f t="array" ref="I53">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H53," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>1</v>
       </c>
-      <c r="J53" s="29" cm="1">
+      <c r="J53" s="28" cm="1">
         <f t="array" ref="J53">IF(I53,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H53," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v>12300</v>
       </c>
     </row>
     <row r="54" spans="2:10">
       <c r="B54" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C54" s="29">
+        <v>97</v>
+      </c>
+      <c r="C54" s="28">
         <v>0</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="I54" t="b" cm="1">
         <f t="array" ref="I54">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H54," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
         <v>0</v>
       </c>
-      <c r="J54" s="29" t="str" cm="1">
+      <c r="J54" s="28" t="str" cm="1">
         <f t="array" ref="J54">IF(I54,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H54," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
         <v/>
       </c>
     </row>
     <row r="55" spans="2:10">
       <c r="B55" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C55" s="29" t="s">
-        <v>149</v>
+        <v>98</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>128</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="I55" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="J55" s="30">
+        <v>127</v>
+      </c>
+      <c r="I55" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="J55" s="29">
         <f>C84</f>
         <v>110000</v>
       </c>
     </row>
     <row r="56" spans="2:10">
       <c r="B56" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C56" s="29">
+        <v>99</v>
+      </c>
+      <c r="C56" s="28">
         <v>0</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
     </row>
     <row r="57" spans="2:10">
       <c r="B57" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C57" s="29">
+        <v>100</v>
+      </c>
+      <c r="C57" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="2:10">
       <c r="B58" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C58" s="29">
+        <v>101</v>
+      </c>
+      <c r="C58" s="28">
         <v>11900</v>
       </c>
     </row>
     <row r="59" spans="2:10">
       <c r="B59" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C59" s="29">
+        <v>102</v>
+      </c>
+      <c r="C59" s="28">
         <v>718</v>
       </c>
     </row>
     <row r="60" spans="2:10">
       <c r="B60" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C60" s="29" t="s">
-        <v>149</v>
+        <v>103</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="61" spans="2:10">
       <c r="B61" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C61" s="29">
+        <v>104</v>
+      </c>
+      <c r="C61" s="28">
         <v>599</v>
       </c>
     </row>
     <row r="62" spans="2:10">
       <c r="B62" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C62" s="29">
+        <v>105</v>
+      </c>
+      <c r="C62" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="2:10">
       <c r="B63" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C63" s="29">
+        <v>106</v>
+      </c>
+      <c r="C63" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="2:10">
       <c r="B64" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C64" s="29">
+        <v>107</v>
+      </c>
+      <c r="C64" s="28">
         <v>514</v>
       </c>
     </row>
     <row r="65" spans="2:3">
       <c r="B65" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C65" s="29">
+        <v>108</v>
+      </c>
+      <c r="C65" s="28">
         <v>2150</v>
       </c>
     </row>
     <row r="66" spans="2:3">
       <c r="B66" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C66" s="29">
+        <v>109</v>
+      </c>
+      <c r="C66" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="2:3">
       <c r="B67" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C67" s="29">
+        <v>110</v>
+      </c>
+      <c r="C67" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="2:3">
       <c r="B68" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C68" s="29">
+        <v>111</v>
+      </c>
+      <c r="C68" s="28">
         <v>1140</v>
       </c>
     </row>
     <row r="69" spans="2:3">
       <c r="B69" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C69" s="29">
+        <v>112</v>
+      </c>
+      <c r="C69" s="28">
         <v>1890</v>
       </c>
     </row>
     <row r="70" spans="2:3">
       <c r="B70" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C70" s="29" t="s">
-        <v>149</v>
+        <v>113</v>
+      </c>
+      <c r="C70" s="28" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="71" spans="2:3">
       <c r="B71" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C71" s="29">
+        <v>114</v>
+      </c>
+      <c r="C71" s="28">
         <v>5190</v>
       </c>
     </row>
     <row r="72" spans="2:3">
       <c r="B72" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C72" s="29">
+        <v>115</v>
+      </c>
+      <c r="C72" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="2:3">
       <c r="B73" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C73" s="29">
+        <v>116</v>
+      </c>
+      <c r="C73" s="28">
         <v>2060</v>
       </c>
     </row>
     <row r="74" spans="2:3">
       <c r="B74" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C74" s="29" t="s">
-        <v>149</v>
+        <v>117</v>
+      </c>
+      <c r="C74" s="28" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="75" spans="2:3">
       <c r="B75" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C75" s="29" t="s">
-        <v>149</v>
+        <v>118</v>
+      </c>
+      <c r="C75" s="28" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="76" spans="2:3">
       <c r="B76" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C76" s="29">
+        <v>119</v>
+      </c>
+      <c r="C76" s="28">
         <v>20300</v>
       </c>
     </row>
     <row r="77" spans="2:3">
       <c r="B77" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C77" s="29" t="s">
-        <v>149</v>
+        <v>120</v>
+      </c>
+      <c r="C77" s="28" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="78" spans="2:3">
       <c r="B78" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C78" s="29">
+        <v>121</v>
+      </c>
+      <c r="C78" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="2:3">
       <c r="B79" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C79" s="29">
+        <v>122</v>
+      </c>
+      <c r="C79" s="28">
         <v>1460</v>
       </c>
     </row>
     <row r="80" spans="2:3">
       <c r="B80" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C80" s="29">
+        <v>123</v>
+      </c>
+      <c r="C80" s="28">
         <v>637</v>
       </c>
     </row>
     <row r="81" spans="1:19">
       <c r="B81" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C81" s="29" t="s">
-        <v>149</v>
+        <v>124</v>
+      </c>
+      <c r="C81" s="28" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="82" spans="1:19">
       <c r="B82" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C82" s="29">
+        <v>125</v>
+      </c>
+      <c r="C82" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:19">
       <c r="B83" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C83" s="29" t="s">
-        <v>149</v>
+        <v>126</v>
+      </c>
+      <c r="C83" s="28" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="84" spans="1:19">
       <c r="B84" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C84" s="38">
+        <v>127</v>
+      </c>
+      <c r="C84" s="37">
         <v>110000</v>
       </c>
     </row>
     <row r="85" spans="1:19">
       <c r="B85" s="12" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
     </row>
     <row r="87" spans="1:19">
@@ -4433,351 +4024,351 @@
     </row>
     <row r="89" spans="1:19" ht="24">
       <c r="B89" s="3" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
     </row>
     <row r="90" spans="1:19" ht="19">
       <c r="B90" s="26" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="H90" s="26" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
     </row>
     <row r="91" spans="1:19">
       <c r="B91" s="14" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="C91" s="16" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="H91" s="14" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="I91" s="16" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
     </row>
     <row r="92" spans="1:19">
       <c r="B92" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="C92" s="32">
+        <v>138</v>
+      </c>
+      <c r="C92" s="31">
         <v>1944</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I92" s="66">
+        <v>138</v>
+      </c>
+      <c r="I92" s="60">
         <f>SUMIF($B$92:$B$113,H92,$C$92:$C$113)</f>
         <v>1944</v>
       </c>
     </row>
     <row r="93" spans="1:19">
       <c r="B93" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C93" s="32">
+        <v>114</v>
+      </c>
+      <c r="C93" s="31">
         <v>3450</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I93" s="66">
+        <v>114</v>
+      </c>
+      <c r="I93" s="60">
         <f t="shared" ref="I93:I110" si="5">SUMIF($B$92:$B$113,H93,$C$92:$C$113)</f>
         <v>3450</v>
       </c>
     </row>
     <row r="94" spans="1:19">
       <c r="B94" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="C94" s="32">
+        <v>89</v>
+      </c>
+      <c r="C94" s="31">
         <v>1329</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="I94" s="66">
+        <v>89</v>
+      </c>
+      <c r="I94" s="60">
         <f t="shared" si="5"/>
         <v>1329</v>
       </c>
     </row>
     <row r="95" spans="1:19">
       <c r="B95" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="C95" s="32">
+        <v>136</v>
+      </c>
+      <c r="C95" s="31">
         <v>3842</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I95" s="66">
+        <v>136</v>
+      </c>
+      <c r="I95" s="60">
         <f t="shared" si="5"/>
         <v>3842</v>
       </c>
     </row>
     <row r="96" spans="1:19">
       <c r="B96" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="C96" s="32">
+        <v>98</v>
+      </c>
+      <c r="C96" s="31">
         <v>4778</v>
       </c>
       <c r="H96" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="I96" s="66">
+        <v>98</v>
+      </c>
+      <c r="I96" s="60">
         <f t="shared" si="5"/>
         <v>4778</v>
       </c>
     </row>
     <row r="97" spans="2:9">
       <c r="B97" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="C97" s="32">
+        <v>137</v>
+      </c>
+      <c r="C97" s="31">
         <v>3588</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="I97" s="66">
+        <v>137</v>
+      </c>
+      <c r="I97" s="60">
         <f t="shared" si="5"/>
         <v>3588</v>
       </c>
     </row>
     <row r="98" spans="2:9">
       <c r="B98" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C98" s="32">
+        <v>92</v>
+      </c>
+      <c r="C98" s="31">
         <v>2778</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I98" s="66">
+        <v>92</v>
+      </c>
+      <c r="I98" s="60">
         <f t="shared" si="5"/>
         <v>2778</v>
       </c>
     </row>
     <row r="99" spans="2:9">
       <c r="B99" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="C99" s="32">
+        <v>101</v>
+      </c>
+      <c r="C99" s="31">
         <v>9860</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I99" s="66">
+        <v>101</v>
+      </c>
+      <c r="I99" s="60">
         <f t="shared" si="5"/>
         <v>9860</v>
       </c>
     </row>
     <row r="100" spans="2:9">
       <c r="B100" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C100" s="32">
+        <v>86</v>
+      </c>
+      <c r="C100" s="31">
         <v>6371</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="I100" s="66">
+        <v>86</v>
+      </c>
+      <c r="I100" s="60">
         <f t="shared" si="5"/>
         <v>6371</v>
       </c>
     </row>
     <row r="101" spans="2:9">
       <c r="B101" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="C101" s="32">
+        <v>135</v>
+      </c>
+      <c r="C101" s="31">
         <v>6000</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="I101" s="66">
+        <v>135</v>
+      </c>
+      <c r="I101" s="60">
         <f t="shared" si="5"/>
         <v>6000</v>
       </c>
     </row>
     <row r="102" spans="2:9">
       <c r="B102" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C102" s="32">
+        <v>116</v>
+      </c>
+      <c r="C102" s="31">
         <v>2931</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="I102" s="66">
+        <v>116</v>
+      </c>
+      <c r="I102" s="60">
         <f t="shared" si="5"/>
         <v>2931</v>
       </c>
     </row>
     <row r="103" spans="2:9">
       <c r="B103" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="C103" s="32">
+        <v>131</v>
+      </c>
+      <c r="C103" s="31">
         <v>7893</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="I103" s="66">
+        <v>131</v>
+      </c>
+      <c r="I103" s="60">
         <f t="shared" si="5"/>
         <v>7893</v>
       </c>
     </row>
     <row r="104" spans="2:9">
       <c r="B104" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C104" s="32">
+        <v>133</v>
+      </c>
+      <c r="C104" s="31">
         <v>2234</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="I104" s="66">
+        <v>133</v>
+      </c>
+      <c r="I104" s="60">
         <f t="shared" si="5"/>
         <v>2234</v>
       </c>
     </row>
     <row r="105" spans="2:9">
       <c r="B105" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="C105" s="32">
+        <v>142</v>
+      </c>
+      <c r="C105" s="31">
         <v>6150</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="I105" s="66">
+        <v>119</v>
+      </c>
+      <c r="I105" s="60">
         <f>SUM(C105:C106)</f>
         <v>11740</v>
       </c>
     </row>
     <row r="106" spans="2:9">
       <c r="B106" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="C106" s="32">
+        <v>143</v>
+      </c>
+      <c r="C106" s="31">
         <v>5590</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="I106" s="66">
+        <v>132</v>
+      </c>
+      <c r="I106" s="60">
         <f t="shared" si="5"/>
         <v>3037</v>
       </c>
     </row>
     <row r="107" spans="2:9">
       <c r="B107" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="C107" s="32">
+        <v>132</v>
+      </c>
+      <c r="C107" s="31">
         <v>3037</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="I107" s="66">
+        <v>134</v>
+      </c>
+      <c r="I107" s="60">
         <f t="shared" si="5"/>
         <v>2811</v>
       </c>
     </row>
     <row r="108" spans="2:9">
       <c r="B108" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="C108" s="32">
+        <v>134</v>
+      </c>
+      <c r="C108" s="31">
         <v>2811</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I108" s="66">
+        <v>140</v>
+      </c>
+      <c r="I108" s="60">
         <f t="shared" si="5"/>
         <v>2450</v>
       </c>
     </row>
     <row r="109" spans="2:9">
       <c r="B109" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="C109" s="32">
+        <v>140</v>
+      </c>
+      <c r="C109" s="31">
         <v>2450</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I109" s="66">
+        <v>82</v>
+      </c>
+      <c r="I109" s="60">
         <f t="shared" si="5"/>
         <v>8940</v>
       </c>
     </row>
     <row r="110" spans="2:9">
       <c r="B110" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="C110" s="32">
+        <v>144</v>
+      </c>
+      <c r="C110" s="31">
         <v>0</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="I110" s="66">
+        <v>141</v>
+      </c>
+      <c r="I110" s="60">
         <f t="shared" si="5"/>
         <v>1458</v>
       </c>
     </row>
     <row r="111" spans="2:9">
       <c r="B111" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C111" s="32">
+        <v>82</v>
+      </c>
+      <c r="C111" s="31">
         <v>8940</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="I111" s="38">
+        <v>127</v>
+      </c>
+      <c r="I111" s="37">
         <f>SUM(I92:I110)</f>
         <v>87434</v>
       </c>
     </row>
     <row r="112" spans="2:9">
       <c r="B112" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="C112" s="32">
+        <v>141</v>
+      </c>
+      <c r="C112" s="31">
         <v>1458</v>
       </c>
     </row>
     <row r="113" spans="1:19">
-      <c r="B113" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="C113" s="34">
+      <c r="B113" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="C113" s="33">
         <f>SUM(C92:C112)</f>
         <v>87434</v>
       </c>
     </row>
     <row r="114" spans="1:19">
       <c r="B114" s="13" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
     </row>
     <row r="115" spans="1:19">
@@ -4806,1167 +4397,1167 @@
     </row>
     <row r="118" spans="1:19" ht="24">
       <c r="B118" s="3" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:19" ht="19">
       <c r="B119" s="26" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H119" s="26" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
     </row>
     <row r="120" spans="1:19" ht="18">
       <c r="B120" s="14" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="H120" s="14" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="I120" s="16" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:19">
       <c r="B121" s="5" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="C121" t="s">
-        <v>140</v>
-      </c>
-      <c r="D121" s="66">
+        <v>119</v>
+      </c>
+      <c r="D121" s="60">
         <v>787292</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I121" s="66" cm="1">
+        <v>138</v>
+      </c>
+      <c r="I121" s="60" cm="1">
         <f t="array" ref="I121">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H121," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>1419236</v>
       </c>
     </row>
     <row r="122" spans="1:19">
       <c r="B122" s="5" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="C122" t="s">
-        <v>107</v>
-      </c>
-      <c r="D122" s="66">
+        <v>86</v>
+      </c>
+      <c r="D122" s="60">
         <v>873429</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I122" s="66" cm="1">
+        <v>114</v>
+      </c>
+      <c r="I122" s="60" cm="1">
         <f t="array" ref="I122">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H122," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2934594</v>
       </c>
     </row>
     <row r="123" spans="1:19">
       <c r="B123" s="5" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="C123" t="s">
-        <v>137</v>
-      </c>
-      <c r="D123" s="66">
+        <v>116</v>
+      </c>
+      <c r="D123" s="60">
         <v>617861</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="I123" s="66" cm="1">
+        <v>89</v>
+      </c>
+      <c r="I123" s="60" cm="1">
         <f t="array" ref="I123">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H123," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>1142298</v>
       </c>
     </row>
     <row r="124" spans="1:19">
       <c r="B124" s="5" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="C124" t="s">
-        <v>100</v>
-      </c>
-      <c r="D124" s="66">
+        <v>79</v>
+      </c>
+      <c r="D124" s="60">
         <v>1058822</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I124" s="66" cm="1">
+        <v>136</v>
+      </c>
+      <c r="I124" s="60" cm="1">
         <f t="array" ref="I124">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H124," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>3285382</v>
       </c>
     </row>
     <row r="125" spans="1:19">
       <c r="B125" s="5" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="C125" t="s">
-        <v>145</v>
-      </c>
-      <c r="D125" s="66">
+        <v>124</v>
+      </c>
+      <c r="D125" s="60">
         <v>846192</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="I125" s="66" cm="1">
+        <v>98</v>
+      </c>
+      <c r="I125" s="60" cm="1">
         <f t="array" ref="I125">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H125," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>3198425</v>
       </c>
     </row>
     <row r="126" spans="1:19">
       <c r="B126" s="5" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="C126" t="s">
-        <v>135</v>
-      </c>
-      <c r="D126" s="66">
+        <v>114</v>
+      </c>
+      <c r="D126" s="60">
         <v>184561</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="I126" s="66" cm="1">
+        <v>137</v>
+      </c>
+      <c r="I126" s="60" cm="1">
         <f t="array" ref="I126">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H126," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2798493</v>
       </c>
     </row>
     <row r="127" spans="1:19">
       <c r="B127" s="5" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="C127" t="s">
-        <v>113</v>
-      </c>
-      <c r="D127" s="66">
+        <v>92</v>
+      </c>
+      <c r="D127" s="60">
         <v>1299990</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I127" s="66" cm="1">
+        <v>92</v>
+      </c>
+      <c r="I127" s="60" cm="1">
         <f t="array" ref="I127">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H127," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2239671</v>
       </c>
     </row>
     <row r="128" spans="1:19">
       <c r="B128" s="5" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="C128" t="s">
-        <v>140</v>
-      </c>
-      <c r="D128" s="66">
+        <v>119</v>
+      </c>
+      <c r="D128" s="60">
         <v>642168</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I128" s="66" cm="1">
+        <v>101</v>
+      </c>
+      <c r="I128" s="60" cm="1">
         <f t="array" ref="I128">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H128," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>6864697</v>
       </c>
     </row>
     <row r="129" spans="2:9">
       <c r="B129" s="5" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="C129" t="s">
-        <v>134</v>
-      </c>
-      <c r="D129" s="66">
+        <v>113</v>
+      </c>
+      <c r="D129" s="60">
         <v>580299</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="I129" s="66" cm="1">
+        <v>86</v>
+      </c>
+      <c r="I129" s="60" cm="1">
         <f t="array" ref="I129">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H129," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>4223240</v>
       </c>
     </row>
     <row r="130" spans="2:9">
       <c r="B130" s="5" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="C130" t="s">
-        <v>141</v>
-      </c>
-      <c r="D130" s="66">
+        <v>120</v>
+      </c>
+      <c r="D130" s="60">
         <v>548943</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="I130" s="66" cm="1">
+        <v>135</v>
+      </c>
+      <c r="I130" s="60" cm="1">
         <f t="array" ref="I130">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H130," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>4368519</v>
       </c>
     </row>
     <row r="131" spans="2:9">
       <c r="B131" s="5" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="C131" t="s">
-        <v>124</v>
-      </c>
-      <c r="D131" s="66">
+        <v>103</v>
+      </c>
+      <c r="D131" s="60">
         <v>612375</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="I131" s="66" cm="1">
+        <v>116</v>
+      </c>
+      <c r="I131" s="60" cm="1">
         <f t="array" ref="I131">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H131," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2322955</v>
       </c>
     </row>
     <row r="132" spans="2:9">
       <c r="B132" s="5" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="C132" t="s">
-        <v>123</v>
-      </c>
-      <c r="D132" s="66">
+        <v>102</v>
+      </c>
+      <c r="D132" s="60">
         <v>323958</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="I132" s="66" cm="1">
+        <v>131</v>
+      </c>
+      <c r="I132" s="60" cm="1">
         <f t="array" ref="I132">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H132," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>6230375</v>
       </c>
     </row>
     <row r="133" spans="2:9">
       <c r="B133" s="5" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="C133" t="s">
-        <v>144</v>
-      </c>
-      <c r="D133" s="66">
+        <v>123</v>
+      </c>
+      <c r="D133" s="60">
         <v>367651</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="I133" s="66" cm="1">
+        <v>133</v>
+      </c>
+      <c r="I133" s="60" cm="1">
         <f t="array" ref="I133">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H133," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2065476</v>
       </c>
     </row>
     <row r="134" spans="2:9">
       <c r="B134" s="5" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="C134" t="s">
-        <v>102</v>
-      </c>
-      <c r="D134" s="66">
+        <v>81</v>
+      </c>
+      <c r="D134" s="60">
         <v>884375</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="I134" s="66" cm="1">
+        <v>119</v>
+      </c>
+      <c r="I134" s="60" cm="1">
         <f t="array" ref="I134">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H134," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>8749623</v>
       </c>
     </row>
     <row r="135" spans="2:9">
       <c r="B135" s="5" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="C135" t="s">
-        <v>107</v>
-      </c>
-      <c r="D135" s="66">
+        <v>86</v>
+      </c>
+      <c r="D135" s="60">
         <v>746907</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="I135" s="66" cm="1">
+        <v>132</v>
+      </c>
+      <c r="I135" s="60" cm="1">
         <f t="array" ref="I135">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H135," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2345226</v>
       </c>
     </row>
     <row r="136" spans="2:9">
       <c r="B136" s="5" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="C136" t="s">
-        <v>103</v>
-      </c>
-      <c r="D136" s="66">
+        <v>82</v>
+      </c>
+      <c r="D136" s="60">
         <v>991489</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="I136" s="66" cm="1">
+        <v>134</v>
+      </c>
+      <c r="I136" s="60" cm="1">
         <f t="array" ref="I136">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H136," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2126767</v>
       </c>
     </row>
     <row r="137" spans="2:9">
       <c r="B137" s="5" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="C137" t="s">
-        <v>103</v>
-      </c>
-      <c r="D137" s="66">
+        <v>82</v>
+      </c>
+      <c r="D137" s="60">
         <v>1424150</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I137" s="66" cm="1">
+        <v>140</v>
+      </c>
+      <c r="I137" s="60" cm="1">
         <f t="array" ref="I137">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H137," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>2087707</v>
       </c>
     </row>
     <row r="138" spans="2:9">
       <c r="B138" s="5" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="C138" t="s">
-        <v>101</v>
-      </c>
-      <c r="D138" s="66">
+        <v>80</v>
+      </c>
+      <c r="D138" s="60">
         <v>789422</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I138" s="66" cm="1">
+        <v>82</v>
+      </c>
+      <c r="I138" s="60" cm="1">
         <f t="array" ref="I138">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H138," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>7295297</v>
       </c>
     </row>
     <row r="139" spans="2:9">
       <c r="B139" s="5" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="C139" t="s">
-        <v>103</v>
-      </c>
-      <c r="D139" s="66">
+        <v>82</v>
+      </c>
+      <c r="D139" s="60">
         <v>372759</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="I139" s="66" cm="1">
+        <v>141</v>
+      </c>
+      <c r="I139" s="60" cm="1">
         <f t="array" ref="I139">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H139," and ",","),",")),0))*$D$121:$D$210)</f>
         <v>947950</v>
       </c>
     </row>
     <row r="140" spans="2:9">
       <c r="B140" s="5" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="C140" t="s">
-        <v>140</v>
-      </c>
-      <c r="D140" s="66">
+        <v>119</v>
+      </c>
+      <c r="D140" s="60">
         <v>492032</v>
       </c>
       <c r="H140" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="I140" s="38">
+        <v>127</v>
+      </c>
+      <c r="I140" s="37">
         <f>SUM(D121:D210)</f>
         <v>66645931</v>
       </c>
     </row>
     <row r="141" spans="2:9">
       <c r="B141" s="5" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C141" t="s">
-        <v>139</v>
-      </c>
-      <c r="D141" s="66">
+        <v>118</v>
+      </c>
+      <c r="D141" s="60">
         <v>441463</v>
       </c>
     </row>
     <row r="142" spans="2:9">
       <c r="B142" s="5" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="C142" t="s">
-        <v>103</v>
-      </c>
-      <c r="D142" s="66">
+        <v>82</v>
+      </c>
+      <c r="D142" s="60">
         <v>1951045</v>
       </c>
     </row>
     <row r="143" spans="2:9">
       <c r="B143" s="5" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="C143" t="s">
-        <v>104</v>
-      </c>
-      <c r="D143" s="66">
+        <v>83</v>
+      </c>
+      <c r="D143" s="60">
         <v>243722</v>
       </c>
     </row>
     <row r="144" spans="2:9">
       <c r="B144" s="5" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="C144" t="s">
-        <v>140</v>
-      </c>
-      <c r="D144" s="66">
+        <v>119</v>
+      </c>
+      <c r="D144" s="60">
         <v>1122560</v>
       </c>
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="5" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="C145" t="s">
-        <v>107</v>
-      </c>
-      <c r="D145" s="66">
+        <v>86</v>
+      </c>
+      <c r="D145" s="60">
         <v>581354</v>
       </c>
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="5" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="C146" t="s">
-        <v>108</v>
-      </c>
-      <c r="D146" s="66">
+        <v>87</v>
+      </c>
+      <c r="D146" s="60">
         <v>405369</v>
       </c>
     </row>
     <row r="147" spans="2:4">
       <c r="B147" s="5" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="C147" t="s">
-        <v>100</v>
-      </c>
-      <c r="D147" s="66">
+        <v>79</v>
+      </c>
+      <c r="D147" s="60">
         <v>520546</v>
       </c>
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="5" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="C148" t="s">
-        <v>133</v>
-      </c>
-      <c r="D148" s="66">
+        <v>112</v>
+      </c>
+      <c r="D148" s="60">
         <v>494937</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="5" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="C149" t="s">
-        <v>122</v>
-      </c>
-      <c r="D149" s="66">
+        <v>101</v>
+      </c>
+      <c r="D149" s="60">
         <v>780363</v>
       </c>
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="5" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C150" t="s">
-        <v>122</v>
-      </c>
-      <c r="D150" s="66">
+        <v>101</v>
+      </c>
+      <c r="D150" s="60">
         <v>548811</v>
       </c>
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="5" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="C151" t="s">
-        <v>112</v>
-      </c>
-      <c r="D151" s="66">
+        <v>91</v>
+      </c>
+      <c r="D151" s="60">
         <v>841277</v>
       </c>
     </row>
     <row r="152" spans="2:4">
       <c r="B152" s="5" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="C152" t="s">
-        <v>116</v>
-      </c>
-      <c r="D152" s="66">
+        <v>95</v>
+      </c>
+      <c r="D152" s="60">
         <v>236953</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="5" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="C153" t="s">
-        <v>101</v>
-      </c>
-      <c r="D153" s="66">
+        <v>80</v>
+      </c>
+      <c r="D153" s="60">
         <v>483450</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="5" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="C154" t="s">
-        <v>132</v>
-      </c>
-      <c r="D154" s="66">
+        <v>111</v>
+      </c>
+      <c r="D154" s="60">
         <v>478200</v>
       </c>
     </row>
     <row r="155" spans="2:4">
       <c r="B155" s="5" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="C155" t="s">
-        <v>138</v>
-      </c>
-      <c r="D155" s="66">
+        <v>117</v>
+      </c>
+      <c r="D155" s="60">
         <v>825771</v>
       </c>
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="5" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="C156" t="s">
-        <v>140</v>
-      </c>
-      <c r="D156" s="66">
+        <v>119</v>
+      </c>
+      <c r="D156" s="60">
         <v>309171</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="5" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="C157" t="s">
-        <v>104</v>
-      </c>
-      <c r="D157" s="66">
+        <v>83</v>
+      </c>
+      <c r="D157" s="60">
         <v>623704</v>
       </c>
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="5" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="C158" t="s">
-        <v>128</v>
-      </c>
-      <c r="D158" s="66">
+        <v>107</v>
+      </c>
+      <c r="D158" s="60">
         <v>304227</v>
       </c>
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="5" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="C159" t="s">
-        <v>137</v>
-      </c>
-      <c r="D159" s="66">
+        <v>116</v>
+      </c>
+      <c r="D159" s="60">
         <v>499783</v>
       </c>
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="5" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="C160" t="s">
-        <v>111</v>
-      </c>
-      <c r="D160" s="66">
+        <v>90</v>
+      </c>
+      <c r="D160" s="60">
         <v>444881</v>
       </c>
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="5" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="C161" t="s">
-        <v>135</v>
-      </c>
-      <c r="D161" s="66">
+        <v>114</v>
+      </c>
+      <c r="D161" s="60">
         <v>583943</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="5" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="C162" t="s">
-        <v>129</v>
-      </c>
-      <c r="D162" s="66">
+        <v>108</v>
+      </c>
+      <c r="D162" s="60">
         <v>61388</v>
       </c>
     </row>
     <row r="163" spans="2:4">
       <c r="B163" s="5" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="C163" t="s">
-        <v>111</v>
-      </c>
-      <c r="D163" s="66">
+        <v>90</v>
+      </c>
+      <c r="D163" s="60">
         <v>67822</v>
       </c>
     </row>
     <row r="164" spans="2:4">
       <c r="B164" s="5" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="C164" t="s">
-        <v>117</v>
-      </c>
-      <c r="D164" s="66">
+        <v>96</v>
+      </c>
+      <c r="D164" s="60">
         <v>1857878</v>
       </c>
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="5" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="C165" t="s">
-        <v>111</v>
-      </c>
-      <c r="D165" s="66">
+        <v>90</v>
+      </c>
+      <c r="D165" s="60">
         <v>833267</v>
       </c>
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="5" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="C166" t="s">
-        <v>135</v>
-      </c>
-      <c r="D166" s="66">
+        <v>114</v>
+      </c>
+      <c r="D166" s="60">
         <v>646387</v>
       </c>
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="5" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="C167" t="s">
-        <v>135</v>
-      </c>
-      <c r="D167" s="66">
+        <v>114</v>
+      </c>
+      <c r="D167" s="60">
         <v>456577</v>
       </c>
     </row>
     <row r="168" spans="2:4">
       <c r="B168" s="5" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="C168" t="s">
-        <v>100</v>
-      </c>
-      <c r="D168" s="66">
+        <v>79</v>
+      </c>
+      <c r="D168" s="60">
         <v>522543</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="5" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="C169" t="s">
-        <v>133</v>
-      </c>
-      <c r="D169" s="66">
+        <v>112</v>
+      </c>
+      <c r="D169" s="60">
         <v>429907</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="5" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="C170" t="s">
-        <v>140</v>
-      </c>
-      <c r="D170" s="66">
+        <v>119</v>
+      </c>
+      <c r="D170" s="60">
         <v>1253349</v>
       </c>
     </row>
     <row r="171" spans="2:4">
       <c r="B171" s="5" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="C171" t="s">
-        <v>100</v>
-      </c>
-      <c r="D171" s="66">
+        <v>79</v>
+      </c>
+      <c r="D171" s="60">
         <v>615636</v>
       </c>
     </row>
     <row r="172" spans="2:4">
       <c r="B172" s="5" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="C172" t="s">
-        <v>137</v>
-      </c>
-      <c r="D172" s="66">
+        <v>116</v>
+      </c>
+      <c r="D172" s="60">
         <v>1205311</v>
       </c>
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="5" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="C173" t="s">
-        <v>117</v>
-      </c>
-      <c r="D173" s="66">
+        <v>96</v>
+      </c>
+      <c r="D173" s="60">
         <v>451527</v>
       </c>
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="5" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="C174" t="s">
-        <v>119</v>
-      </c>
-      <c r="D174" s="66">
+        <v>98</v>
+      </c>
+      <c r="D174" s="60">
         <v>1769013</v>
       </c>
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="5" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="C175" t="s">
-        <v>141</v>
-      </c>
-      <c r="D175" s="66">
+        <v>120</v>
+      </c>
+      <c r="D175" s="60">
         <v>579152</v>
       </c>
     </row>
     <row r="176" spans="2:4">
       <c r="B176" s="5" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="C176" t="s">
-        <v>110</v>
-      </c>
-      <c r="D176" s="66">
+        <v>89</v>
+      </c>
+      <c r="D176" s="60">
         <v>380737</v>
       </c>
     </row>
     <row r="177" spans="2:4">
       <c r="B177" s="5" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="C177" t="s">
-        <v>104</v>
-      </c>
-      <c r="D177" s="66">
+        <v>83</v>
+      </c>
+      <c r="D177" s="60">
         <v>737083</v>
       </c>
     </row>
     <row r="178" spans="2:4">
       <c r="B178" s="5" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="C178" t="s">
-        <v>122</v>
-      </c>
-      <c r="D178" s="66">
+        <v>101</v>
+      </c>
+      <c r="D178" s="60">
         <v>2967851</v>
       </c>
     </row>
     <row r="179" spans="2:4">
       <c r="B179" s="5" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="C179" t="s">
-        <v>132</v>
-      </c>
-      <c r="D179" s="66">
+        <v>111</v>
+      </c>
+      <c r="D179" s="60">
         <v>358128</v>
       </c>
     </row>
     <row r="180" spans="2:4">
       <c r="B180" s="5" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="C180" t="s">
-        <v>110</v>
-      </c>
-      <c r="D180" s="66">
+        <v>89</v>
+      </c>
+      <c r="D180" s="60">
         <v>761561</v>
       </c>
     </row>
     <row r="181" spans="2:4">
       <c r="B181" s="5" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="C181" t="s">
-        <v>135</v>
-      </c>
-      <c r="D181" s="66">
+        <v>114</v>
+      </c>
+      <c r="D181" s="60">
         <v>684874</v>
       </c>
     </row>
     <row r="182" spans="2:4">
       <c r="B182" s="5" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="C182" t="s">
-        <v>114</v>
-      </c>
-      <c r="D182" s="66">
+        <v>93</v>
+      </c>
+      <c r="D182" s="60">
         <v>1333431</v>
       </c>
     </row>
     <row r="183" spans="2:4">
       <c r="B183" s="5" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="C183" t="s">
-        <v>135</v>
-      </c>
-      <c r="D183" s="66">
+        <v>114</v>
+      </c>
+      <c r="D183" s="60">
         <v>295726</v>
       </c>
     </row>
     <row r="184" spans="2:4">
       <c r="B184" s="5" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="C184" t="s">
-        <v>129</v>
-      </c>
-      <c r="D184" s="66">
+        <v>108</v>
+      </c>
+      <c r="D184" s="60">
         <v>1120895</v>
       </c>
     </row>
     <row r="185" spans="2:4">
       <c r="B185" s="5" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="C185" t="s">
-        <v>112</v>
-      </c>
-      <c r="D185" s="66">
+        <v>91</v>
+      </c>
+      <c r="D185" s="60">
         <v>519070</v>
       </c>
     </row>
     <row r="186" spans="2:4">
       <c r="B186" s="5" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="C186" t="s">
-        <v>140</v>
-      </c>
-      <c r="D186" s="66">
+        <v>119</v>
+      </c>
+      <c r="D186" s="60">
         <v>80285</v>
       </c>
     </row>
     <row r="187" spans="2:4">
       <c r="B187" s="5" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="C187" t="s">
-        <v>135</v>
-      </c>
-      <c r="D187" s="66">
+        <v>114</v>
+      </c>
+      <c r="D187" s="60">
         <v>82526</v>
       </c>
     </row>
     <row r="188" spans="2:4">
       <c r="B188" s="5" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="C188" t="s">
-        <v>133</v>
-      </c>
-      <c r="D188" s="66">
+        <v>112</v>
+      </c>
+      <c r="D188" s="60">
         <v>256257</v>
       </c>
     </row>
     <row r="189" spans="2:4">
       <c r="B189" s="5" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="C189" t="s">
-        <v>122</v>
-      </c>
-      <c r="D189" s="66">
+        <v>101</v>
+      </c>
+      <c r="D189" s="60">
         <v>1010547</v>
       </c>
     </row>
     <row r="190" spans="2:4">
       <c r="B190" s="5" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="C190" t="s">
-        <v>111</v>
-      </c>
-      <c r="D190" s="66">
+        <v>90</v>
+      </c>
+      <c r="D190" s="60">
         <v>1103084</v>
       </c>
     </row>
     <row r="191" spans="2:4">
       <c r="B191" s="5" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="C191" t="s">
-        <v>140</v>
-      </c>
-      <c r="D191" s="66">
+        <v>119</v>
+      </c>
+      <c r="D191" s="60">
         <v>632181</v>
       </c>
     </row>
     <row r="192" spans="2:4">
       <c r="B192" s="5" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="C192" t="s">
-        <v>140</v>
-      </c>
-      <c r="D192" s="66">
+        <v>119</v>
+      </c>
+      <c r="D192" s="60">
         <v>1323231</v>
       </c>
     </row>
     <row r="193" spans="2:4">
       <c r="B193" s="5" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="C193" t="s">
-        <v>140</v>
-      </c>
-      <c r="D193" s="66">
+        <v>119</v>
+      </c>
+      <c r="D193" s="60">
         <v>1289116</v>
       </c>
     </row>
     <row r="194" spans="2:4">
       <c r="B194" s="5" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="C194" t="s">
-        <v>103</v>
-      </c>
-      <c r="D194" s="66">
+        <v>82</v>
+      </c>
+      <c r="D194" s="60">
         <v>1221243</v>
       </c>
     </row>
     <row r="195" spans="2:4">
       <c r="B195" s="5" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="C195" t="s">
-        <v>113</v>
-      </c>
-      <c r="D195" s="66">
+        <v>92</v>
+      </c>
+      <c r="D195" s="60">
         <v>939681</v>
       </c>
     </row>
     <row r="196" spans="2:4">
       <c r="B196" s="5" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="C196" t="s">
-        <v>147</v>
-      </c>
-      <c r="D196" s="66">
+        <v>126</v>
+      </c>
+      <c r="D196" s="60">
         <v>522258</v>
       </c>
     </row>
     <row r="197" spans="2:4">
       <c r="B197" s="5" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="C197" t="s">
-        <v>100</v>
-      </c>
-      <c r="D197" s="66">
+        <v>79</v>
+      </c>
+      <c r="D197" s="60">
         <v>923191</v>
       </c>
     </row>
     <row r="198" spans="2:4">
       <c r="B198" s="5" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="C198" t="s">
-        <v>103</v>
-      </c>
-      <c r="D198" s="66">
+        <v>82</v>
+      </c>
+      <c r="D198" s="60">
         <v>807598</v>
       </c>
     </row>
     <row r="199" spans="2:4">
       <c r="B199" s="5" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="C199" t="s">
-        <v>125</v>
-      </c>
-      <c r="D199" s="66">
+        <v>104</v>
+      </c>
+      <c r="D199" s="60">
         <v>385165</v>
       </c>
     </row>
     <row r="200" spans="2:4">
       <c r="B200" s="5" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="C200" t="s">
-        <v>101</v>
-      </c>
-      <c r="D200" s="66">
+        <v>80</v>
+      </c>
+      <c r="D200" s="60">
         <v>768127</v>
       </c>
     </row>
     <row r="201" spans="2:4">
       <c r="B201" s="5" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="C201" t="s">
-        <v>122</v>
-      </c>
-      <c r="D201" s="66">
+        <v>101</v>
+      </c>
+      <c r="D201" s="60">
         <v>1557125</v>
       </c>
     </row>
     <row r="202" spans="2:4">
       <c r="B202" s="5" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="C202" t="s">
-        <v>143</v>
-      </c>
-      <c r="D202" s="66">
+        <v>122</v>
+      </c>
+      <c r="D202" s="60">
         <v>807553</v>
       </c>
     </row>
     <row r="203" spans="2:4">
       <c r="B203" s="5" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="C203" t="s">
-        <v>139</v>
-      </c>
-      <c r="D203" s="66">
+        <v>118</v>
+      </c>
+      <c r="D203" s="60">
         <v>814743</v>
       </c>
     </row>
     <row r="204" spans="2:4">
       <c r="B204" s="5" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="C204" t="s">
-        <v>119</v>
-      </c>
-      <c r="D204" s="66">
+        <v>98</v>
+      </c>
+      <c r="D204" s="60">
         <v>1429412</v>
       </c>
     </row>
     <row r="205" spans="2:4">
       <c r="B205" s="5" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="C205" t="s">
-        <v>107</v>
-      </c>
-      <c r="D205" s="66">
+        <v>86</v>
+      </c>
+      <c r="D205" s="60">
         <v>361182</v>
       </c>
     </row>
     <row r="206" spans="2:4">
       <c r="B206" s="5" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="C206" t="s">
-        <v>107</v>
-      </c>
-      <c r="D206" s="66">
+        <v>86</v>
+      </c>
+      <c r="D206" s="60">
         <v>567263</v>
       </c>
     </row>
     <row r="207" spans="2:4">
       <c r="B207" s="5" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="C207" t="s">
-        <v>107</v>
-      </c>
-      <c r="D207" s="66">
+        <v>86</v>
+      </c>
+      <c r="D207" s="60">
         <v>1093105</v>
       </c>
     </row>
     <row r="208" spans="2:4">
       <c r="B208" s="5" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="C208" t="s">
-        <v>103</v>
-      </c>
-      <c r="D208" s="66">
+        <v>82</v>
+      </c>
+      <c r="D208" s="60">
         <v>527013</v>
       </c>
     </row>
     <row r="209" spans="1:19">
       <c r="B209" s="5" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="C209" t="s">
-        <v>140</v>
-      </c>
-      <c r="D209" s="66">
+        <v>119</v>
+      </c>
+      <c r="D209" s="60">
         <v>818238</v>
       </c>
     </row>
     <row r="210" spans="1:19">
       <c r="B210" s="8" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="C210" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="D210" s="38">
+        <v>102</v>
+      </c>
+      <c r="D210" s="37">
         <v>250489</v>
       </c>
     </row>
     <row r="211" spans="1:19">
       <c r="B211" s="12" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
     </row>
     <row r="213" spans="1:19">
@@ -5992,351 +5583,351 @@
     </row>
     <row r="215" spans="1:19" ht="24">
       <c r="B215" s="3" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
     </row>
     <row r="216" spans="1:19" ht="19">
       <c r="B216" s="26" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="H216" s="26" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
     </row>
     <row r="217" spans="1:19">
       <c r="B217" s="14" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="C217" s="16" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="H217" s="14" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="I217" s="16" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
     </row>
     <row r="218" spans="1:19">
       <c r="B218" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="C218" s="32">
+        <v>138</v>
+      </c>
+      <c r="C218" s="31">
         <v>3258</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I218" s="66">
+        <v>138</v>
+      </c>
+      <c r="I218" s="60">
         <f>SUMIF($B$218:$B$238,H218,$C$218:$C$238)</f>
         <v>3258</v>
       </c>
     </row>
     <row r="219" spans="1:19">
       <c r="B219" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C219" s="32">
+        <v>114</v>
+      </c>
+      <c r="C219" s="31">
         <v>5790</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I219" s="66">
+        <v>114</v>
+      </c>
+      <c r="I219" s="60">
         <f t="shared" ref="I219:I236" si="6">SUMIF($B$218:$B$238,H219,$C$218:$C$238)</f>
         <v>5790</v>
       </c>
     </row>
     <row r="220" spans="1:19">
       <c r="B220" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="C220" s="32">
+        <v>89</v>
+      </c>
+      <c r="C220" s="31">
         <v>2531</v>
       </c>
       <c r="H220" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="I220" s="66">
+        <v>89</v>
+      </c>
+      <c r="I220" s="60">
         <f t="shared" si="6"/>
         <v>2531</v>
       </c>
     </row>
     <row r="221" spans="1:19">
       <c r="B221" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="C221" s="32">
+        <v>136</v>
+      </c>
+      <c r="C221" s="31">
         <v>5679</v>
       </c>
       <c r="H221" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I221" s="66">
+        <v>136</v>
+      </c>
+      <c r="I221" s="60">
         <f t="shared" si="6"/>
         <v>5679</v>
       </c>
     </row>
     <row r="222" spans="1:19">
       <c r="B222" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="C222" s="32">
+        <v>98</v>
+      </c>
+      <c r="C222" s="31">
         <v>5738</v>
       </c>
       <c r="H222" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="I222" s="66">
+        <v>98</v>
+      </c>
+      <c r="I222" s="60">
         <f t="shared" si="6"/>
         <v>5738</v>
       </c>
     </row>
     <row r="223" spans="1:19">
       <c r="B223" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="C223" s="32">
+        <v>137</v>
+      </c>
+      <c r="C223" s="31">
         <v>4285</v>
       </c>
       <c r="H223" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="I223" s="66">
+        <v>137</v>
+      </c>
+      <c r="I223" s="60">
         <f t="shared" si="6"/>
         <v>4285</v>
       </c>
     </row>
     <row r="224" spans="1:19">
       <c r="B224" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C224" s="32">
+        <v>92</v>
+      </c>
+      <c r="C224" s="31">
         <v>3172</v>
       </c>
       <c r="H224" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I224" s="66">
+        <v>92</v>
+      </c>
+      <c r="I224" s="60">
         <f t="shared" si="6"/>
         <v>3172</v>
       </c>
     </row>
     <row r="225" spans="2:9">
       <c r="B225" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="C225" s="32">
+        <v>101</v>
+      </c>
+      <c r="C225" s="31">
         <v>11227</v>
       </c>
       <c r="H225" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I225" s="66">
+        <v>101</v>
+      </c>
+      <c r="I225" s="60">
         <f t="shared" si="6"/>
         <v>11227</v>
       </c>
     </row>
     <row r="226" spans="2:9">
       <c r="B226" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C226" s="32">
+        <v>86</v>
+      </c>
+      <c r="C226" s="31">
         <v>10540</v>
       </c>
       <c r="H226" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="I226" s="66">
+        <v>86</v>
+      </c>
+      <c r="I226" s="60">
         <f t="shared" si="6"/>
         <v>10540</v>
       </c>
     </row>
     <row r="227" spans="2:9">
       <c r="B227" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="C227" s="32">
+        <v>135</v>
+      </c>
+      <c r="C227" s="31">
         <v>7930</v>
       </c>
       <c r="H227" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="I227" s="66">
+        <v>135</v>
+      </c>
+      <c r="I227" s="60">
         <f t="shared" si="6"/>
         <v>7930</v>
       </c>
     </row>
     <row r="228" spans="2:9">
       <c r="B228" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C228" s="32">
+        <v>116</v>
+      </c>
+      <c r="C228" s="31">
         <v>5666</v>
       </c>
       <c r="H228" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="I228" s="66">
+        <v>116</v>
+      </c>
+      <c r="I228" s="60">
         <f t="shared" si="6"/>
         <v>5666</v>
       </c>
     </row>
     <row r="229" spans="2:9">
       <c r="B229" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="C229" s="32">
+        <v>131</v>
+      </c>
+      <c r="C229" s="31">
         <v>10124</v>
       </c>
       <c r="H229" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="I229" s="66">
+        <v>131</v>
+      </c>
+      <c r="I229" s="60">
         <f t="shared" si="6"/>
         <v>10124</v>
       </c>
     </row>
     <row r="230" spans="2:9">
       <c r="B230" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C230" s="32">
+        <v>133</v>
+      </c>
+      <c r="C230" s="31">
         <v>3615</v>
       </c>
       <c r="H230" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="I230" s="66">
+        <v>133</v>
+      </c>
+      <c r="I230" s="60">
         <f t="shared" si="6"/>
         <v>3615</v>
       </c>
     </row>
     <row r="231" spans="2:9">
       <c r="B231" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="C231" s="32">
+        <v>142</v>
+      </c>
+      <c r="C231" s="31">
         <v>8140</v>
       </c>
       <c r="H231" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="I231" s="66">
+        <v>119</v>
+      </c>
+      <c r="I231" s="60">
         <f>SUM(C231+C232)</f>
         <v>15760</v>
       </c>
     </row>
     <row r="232" spans="2:9">
       <c r="B232" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="C232" s="32">
+        <v>143</v>
+      </c>
+      <c r="C232" s="31">
         <v>7620</v>
       </c>
       <c r="H232" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="I232" s="66">
+        <v>132</v>
+      </c>
+      <c r="I232" s="60">
         <f t="shared" si="6"/>
         <v>3375</v>
       </c>
     </row>
     <row r="233" spans="2:9">
       <c r="B233" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="C233" s="32">
+        <v>132</v>
+      </c>
+      <c r="C233" s="31">
         <v>3375</v>
       </c>
       <c r="H233" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="I233" s="66">
+        <v>134</v>
+      </c>
+      <c r="I233" s="60">
         <f t="shared" si="6"/>
         <v>4275</v>
       </c>
     </row>
     <row r="234" spans="2:9">
       <c r="B234" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="C234" s="32">
+        <v>134</v>
+      </c>
+      <c r="C234" s="31">
         <v>4275</v>
       </c>
       <c r="H234" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I234" s="66">
+        <v>140</v>
+      </c>
+      <c r="I234" s="60">
         <f t="shared" si="6"/>
         <v>3201</v>
       </c>
     </row>
     <row r="235" spans="2:9">
       <c r="B235" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="C235" s="32">
+        <v>140</v>
+      </c>
+      <c r="C235" s="31">
         <v>3201</v>
       </c>
       <c r="H235" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I235" s="66">
+        <v>82</v>
+      </c>
+      <c r="I235" s="60">
         <f t="shared" si="6"/>
         <v>11300</v>
       </c>
     </row>
     <row r="236" spans="2:9">
       <c r="B236" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="C236" s="32">
+        <v>144</v>
+      </c>
+      <c r="C236" s="31">
         <v>0</v>
       </c>
       <c r="H236" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="I236" s="66">
+        <v>141</v>
+      </c>
+      <c r="I236" s="60">
         <f t="shared" si="6"/>
         <v>2563</v>
       </c>
     </row>
     <row r="237" spans="2:9">
       <c r="B237" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C237" s="32">
+        <v>82</v>
+      </c>
+      <c r="C237" s="31">
         <v>11300</v>
       </c>
       <c r="H237" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="I237" s="38">
+        <v>127</v>
+      </c>
+      <c r="I237" s="37">
         <f>SUM(I218:I236)</f>
         <v>120029</v>
       </c>
     </row>
     <row r="238" spans="2:9">
       <c r="B238" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="C238" s="32">
+        <v>141</v>
+      </c>
+      <c r="C238" s="31">
         <v>2563</v>
       </c>
     </row>
     <row r="239" spans="2:9">
-      <c r="B239" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="C239" s="34">
+      <c r="B239" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="C239" s="33">
         <f>SUM(C218:C238)</f>
         <v>120029</v>
       </c>
     </row>
     <row r="240" spans="2:9">
       <c r="B240" s="13" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
     </row>
     <row r="242" spans="1:19">
@@ -6362,351 +5953,351 @@
     </row>
     <row r="244" spans="1:19" ht="24">
       <c r="B244" s="3" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
     </row>
     <row r="245" spans="1:19" ht="19">
       <c r="B245" s="26" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="H245" s="26" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
     </row>
     <row r="246" spans="1:19">
       <c r="B246" s="14" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="C246" s="16" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="H246" s="14" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="I246" s="16" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
     </row>
     <row r="247" spans="1:19">
       <c r="B247" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="C247" s="32">
+        <v>138</v>
+      </c>
+      <c r="C247" s="31">
         <v>4</v>
       </c>
       <c r="H247" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I247" s="29">
+        <v>138</v>
+      </c>
+      <c r="I247" s="28">
         <f>SUMIF($B$247:$B$267,H247,$C$247:$C$267)</f>
         <v>4</v>
       </c>
     </row>
     <row r="248" spans="1:19">
       <c r="B248" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C248" s="32">
+        <v>114</v>
+      </c>
+      <c r="C248" s="31">
         <v>7</v>
       </c>
       <c r="H248" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I248" s="29">
+        <v>114</v>
+      </c>
+      <c r="I248" s="28">
         <f t="shared" ref="I248:I265" si="7">SUMIF($B$247:$B$267,H248,$C$247:$C$267)</f>
         <v>7</v>
       </c>
     </row>
     <row r="249" spans="1:19">
       <c r="B249" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="C249" s="32">
+        <v>89</v>
+      </c>
+      <c r="C249" s="31">
         <v>3</v>
       </c>
       <c r="H249" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="I249" s="29">
+        <v>89</v>
+      </c>
+      <c r="I249" s="28">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
     <row r="250" spans="1:19">
       <c r="B250" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="C250" s="32">
+        <v>136</v>
+      </c>
+      <c r="C250" s="31">
         <v>6</v>
       </c>
       <c r="H250" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I250" s="29">
+        <v>136</v>
+      </c>
+      <c r="I250" s="28">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
     <row r="251" spans="1:19">
       <c r="B251" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="C251" s="32">
+        <v>98</v>
+      </c>
+      <c r="C251" s="31">
         <v>3</v>
       </c>
-      <c r="H251" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="I251" s="29">
+      <c r="H251" s="57" t="s">
+        <v>98</v>
+      </c>
+      <c r="I251" s="28">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
     <row r="252" spans="1:19">
       <c r="B252" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="C252" s="32">
+        <v>137</v>
+      </c>
+      <c r="C252" s="31">
         <v>4</v>
       </c>
       <c r="H252" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="I252" s="29">
+        <v>137</v>
+      </c>
+      <c r="I252" s="28">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
     <row r="253" spans="1:19">
       <c r="B253" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C253" s="32">
+        <v>92</v>
+      </c>
+      <c r="C253" s="31">
         <v>2</v>
       </c>
       <c r="H253" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I253" s="29">
+        <v>92</v>
+      </c>
+      <c r="I253" s="28">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="254" spans="1:19">
       <c r="B254" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="C254" s="32">
+        <v>101</v>
+      </c>
+      <c r="C254" s="31">
         <v>5</v>
       </c>
       <c r="H254" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I254" s="29">
+        <v>101</v>
+      </c>
+      <c r="I254" s="28">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:19">
       <c r="B255" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C255" s="32">
+        <v>86</v>
+      </c>
+      <c r="C255" s="31">
         <v>8</v>
       </c>
       <c r="H255" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="I255" s="29">
+        <v>86</v>
+      </c>
+      <c r="I255" s="28">
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:19">
       <c r="B256" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="C256" s="32">
+        <v>135</v>
+      </c>
+      <c r="C256" s="31">
         <v>6</v>
       </c>
       <c r="H256" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="I256" s="29">
+        <v>135</v>
+      </c>
+      <c r="I256" s="28">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
     <row r="257" spans="2:9">
       <c r="B257" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C257" s="32">
+        <v>116</v>
+      </c>
+      <c r="C257" s="31">
         <v>3</v>
       </c>
       <c r="H257" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="I257" s="29">
+        <v>116</v>
+      </c>
+      <c r="I257" s="28">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
     <row r="258" spans="2:9">
       <c r="B258" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="C258" s="32">
+        <v>131</v>
+      </c>
+      <c r="C258" s="31">
         <v>8</v>
       </c>
       <c r="H258" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="I258" s="29">
+        <v>131</v>
+      </c>
+      <c r="I258" s="28">
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
     <row r="259" spans="2:9">
       <c r="B259" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C259" s="32">
+        <v>133</v>
+      </c>
+      <c r="C259" s="31">
         <v>4</v>
       </c>
       <c r="H259" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="I259" s="29">
+        <v>133</v>
+      </c>
+      <c r="I259" s="28">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
     <row r="260" spans="2:9">
       <c r="B260" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="C260" s="32">
+        <v>142</v>
+      </c>
+      <c r="C260" s="31">
         <v>6</v>
       </c>
       <c r="H260" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="I260" s="29">
+        <v>119</v>
+      </c>
+      <c r="I260" s="28">
         <f>SUM(C260:C261)</f>
         <v>12</v>
       </c>
     </row>
     <row r="261" spans="2:9">
       <c r="B261" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="C261" s="32">
+        <v>143</v>
+      </c>
+      <c r="C261" s="31">
         <v>6</v>
       </c>
       <c r="H261" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="I261" s="29">
+        <v>132</v>
+      </c>
+      <c r="I261" s="28">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
     <row r="262" spans="2:9">
       <c r="B262" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="C262" s="32">
+        <v>132</v>
+      </c>
+      <c r="C262" s="31">
         <v>4</v>
       </c>
       <c r="H262" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="I262" s="29">
+        <v>134</v>
+      </c>
+      <c r="I262" s="28">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
     <row r="263" spans="2:9">
       <c r="B263" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="C263" s="32">
+        <v>134</v>
+      </c>
+      <c r="C263" s="31">
         <v>4</v>
       </c>
       <c r="H263" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I263" s="29">
+        <v>140</v>
+      </c>
+      <c r="I263" s="28">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
     <row r="264" spans="2:9">
       <c r="B264" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="C264" s="32">
+        <v>140</v>
+      </c>
+      <c r="C264" s="31">
         <v>5</v>
       </c>
       <c r="H264" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I264" s="29">
+        <v>82</v>
+      </c>
+      <c r="I264" s="28">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
     <row r="265" spans="2:9">
       <c r="B265" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="C265" s="32">
+        <v>144</v>
+      </c>
+      <c r="C265" s="31">
         <v>0</v>
       </c>
       <c r="H265" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="I265" s="29">
+        <v>141</v>
+      </c>
+      <c r="I265" s="28">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
     <row r="266" spans="2:9">
       <c r="B266" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C266" s="32">
+        <v>82</v>
+      </c>
+      <c r="C266" s="31">
         <v>7</v>
       </c>
       <c r="H266" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="I266" s="30">
+        <v>127</v>
+      </c>
+      <c r="I266" s="29">
         <f>SUM(I247:I265)</f>
         <v>99</v>
       </c>
     </row>
     <row r="267" spans="2:9">
       <c r="B267" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="C267" s="32">
+        <v>141</v>
+      </c>
+      <c r="C267" s="31">
         <v>4</v>
       </c>
     </row>
     <row r="268" spans="2:9">
-      <c r="B268" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="C268" s="34">
+      <c r="B268" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="C268" s="33">
         <f>SUM(C247:C267)</f>
         <v>99</v>
       </c>
     </row>
     <row r="269" spans="2:9">
       <c r="B269" s="12" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -6727,7 +6318,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74115B67-C74D-9145-AB87-1B4950580BA5}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="40.1640625" customWidth="1"/>
@@ -6735,21 +6326,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B2" t="str" cm="1">
         <f t="array" ref="B2:B7">_xlfn.UNIQUE(_xlfn.VSTACK('V1. Markets'!B10:B14,'V1. Markets'!B19:B29))</f>
@@ -6766,7 +6357,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B3" t="str">
         <v>Oil and Gas Drilling</v>
@@ -6782,7 +6373,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B4" t="str">
         <v>Organic Chemical Manufacturing</v>
@@ -6798,7 +6389,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B5" t="str">
         <v>Pharmaceutical Manufacturing</v>
@@ -6814,7 +6405,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B6" t="str">
         <v>Industrial Water Treatment</v>
@@ -6830,7 +6421,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B7" t="str">
         <v>Other</v>
@@ -6842,71 +6433,6 @@
       <c r="D7">
         <f>SUMIF('V1. Markets'!$B$19:$B$29,'X1. Markets'!B7,'V1. Markets'!$E$19:$E$29)</f>
         <v>0.14882981140649851</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" t="str" cm="1">
-        <f t="array" ref="B8:B11">_xlfn.UNIQUE(_xlfn.VSTACK('V1. Markets'!B37:B42,'V1. Markets'!B47:B53))</f>
-        <v>Organic Chemical Manufacturing</v>
-      </c>
-      <c r="C8">
-        <f>SUMIF('V1. Markets'!$B$37:$B$42,'X1. Markets'!B8,'V1. Markets'!$E$37:$E$42)</f>
-        <v>0.74</v>
-      </c>
-      <c r="D8">
-        <f>SUMIF('V1. Markets'!$B$47:$B$53,'X1. Markets'!B8,'V1. Markets'!$E$47:$E$53)</f>
-        <v>0.77758342303552197</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Steel Pickling</v>
-      </c>
-      <c r="C9">
-        <f>SUMIF('V1. Markets'!$B$37:$B$42,'X1. Markets'!B9,'V1. Markets'!$E$37:$E$42)</f>
-        <v>0.11</v>
-      </c>
-      <c r="D9">
-        <f>SUMIF('V1. Markets'!$B$47:$B$53,'X1. Markets'!B9,'V1. Markets'!$E$47:$E$53)</f>
-        <v>7.0102260495156082E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Semiconductor Manufacturing</v>
-      </c>
-      <c r="C10">
-        <f>SUMIF('V1. Markets'!$B$37:$B$42,'X1. Markets'!B10,'V1. Markets'!$E$37:$E$42)</f>
-        <v>0.06</v>
-      </c>
-      <c r="D10">
-        <f>SUMIF('V1. Markets'!$B$47:$B$53,'X1. Markets'!B10,'V1. Markets'!$E$47:$E$53)</f>
-        <v>5.086114101184068E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Other</v>
-      </c>
-      <c r="C11">
-        <f>SUMIF('V1. Markets'!$B$37:$B$42,'X1. Markets'!B11,'V1. Markets'!$E$37:$E$42)</f>
-        <v>0.09</v>
-      </c>
-      <c r="D11">
-        <f>SUMIF('V1. Markets'!$B$47:$B$53,'X1. Markets'!B11,'V1. Markets'!$E$47:$E$53)</f>
-        <v>0.10145317545748117</v>
       </c>
     </row>
   </sheetData>
@@ -6917,7 +6443,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C150CD-4522-2042-8723-88D7EFAA8ACD}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
@@ -6925,109 +6451,91 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A12">_xlfn.UNIQUE('V2. Demand'!B6:B16)</f>
-        <v>B2O3</v>
+        <f t="array" ref="A2:A10">_xlfn.UNIQUE('V2. Demand'!B6:B14)</f>
+        <v>BaSO4</v>
       </c>
       <c r="B2">
         <f>_xlfn.XLOOKUP($A2,'V2. Demand'!$B:$B,'V2. Demand'!D:D)</f>
-        <v>580</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="str">
-        <v>BaSO4</v>
+        <v>Br</v>
       </c>
       <c r="B3">
         <f>_xlfn.XLOOKUP($A3,'V2. Demand'!$B:$B,'V2. Demand'!D:D)</f>
-        <v>2000</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="str">
-        <v>Br</v>
+        <v>Ca(OH)2</v>
       </c>
       <c r="B4">
         <f>_xlfn.XLOOKUP($A4,'V2. Demand'!$B:$B,'V2. Demand'!D:D)</f>
-        <v>275</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="str">
-        <v>Ca(OH)2</v>
+        <v>HCl</v>
       </c>
       <c r="B5">
         <f>_xlfn.XLOOKUP($A5,'V2. Demand'!$B:$B,'V2. Demand'!D:D)</f>
-        <v>2470</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="str">
-        <v>HCl</v>
+        <v>Li</v>
       </c>
       <c r="B6">
         <f>_xlfn.XLOOKUP($A6,'V2. Demand'!$B:$B,'V2. Demand'!D:D)</f>
-        <v>1458</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="str">
-        <v>HF</v>
+        <v>Mg(OH)2</v>
       </c>
       <c r="B7">
         <f>_xlfn.XLOOKUP($A7,'V2. Demand'!$B:$B,'V2. Demand'!D:D)</f>
-        <v>320</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="str">
-        <v>Li</v>
+        <v>MgSO4</v>
       </c>
       <c r="B8">
         <f>_xlfn.XLOOKUP($A8,'V2. Demand'!$B:$B,'V2. Demand'!D:D)</f>
-        <v>3.75</v>
+        <v>72.900000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="str">
-        <v>Mg(OH)2</v>
+        <v>NaOH</v>
       </c>
       <c r="B9">
         <f>_xlfn.XLOOKUP($A9,'V2. Demand'!$B:$B,'V2. Demand'!D:D)</f>
-        <v>190</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="str">
-        <v>MgSO4</v>
+        <v>P2O5</v>
       </c>
       <c r="B10">
         <f>_xlfn.XLOOKUP($A10,'V2. Demand'!$B:$B,'V2. Demand'!D:D)</f>
-        <v>72.900000000000006</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="str">
-        <v>NaOH</v>
-      </c>
-      <c r="B11">
-        <f>_xlfn.XLOOKUP($A11,'V2. Demand'!$B:$B,'V2. Demand'!D:D)</f>
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="str">
-        <v>P2O5</v>
-      </c>
-      <c r="B12">
-        <f>_xlfn.XLOOKUP($A12,'V2. Demand'!$B:$B,'V2. Demand'!D:D)</f>
         <v>5700</v>
       </c>
     </row>

--- a/data/inputs/sw3_validation.xlsx
+++ b/data/inputs/sw3_validation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carolineadkins/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA10794F-870B-5242-8A25-AB5A38420F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE60838-792B-134C-88D5-949B5DA31DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17800" yWindow="-26680" windowWidth="28400" windowHeight="21000" activeTab="6" xr2:uid="{DD733A40-C352-434B-90DD-0C52971768EC}"/>
+    <workbookView xWindow="5340" yWindow="800" windowWidth="28400" windowHeight="21000" activeTab="3" xr2:uid="{DD733A40-C352-434B-90DD-0C52971768EC}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="12" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="288">
   <si>
     <t>Major End-Use Markets</t>
   </si>
@@ -1072,6 +1072,12 @@
   </si>
   <si>
     <t>Greenhouse Gas Emissions from Cement Production Facilities in 2023, by District</t>
+  </si>
+  <si>
+    <t>Mean Absolute Error (MAE)</t>
+  </si>
+  <si>
+    <t>Coefficient of Variation (Tiers 1-4)</t>
   </si>
 </sst>
 </file>
@@ -1190,7 +1196,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1224,6 +1230,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1322,7 +1334,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1377,7 +1389,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1438,6 +1449,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="10" fillId="7" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="7" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1789,352 +1811,352 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" s="38"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-      <c r="Z1" s="38"/>
+      <c r="A1" s="37"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
     </row>
     <row r="2" spans="1:26" ht="27">
-      <c r="A2" s="40"/>
-      <c r="B2" s="41" t="s">
+      <c r="A2" s="39"/>
+      <c r="B2" s="40" t="s">
         <v>258</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="40"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="39"/>
+      <c r="W2" s="39"/>
+      <c r="X2" s="39"/>
+      <c r="Y2" s="39"/>
+      <c r="Z2" s="39"/>
     </row>
     <row r="3" spans="1:26" ht="19">
-      <c r="A3" s="40"/>
-      <c r="B3" s="42" t="s">
+      <c r="A3" s="39"/>
+      <c r="B3" s="41" t="s">
         <v>259</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40"/>
-      <c r="X3" s="40"/>
-      <c r="Y3" s="40"/>
-      <c r="Z3" s="40"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
     </row>
     <row r="4" spans="1:26">
-      <c r="A4" s="40"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="40"/>
-      <c r="U4" s="40"/>
-      <c r="V4" s="40"/>
-      <c r="W4" s="40"/>
-      <c r="X4" s="40"/>
-      <c r="Y4" s="40"/>
-      <c r="Z4" s="40"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="39"/>
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39"/>
+      <c r="W4" s="39"/>
+      <c r="X4" s="39"/>
+      <c r="Y4" s="39"/>
+      <c r="Z4" s="39"/>
     </row>
     <row r="5" spans="1:26" ht="42" customHeight="1">
-      <c r="A5" s="40"/>
-      <c r="B5" s="61" t="s">
+      <c r="A5" s="39"/>
+      <c r="B5" s="60" t="s">
         <v>260</v>
       </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="40"/>
-      <c r="T5" s="40"/>
-      <c r="U5" s="40"/>
-      <c r="V5" s="40"/>
-      <c r="W5" s="40"/>
-      <c r="X5" s="40"/>
-      <c r="Y5" s="40"/>
-      <c r="Z5" s="40"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="39"/>
+      <c r="S5" s="39"/>
+      <c r="T5" s="39"/>
+      <c r="U5" s="39"/>
+      <c r="V5" s="39"/>
+      <c r="W5" s="39"/>
+      <c r="X5" s="39"/>
+      <c r="Y5" s="39"/>
+      <c r="Z5" s="39"/>
     </row>
     <row r="6" spans="1:26">
-      <c r="A6" s="40"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="40"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="40"/>
-      <c r="W6" s="40"/>
-      <c r="X6" s="40"/>
-      <c r="Y6" s="40"/>
-      <c r="Z6" s="40"/>
+      <c r="A6" s="39"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="W6" s="39"/>
+      <c r="X6" s="39"/>
+      <c r="Y6" s="39"/>
+      <c r="Z6" s="39"/>
     </row>
     <row r="7" spans="1:26">
-      <c r="A7" s="38"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="38"/>
-      <c r="Z7" s="38"/>
+      <c r="A7" s="37"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="37"/>
+      <c r="T7" s="37"/>
+      <c r="U7" s="37"/>
+      <c r="V7" s="37"/>
+      <c r="W7" s="37"/>
+      <c r="X7" s="37"/>
+      <c r="Y7" s="37"/>
+      <c r="Z7" s="37"/>
     </row>
     <row r="8" spans="1:26">
-      <c r="A8" s="40"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="40"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="40"/>
-      <c r="W8" s="40"/>
-      <c r="X8" s="40"/>
-      <c r="Y8" s="40"/>
-      <c r="Z8" s="40"/>
+      <c r="A8" s="39"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="39"/>
+      <c r="S8" s="39"/>
+      <c r="T8" s="39"/>
+      <c r="U8" s="39"/>
+      <c r="V8" s="39"/>
+      <c r="W8" s="39"/>
+      <c r="X8" s="39"/>
+      <c r="Y8" s="39"/>
+      <c r="Z8" s="39"/>
     </row>
     <row r="9" spans="1:26" ht="27">
-      <c r="A9" s="40"/>
+      <c r="A9" s="39"/>
       <c r="B9" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="40"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="40"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="40"/>
-      <c r="W9" s="40"/>
-      <c r="X9" s="40"/>
-      <c r="Y9" s="40"/>
-      <c r="Z9" s="40"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="39"/>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="39"/>
+      <c r="R9" s="39"/>
+      <c r="S9" s="39"/>
+      <c r="T9" s="39"/>
+      <c r="U9" s="39"/>
+      <c r="V9" s="39"/>
+      <c r="W9" s="39"/>
+      <c r="X9" s="39"/>
+      <c r="Y9" s="39"/>
+      <c r="Z9" s="39"/>
     </row>
     <row r="10" spans="1:26" ht="17">
-      <c r="A10" s="40"/>
-      <c r="B10" s="45" t="s">
+      <c r="A10" s="39"/>
+      <c r="B10" s="44" t="s">
         <v>257</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="45" t="s">
         <v>255</v>
       </c>
-      <c r="D10" s="47" t="s">
+      <c r="D10" s="46" t="s">
         <v>256</v>
       </c>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="40"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="40"/>
-      <c r="V10" s="40"/>
-      <c r="W10" s="40"/>
-      <c r="X10" s="40"/>
-      <c r="Y10" s="40"/>
-      <c r="Z10" s="40"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="39"/>
+      <c r="R10" s="39"/>
+      <c r="S10" s="39"/>
+      <c r="T10" s="39"/>
+      <c r="U10" s="39"/>
+      <c r="V10" s="39"/>
+      <c r="W10" s="39"/>
+      <c r="X10" s="39"/>
+      <c r="Y10" s="39"/>
+      <c r="Z10" s="39"/>
     </row>
     <row r="11" spans="1:26" ht="50" customHeight="1">
-      <c r="B11" s="62" t="s">
+      <c r="B11" s="61" t="s">
         <v>261</v>
       </c>
-      <c r="C11" s="54" t="s">
+      <c r="C11" s="53" t="s">
         <v>262</v>
       </c>
-      <c r="D11" s="49" t="s">
+      <c r="D11" s="48" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="50" customHeight="1">
-      <c r="B12" s="62"/>
-      <c r="C12" s="54" t="s">
+      <c r="B12" s="61"/>
+      <c r="C12" s="53" t="s">
         <v>263</v>
       </c>
-      <c r="D12" s="49" t="s">
+      <c r="D12" s="48" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="50" customHeight="1">
-      <c r="B13" s="62"/>
+      <c r="B13" s="61"/>
       <c r="C13" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="D13" s="49" t="s">
+      <c r="D13" s="48" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="50" customHeight="1">
-      <c r="B14" s="63" t="s">
+      <c r="B14" s="62" t="s">
         <v>268</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="48" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="50" customHeight="1">
-      <c r="B15" s="63"/>
+      <c r="B15" s="62"/>
       <c r="C15" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="D15" s="49" t="s">
+      <c r="D15" s="48" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="50" customHeight="1">
-      <c r="B16" s="64"/>
-      <c r="C16" s="55" t="s">
+      <c r="B16" s="63"/>
+      <c r="C16" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="D16" s="50" t="s">
+      <c r="D16" s="49" t="s">
         <v>274</v>
       </c>
     </row>
@@ -2209,12 +2231,12 @@
       <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:26" ht="39" customHeight="1">
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="64" t="s">
         <v>277</v>
       </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
     </row>
     <row r="6" spans="1:26" ht="19">
       <c r="B6" s="4"/>
@@ -2250,7 +2272,7 @@
       <c r="C10" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="58">
+      <c r="D10" s="57">
         <v>483000</v>
       </c>
       <c r="E10" s="20">
@@ -2264,7 +2286,7 @@
       <c r="C11" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="58">
+      <c r="D11" s="57">
         <v>103500</v>
       </c>
       <c r="E11" s="20">
@@ -2278,7 +2300,7 @@
       <c r="C12" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="58">
+      <c r="D12" s="57">
         <v>86300</v>
       </c>
       <c r="E12" s="20">
@@ -2292,7 +2314,7 @@
       <c r="C13" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="58">
+      <c r="D13" s="57">
         <v>77600</v>
       </c>
       <c r="E13" s="20">
@@ -2306,7 +2328,7 @@
       <c r="C14" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="59">
+      <c r="D14" s="58">
         <v>69000</v>
       </c>
       <c r="E14" s="25">
@@ -2537,8 +2559,8 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -2573,19 +2595,19 @@
       <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:25" ht="17">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="F5" s="52" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2760,7 +2782,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FA4F4B7-6F38-A946-832A-9F44F1650CE9}">
-  <dimension ref="A1:S269"/>
+  <dimension ref="A1:S270"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
@@ -2805,14 +2827,14 @@
       <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:19" ht="37" customHeight="1">
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="65" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
     </row>
     <row r="6" spans="1:19">
       <c r="B6" s="17"/>
@@ -2838,67 +2860,78 @@
       <c r="F8" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="15" t="s">
         <v>78</v>
+      </c>
+      <c r="H8" s="70" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="B9" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C9" s="35">
-        <f t="shared" ref="C9:C27" si="0">IF(ISERROR(_xlfn.XLOOKUP(B9,$H$36:$H$54,$J$36:$J$54)/$J$55), "", (_xlfn.XLOOKUP(B9,$H$36:$H$54,$J$36:$J$54)/$J$55))</f>
+      <c r="C9" s="66">
+        <f t="shared" ref="C9:C28" si="0">IF(ISERROR(_xlfn.XLOOKUP(B9,$H$37:$H$55,$J$37:$J$55)/$J$56), "–", (_xlfn.XLOOKUP(B9,$H$37:$H$55,$J$37:$J$55)/$J$56))</f>
         <v>2.3127272727272729E-2</v>
       </c>
       <c r="D9" s="35">
-        <f>_xlfn.XLOOKUP(B9,$H$92:$H$110,$I$92:$I$110)/$I$111</f>
+        <f>_xlfn.XLOOKUP(B9,$H$93:$H$111,$I$93:$I$111)/$I$112</f>
         <v>2.2233913580529313E-2</v>
       </c>
       <c r="E9" s="35">
-        <f>_xlfn.XLOOKUP(B9,$H$121:$H$139,$I$121:$I$139)/$I$140</f>
+        <f>_xlfn.XLOOKUP(B9,$H$122:$H$140,$I$122:$I$140)/$I$141</f>
         <v>2.1295163541192035E-2</v>
       </c>
       <c r="F9" s="35">
-        <f>_xlfn.XLOOKUP(B9,$H$218:$H$237,$I$218:$I$237)/$I$237</f>
+        <f>_xlfn.XLOOKUP(B9,$H$219:$H$238,$I$219:$I$238)/$I$238</f>
         <v>2.7143440335252313E-2</v>
       </c>
-      <c r="G9" s="7">
-        <f>_xlfn.XLOOKUP(B9,$H$247:$H$265,$I$247:$I$265)/$I$266</f>
+      <c r="G9" s="35">
+        <f>_xlfn.XLOOKUP(B9,$H$248:$H$266,$I$248:$I$266)/$I$267</f>
         <v>4.0404040404040407E-2</v>
+      </c>
+      <c r="H9" s="71">
+        <f>STDEV(D9:G9)/AVERAGE(D9:G9)</f>
+        <v>0.31707808408758864</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="B10" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="66">
         <f t="shared" si="0"/>
         <v>4.7181818181818179E-2</v>
       </c>
       <c r="D10" s="35">
-        <f t="shared" ref="D10:D27" si="1">_xlfn.XLOOKUP(B10,$H$92:$H$110,$I$92:$I$110)/$I$111</f>
+        <f t="shared" ref="D10:D28" si="1">_xlfn.XLOOKUP(B10,$H$93:$H$111,$I$93:$I$111)/$I$112</f>
         <v>3.9458334286433194E-2</v>
       </c>
       <c r="E10" s="35">
-        <f t="shared" ref="E10:E27" si="2">_xlfn.XLOOKUP(B10,$H$121:$H$139,$I$121:$I$139)/$I$140</f>
+        <f t="shared" ref="E10:E28" si="2">_xlfn.XLOOKUP(B10,$H$122:$H$140,$I$122:$I$140)/$I$141</f>
         <v>4.4032605681508151E-2</v>
       </c>
       <c r="F10" s="35">
-        <f t="shared" ref="F10:F27" si="3">_xlfn.XLOOKUP(B10,$H$218:$H$237,$I$218:$I$237)/$I$237</f>
+        <f t="shared" ref="F10:F28" si="3">_xlfn.XLOOKUP(B10,$H$219:$H$238,$I$219:$I$238)/$I$238</f>
         <v>4.8238342400586526E-2</v>
       </c>
-      <c r="G10" s="7">
-        <f t="shared" ref="G10:G27" si="4">_xlfn.XLOOKUP(B10,$H$247:$H$265,$I$247:$I$265)/$I$266</f>
+      <c r="G10" s="35">
+        <f t="shared" ref="G10:G28" si="4">_xlfn.XLOOKUP(B10,$H$248:$H$266,$I$248:$I$266)/$I$267</f>
         <v>7.0707070707070704E-2</v>
+      </c>
+      <c r="H10" s="71">
+        <f t="shared" ref="H10:H28" si="5">STDEV(D10:G10)/AVERAGE(D10:G10)</f>
+        <v>0.27406336422733096</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="B11" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C11" s="35" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="C11" s="66" t="str">
+        <f>IF(ISERROR(_xlfn.XLOOKUP(B11,$H$37:$H$55,$J$37:$J$55)/$J$56), "–", (_xlfn.XLOOKUP(B11,$H$37:$H$55,$J$37:$J$55)/$J$56))</f>
+        <v>–</v>
       </c>
       <c r="D11" s="35">
         <f t="shared" si="1"/>
@@ -2912,16 +2945,20 @@
         <f t="shared" si="3"/>
         <v>2.1086570745403193E-2</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="35">
         <f t="shared" si="4"/>
         <v>3.0303030303030304E-2</v>
+      </c>
+      <c r="H11" s="71">
+        <f t="shared" si="5"/>
+        <v>0.32056103086417709</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="B12" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="66">
         <f t="shared" si="0"/>
         <v>4.236363636363636E-2</v>
       </c>
@@ -2937,18 +2974,22 @@
         <f t="shared" si="3"/>
         <v>4.7313565888243675E-2</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="35">
         <f t="shared" si="4"/>
         <v>6.0606060606060608E-2</v>
+      </c>
+      <c r="H12" s="71">
+        <f t="shared" si="5"/>
+        <v>0.14365345262752549</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="B13" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C13" s="35" t="str">
+      <c r="C13" s="66" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>–</v>
       </c>
       <c r="D13" s="35">
         <f t="shared" si="1"/>
@@ -2962,18 +3003,22 @@
         <f t="shared" si="3"/>
         <v>4.7805113764173658E-2</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="35">
         <f t="shared" si="4"/>
         <v>3.0303030303030304E-2</v>
+      </c>
+      <c r="H13" s="71">
+        <f t="shared" si="5"/>
+        <v>0.23060372654753855</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="B14" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="35" t="str">
+      <c r="C14" s="66" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>–</v>
       </c>
       <c r="D14" s="35">
         <f t="shared" si="1"/>
@@ -2987,18 +3032,22 @@
         <f t="shared" si="3"/>
         <v>3.5699705904406437E-2</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="35">
         <f t="shared" si="4"/>
         <v>4.0404040404040407E-2</v>
+      </c>
+      <c r="H14" s="71">
+        <f t="shared" si="5"/>
+        <v>7.0357665200017294E-2</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="B15" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="35" t="str">
+      <c r="C15" s="66" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>–</v>
       </c>
       <c r="D15" s="35">
         <f t="shared" si="1"/>
@@ -3012,16 +3061,20 @@
         <f t="shared" si="3"/>
         <v>2.642694682118488E-2</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="35">
         <f t="shared" si="4"/>
         <v>2.0202020202020204E-2</v>
+      </c>
+      <c r="H15" s="71">
+        <f t="shared" si="5"/>
+        <v>0.21519961564863163</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="B16" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="66">
         <f t="shared" si="0"/>
         <v>0.10818181818181818</v>
       </c>
@@ -3037,16 +3090,20 @@
         <f t="shared" si="3"/>
         <v>9.3535728865524165E-2</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="35">
         <f t="shared" si="4"/>
         <v>5.0505050505050504E-2</v>
+      </c>
+      <c r="H16" s="71">
+        <f t="shared" si="5"/>
+        <v>0.30511775130324831</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="B17" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="66">
         <f t="shared" si="0"/>
         <v>4.8818181818181816E-2</v>
       </c>
@@ -3062,18 +3119,22 @@
         <f t="shared" si="3"/>
         <v>8.7812112072915713E-2</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="35">
         <f t="shared" si="4"/>
         <v>8.0808080808080815E-2</v>
+      </c>
+      <c r="H17" s="71">
+        <f t="shared" si="5"/>
+        <v>0.13799729680366252</v>
       </c>
     </row>
     <row r="18" spans="1:19">
       <c r="B18" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C18" s="35" t="str">
+      <c r="C18" s="66" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>–</v>
       </c>
       <c r="D18" s="35">
         <f t="shared" si="1"/>
@@ -3087,16 +3148,20 @@
         <f t="shared" si="3"/>
         <v>6.6067367052962206E-2</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="35">
         <f t="shared" si="4"/>
         <v>6.0606060606060608E-2</v>
+      </c>
+      <c r="H18" s="71">
+        <f t="shared" si="5"/>
+        <v>5.1392946872039817E-2</v>
       </c>
     </row>
     <row r="19" spans="1:19">
       <c r="B19" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="66">
         <f t="shared" si="0"/>
         <v>1.8727272727272728E-2</v>
       </c>
@@ -3112,18 +3177,22 @@
         <f t="shared" si="3"/>
         <v>4.7205258729140456E-2</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="35">
         <f t="shared" si="4"/>
         <v>3.0303030303030304E-2</v>
+      </c>
+      <c r="H19" s="71">
+        <f t="shared" si="5"/>
+        <v>0.20307926806952611</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="B20" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C20" s="35" t="str">
+      <c r="C20" s="66" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>–</v>
       </c>
       <c r="D20" s="35">
         <f t="shared" si="1"/>
@@ -3137,18 +3206,22 @@
         <f t="shared" si="3"/>
         <v>8.4346282981612772E-2</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="35">
         <f t="shared" si="4"/>
         <v>8.0808080808080815E-2</v>
+      </c>
+      <c r="H20" s="71">
+        <f t="shared" si="5"/>
+        <v>6.5504159670119105E-2</v>
       </c>
     </row>
     <row r="21" spans="1:19">
       <c r="B21" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="35" t="str">
+      <c r="C21" s="66" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>–</v>
       </c>
       <c r="D21" s="35">
         <f t="shared" si="1"/>
@@ -3162,16 +3235,20 @@
         <f t="shared" si="3"/>
         <v>3.0117721550625264E-2</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="35">
         <f t="shared" si="4"/>
         <v>4.0404040404040407E-2</v>
+      </c>
+      <c r="H21" s="71">
+        <f t="shared" si="5"/>
+        <v>0.19622501058620939</v>
       </c>
     </row>
     <row r="22" spans="1:19">
       <c r="B22" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="66">
         <f t="shared" si="0"/>
         <v>0.18454545454545454</v>
       </c>
@@ -3187,18 +3264,22 @@
         <f t="shared" si="3"/>
         <v>0.13130160211282274</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="35">
         <f t="shared" si="4"/>
         <v>0.12121212121212122</v>
+      </c>
+      <c r="H22" s="71">
+        <f t="shared" si="5"/>
+        <v>4.4106111859334038E-2</v>
       </c>
     </row>
     <row r="23" spans="1:19">
       <c r="B23" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C23" s="35" t="str">
+      <c r="C23" s="66" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>–</v>
       </c>
       <c r="D23" s="35">
         <f t="shared" si="1"/>
@@ -3212,18 +3293,22 @@
         <f t="shared" si="3"/>
         <v>2.8118204767181264E-2</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="35">
         <f t="shared" si="4"/>
         <v>4.0404040404040407E-2</v>
+      </c>
+      <c r="H23" s="71">
+        <f t="shared" si="5"/>
+        <v>0.14548281659884624</v>
       </c>
     </row>
     <row r="24" spans="1:19">
       <c r="B24" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C24" s="35" t="str">
+      <c r="C24" s="66" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>–</v>
       </c>
       <c r="D24" s="35">
         <f t="shared" si="1"/>
@@ -3237,18 +3322,22 @@
         <f t="shared" si="3"/>
         <v>3.561639270509627E-2</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="35">
         <f t="shared" si="4"/>
         <v>4.0404040404040407E-2</v>
+      </c>
+      <c r="H24" s="71">
+        <f t="shared" si="5"/>
+        <v>0.11331576900443195</v>
       </c>
     </row>
     <row r="25" spans="1:19">
       <c r="B25" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C25" s="35" t="str">
+      <c r="C25" s="66" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>–</v>
       </c>
       <c r="D25" s="35">
         <f t="shared" si="1"/>
@@ -3262,16 +3351,20 @@
         <f t="shared" si="3"/>
         <v>2.6668555099184362E-2</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="35">
         <f t="shared" si="4"/>
         <v>5.0505050505050504E-2</v>
+      </c>
+      <c r="H25" s="71">
+        <f t="shared" si="5"/>
+        <v>0.32494946257085133</v>
       </c>
     </row>
     <row r="26" spans="1:19">
       <c r="B26" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="66">
         <f t="shared" si="0"/>
         <v>0.11181818181818182</v>
       </c>
@@ -3287,542 +3380,570 @@
         <f t="shared" si="3"/>
         <v>9.4143915220488386E-2</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="35">
         <f t="shared" si="4"/>
         <v>7.0707070707070704E-2</v>
       </c>
+      <c r="H26" s="71">
+        <f t="shared" si="5"/>
+        <v>0.17876578277400851</v>
+      </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C27" s="36" t="str">
+      <c r="C27" s="66" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D27" s="36">
-        <f t="shared" si="1"/>
+        <v>–</v>
+      </c>
+      <c r="D27" s="35">
+        <f t="shared" ref="D27:D28" si="6">_xlfn.XLOOKUP(B27,$H$93:$H$111,$I$93:$I$111)/$I$112</f>
         <v>1.6675435185396985E-2</v>
       </c>
-      <c r="E27" s="36">
-        <f t="shared" si="2"/>
+      <c r="E27" s="35">
+        <f t="shared" ref="E27:E28" si="7">_xlfn.XLOOKUP(B27,$H$122:$H$140,$I$122:$I$140)/$I$141</f>
         <v>1.4223674060461395E-2</v>
       </c>
-      <c r="F27" s="36">
-        <f t="shared" si="3"/>
+      <c r="F27" s="35">
+        <f t="shared" ref="F27:F28" si="8">_xlfn.XLOOKUP(B27,$H$219:$H$238,$I$219:$I$238)/$I$238</f>
         <v>2.1353172983195726E-2</v>
       </c>
-      <c r="G27" s="10">
-        <f t="shared" si="4"/>
+      <c r="G27" s="35">
+        <f t="shared" ref="G27:G28" si="9">_xlfn.XLOOKUP(B27,$H$248:$H$266,$I$248:$I$266)/$I$267</f>
         <v>4.0404040404040407E-2</v>
       </c>
+      <c r="H27" s="71">
+        <f t="shared" si="5"/>
+        <v>0.51233327027563147</v>
+      </c>
     </row>
     <row r="28" spans="1:19">
-      <c r="B28" t="s">
-        <v>147</v>
+      <c r="B28" s="67" t="s">
+        <v>286</v>
+      </c>
+      <c r="C28" s="68" t="str">
+        <f t="shared" si="0"/>
+        <v>–</v>
+      </c>
+      <c r="D28" s="69" cm="1">
+        <f t="array" ref="D28">AVERAGE(IF(ISNUMBER($C$9:$C$27), ABS(D9:D27-$C$9:$C$27)))</f>
+        <v>1.4183702408258074E-2</v>
+      </c>
+      <c r="E28" s="69" cm="1">
+        <f t="array" ref="E28">AVERAGE(IF(ISNUMBER($C$9:$C$27), ABS(E9:E27-$C$9:$C$27)))</f>
+        <v>1.29232563020239E-2</v>
+      </c>
+      <c r="F28" s="69" cm="1">
+        <f t="array" ref="F28">AVERAGE(IF(ISNUMBER($C$9:$C$27), ABS(F9:F27-$C$9:$C$27)))</f>
+        <v>2.0382343244322018E-2</v>
+      </c>
+      <c r="G28" s="69" cm="1">
+        <f t="array" ref="G28">AVERAGE(IF(ISNUMBER($C$9:$C$27), ABS(G9:G27-$C$9:$C$27)))</f>
+        <v>3.3091414141414144E-2</v>
+      </c>
+      <c r="H28" s="72" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:19">
       <c r="B29" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="B30" t="s">
         <v>245</v>
       </c>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-    </row>
-    <row r="31" spans="1:19">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-    </row>
-    <row r="33" spans="2:10" ht="24">
-      <c r="B33" s="3" t="s">
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="55"/>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+    </row>
+    <row r="34" spans="2:10" ht="24">
+      <c r="B34" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="2:10" ht="19">
-      <c r="B34" s="26" t="s">
+    <row r="35" spans="2:10" ht="19">
+      <c r="B35" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="H34" s="26" t="s">
+      <c r="H35" s="26" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="35" spans="2:10" ht="19">
-      <c r="B35" s="14" t="s">
+    <row r="36" spans="2:10" ht="19">
+      <c r="B36" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C36" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="H35" s="14" t="s">
+      <c r="H36" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="I36" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="J35" s="16" t="s">
+      <c r="J36" s="16" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10">
-      <c r="B36" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" s="28">
-        <v>4660</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="I36" t="b" cm="1">
-        <f t="array" ref="I36">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H36," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
-        <v>1</v>
-      </c>
-      <c r="J36" s="28" cm="1">
-        <f t="array" ref="J36">IF(I36,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H36," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
-        <v>2544</v>
       </c>
     </row>
     <row r="37" spans="2:10">
       <c r="B37" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C37" s="28" t="s">
-        <v>128</v>
+        <v>79</v>
+      </c>
+      <c r="C37" s="28">
+        <v>4660</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="I37" t="b" cm="1">
-        <f t="array" ref="I37">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H37," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
+        <f t="array" ref="I37">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H37," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
         <v>1</v>
       </c>
       <c r="J37" s="28" cm="1">
-        <f t="array" ref="J37">IF(I37,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H37," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
-        <v>5190</v>
+        <f t="array" ref="J37">IF(I37,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H37," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
+        <v>2544</v>
       </c>
     </row>
     <row r="38" spans="2:10">
       <c r="B38" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C38" s="28" t="s">
         <v>128</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="I38" t="b" cm="1">
-        <f t="array" ref="I38">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H38," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="28" t="str" cm="1">
-        <f t="array" ref="J38">IF(I38,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H38," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
-        <v/>
+        <f t="array" ref="I38">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H38," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
+        <v>1</v>
+      </c>
+      <c r="J38" s="28" cm="1">
+        <f t="array" ref="J38">IF(I38,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H38," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
+        <v>5190</v>
       </c>
     </row>
     <row r="39" spans="2:10">
       <c r="B39" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C39" s="28">
-        <v>12300</v>
+        <v>81</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>128</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="I39" t="b" cm="1">
-        <f t="array" ref="I39">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H39," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
-        <v>1</v>
-      </c>
-      <c r="J39" s="28" cm="1">
-        <f t="array" ref="J39">IF(I39,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H39," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
-        <v>4660</v>
+        <f t="array" ref="I39">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H39," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="28" t="str" cm="1">
+        <f t="array" ref="J39">IF(I39,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H39," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="40" spans="2:10">
       <c r="B40" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C40" s="28">
-        <v>3140</v>
+        <v>12300</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I40" t="b" cm="1">
-        <f t="array" ref="I40">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H40," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="28" t="str" cm="1">
-        <f t="array" ref="J40">IF(I40,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H40," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
-        <v/>
+        <f t="array" ref="I40">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H40," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
+        <v>1</v>
+      </c>
+      <c r="J40" s="28" cm="1">
+        <f t="array" ref="J40">IF(I40,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H40," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
+        <v>4660</v>
       </c>
     </row>
     <row r="41" spans="2:10">
       <c r="B41" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C41" s="28">
+        <v>3140</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="I41" t="b" cm="1">
+        <f t="array" ref="I41">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H41," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
         <v>0</v>
       </c>
-      <c r="H41" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="I41" t="b" cm="1">
-        <f t="array" ref="I41">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H41," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
-        <v>0</v>
-      </c>
       <c r="J41" s="28" t="str" cm="1">
-        <f t="array" ref="J41">IF(I41,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H41," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
+        <f t="array" ref="J41">IF(I41,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H41," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" spans="2:10">
       <c r="B42" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C42" s="28">
         <v>0</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="I42" t="b" cm="1">
-        <f t="array" ref="I42">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H42," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
+        <f t="array" ref="I42">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H42," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
         <v>0</v>
       </c>
       <c r="J42" s="28" t="str" cm="1">
-        <f t="array" ref="J42">IF(I42,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H42," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
+        <f t="array" ref="J42">IF(I42,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H42," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" spans="2:10">
       <c r="B43" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C43" s="28">
-        <v>5370</v>
+        <v>0</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="I43" t="b" cm="1">
-        <f t="array" ref="I43">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H43," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
-        <v>1</v>
-      </c>
-      <c r="J43" s="28" cm="1">
-        <f t="array" ref="J43">IF(I43,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H43," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
-        <v>11900</v>
+        <f t="array" ref="I43">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H43," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="28" t="str" cm="1">
+        <f t="array" ref="J43">IF(I43,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H43," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="44" spans="2:10">
       <c r="B44" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C44" s="28">
-        <v>530</v>
+        <v>5370</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="I44" t="b" cm="1">
-        <f t="array" ref="I44">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H44," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
+        <f t="array" ref="I44">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H44," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
         <v>1</v>
       </c>
       <c r="J44" s="28" cm="1">
-        <f t="array" ref="J44">IF(I44,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H44," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
-        <v>5370</v>
+        <f t="array" ref="J44">IF(I44,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H44," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
+        <v>11900</v>
       </c>
     </row>
     <row r="45" spans="2:10">
       <c r="B45" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C45" s="28">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="I45" t="b" cm="1">
-        <f t="array" ref="I45">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H45," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
-        <v>0</v>
-      </c>
-      <c r="J45" s="28" t="str" cm="1">
-        <f t="array" ref="J45">IF(I45,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H45," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
-        <v/>
+        <f t="array" ref="I45">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H45," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
+        <v>1</v>
+      </c>
+      <c r="J45" s="28" cm="1">
+        <f t="array" ref="J45">IF(I45,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H45," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
+        <v>5370</v>
       </c>
     </row>
     <row r="46" spans="2:10">
       <c r="B46" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" s="28" t="s">
-        <v>128</v>
+        <v>88</v>
+      </c>
+      <c r="C46" s="28">
+        <v>0</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="I46" t="b" cm="1">
-        <f t="array" ref="I46">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H46," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
-        <v>1</v>
-      </c>
-      <c r="J46" s="28" cm="1">
-        <f t="array" ref="J46">IF(I46,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H46," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
-        <v>2060</v>
+        <f t="array" ref="I46">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H46," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="28" t="str" cm="1">
+        <f t="array" ref="J46">IF(I46,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H46," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="47" spans="2:10">
       <c r="B47" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" s="28">
-        <v>3520</v>
+        <v>89</v>
+      </c>
+      <c r="C47" s="28" t="s">
+        <v>128</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="I47" t="b" cm="1">
-        <f t="array" ref="I47">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H47," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
-        <v>0</v>
-      </c>
-      <c r="J47" s="28" t="str" cm="1">
-        <f t="array" ref="J47">IF(I47,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H47," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
-        <v/>
+        <f t="array" ref="I47">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H47," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
+        <v>1</v>
+      </c>
+      <c r="J47" s="28" cm="1">
+        <f t="array" ref="J47">IF(I47,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H47," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
+        <v>2060</v>
       </c>
     </row>
     <row r="48" spans="2:10">
       <c r="B48" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C48" s="28">
-        <v>2150</v>
+        <v>3520</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I48" t="b" cm="1">
-        <f t="array" ref="I48">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H48," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
+        <f t="array" ref="I48">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H48," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
         <v>0</v>
       </c>
       <c r="J48" s="28" t="str" cm="1">
-        <f t="array" ref="J48">IF(I48,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H48," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
+        <f t="array" ref="J48">IF(I48,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H48," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
         <v/>
       </c>
     </row>
     <row r="49" spans="2:10">
       <c r="B49" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C49" s="28" t="s">
-        <v>128</v>
+        <v>91</v>
+      </c>
+      <c r="C49" s="28">
+        <v>2150</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="I49" t="b" cm="1">
-        <f t="array" ref="I49">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H49," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
-        <v>1</v>
-      </c>
-      <c r="J49" s="28" cm="1">
-        <f t="array" ref="J49">IF(I49,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H49," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
-        <v>20300</v>
+        <f t="array" ref="I49">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H49," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="28" t="str" cm="1">
+        <f t="array" ref="J49">IF(I49,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H49," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="50" spans="2:10">
       <c r="B50" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C50" s="28">
-        <v>1770</v>
+        <v>92</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>128</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="I50" t="b" cm="1">
-        <f t="array" ref="I50">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H50," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
-        <v>0</v>
-      </c>
-      <c r="J50" s="28" t="str" cm="1">
-        <f t="array" ref="J50">IF(I50,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H50," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
-        <v/>
+        <f t="array" ref="I50">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H50," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
+        <v>1</v>
+      </c>
+      <c r="J50" s="28" cm="1">
+        <f t="array" ref="J50">IF(I50,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H50," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
+        <v>20300</v>
       </c>
     </row>
     <row r="51" spans="2:10">
       <c r="B51" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C51" s="28">
+        <v>1770</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I51" t="b" cm="1">
+        <f t="array" ref="I51">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H51," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
         <v>0</v>
       </c>
-      <c r="H51" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I51" t="b" cm="1">
-        <f t="array" ref="I51">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H51," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
-        <v>0</v>
-      </c>
       <c r="J51" s="28" t="str" cm="1">
-        <f t="array" ref="J51">IF(I51,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H51," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
+        <f t="array" ref="J51">IF(I51,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H51," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
         <v/>
       </c>
     </row>
     <row r="52" spans="2:10">
       <c r="B52" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C52" s="28">
-        <v>394</v>
+        <v>0</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="I52" t="b" cm="1">
-        <f t="array" ref="I52">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H52," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
+        <f t="array" ref="I52">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H52," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
         <v>0</v>
       </c>
       <c r="J52" s="28" t="str" cm="1">
-        <f t="array" ref="J52">IF(I52,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H52," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
+        <f t="array" ref="J52">IF(I52,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H52," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
         <v/>
       </c>
     </row>
     <row r="53" spans="2:10">
       <c r="B53" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C53" s="28">
-        <v>3660</v>
+        <v>394</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="I53" t="b" cm="1">
-        <f t="array" ref="I53">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H53," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
-        <v>1</v>
-      </c>
-      <c r="J53" s="28" cm="1">
-        <f t="array" ref="J53">IF(I53,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H53," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
-        <v>12300</v>
+        <f t="array" ref="I53">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H53," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="28" t="str" cm="1">
+        <f t="array" ref="J53">IF(I53,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H53," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="54" spans="2:10">
       <c r="B54" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C54" s="28">
-        <v>0</v>
+        <v>3660</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="I54" t="b" cm="1">
-        <f t="array" ref="I54">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H54," and ",","),",")),$B$36:$B$83,$C$36:$C$83)))</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="28" t="str" cm="1">
-        <f t="array" ref="J54">IF(I54,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H54," and ",","),",")),$B$36:$B$83,$C$36:$C$83)),"")</f>
-        <v/>
+        <f t="array" ref="I54">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H54," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
+        <v>1</v>
+      </c>
+      <c r="J54" s="28" cm="1">
+        <f t="array" ref="J54">IF(I54,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H54," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
+        <v>12300</v>
       </c>
     </row>
     <row r="55" spans="2:10">
       <c r="B55" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C55" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="H55" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="I55" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="J55" s="29">
-        <f>C84</f>
-        <v>110000</v>
+        <v>97</v>
+      </c>
+      <c r="C55" s="28">
+        <v>0</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I55" t="b" cm="1">
+        <f t="array" ref="I55">AND(ISNUMBER(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H55," and ",","),",")),$B$37:$B$84,$C$37:$C$84)))</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="28" t="str" cm="1">
+        <f t="array" ref="J55">IF(I55,SUM(_xlfn.XLOOKUP(TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H55," and ",","),",")),$B$37:$B$84,$C$37:$C$84)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="56" spans="2:10">
       <c r="B56" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C56" s="28">
-        <v>0</v>
-      </c>
-      <c r="H56" s="5" t="s">
-        <v>241</v>
+        <v>98</v>
+      </c>
+      <c r="C56" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I56" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="J56" s="29">
+        <f>C85</f>
+        <v>110000</v>
       </c>
     </row>
     <row r="57" spans="2:10">
       <c r="B57" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C57" s="28">
         <v>0</v>
       </c>
+      <c r="H57" s="5" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="58" spans="2:10">
       <c r="B58" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C58" s="28">
-        <v>11900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="2:10">
       <c r="B59" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C59" s="28">
-        <v>718</v>
+        <v>11900</v>
       </c>
     </row>
     <row r="60" spans="2:10">
       <c r="B60" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C60" s="28" t="s">
-        <v>128</v>
+        <v>102</v>
+      </c>
+      <c r="C60" s="28">
+        <v>718</v>
       </c>
     </row>
     <row r="61" spans="2:10">
       <c r="B61" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C61" s="28">
-        <v>599</v>
+        <v>103</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="62" spans="2:10">
       <c r="B62" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C62" s="28">
-        <v>0</v>
+        <v>599</v>
       </c>
     </row>
     <row r="63" spans="2:10">
       <c r="B63" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C63" s="28">
         <v>0</v>
@@ -3830,31 +3951,31 @@
     </row>
     <row r="64" spans="2:10">
       <c r="B64" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C64" s="28">
-        <v>514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="2:3">
       <c r="B65" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C65" s="28">
-        <v>2150</v>
+        <v>514</v>
       </c>
     </row>
     <row r="66" spans="2:3">
       <c r="B66" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C66" s="28">
-        <v>0</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="67" spans="2:3">
       <c r="B67" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C67" s="28">
         <v>0</v>
@@ -3862,63 +3983,63 @@
     </row>
     <row r="68" spans="2:3">
       <c r="B68" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C68" s="28">
-        <v>1140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="2:3">
       <c r="B69" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C69" s="28">
-        <v>1890</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="70" spans="2:3">
       <c r="B70" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C70" s="28" t="s">
-        <v>128</v>
+        <v>112</v>
+      </c>
+      <c r="C70" s="28">
+        <v>1890</v>
       </c>
     </row>
     <row r="71" spans="2:3">
       <c r="B71" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C71" s="28">
-        <v>5190</v>
+        <v>113</v>
+      </c>
+      <c r="C71" s="28" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="72" spans="2:3">
       <c r="B72" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C72" s="28">
-        <v>0</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="73" spans="2:3">
       <c r="B73" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C73" s="28">
-        <v>2060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="2:3">
       <c r="B74" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C74" s="28" t="s">
-        <v>128</v>
+        <v>116</v>
+      </c>
+      <c r="C74" s="28">
+        <v>2060</v>
       </c>
     </row>
     <row r="75" spans="2:3">
       <c r="B75" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C75" s="28" t="s">
         <v>128</v>
@@ -3926,1105 +4047,1102 @@
     </row>
     <row r="76" spans="2:3">
       <c r="B76" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C76" s="28">
-        <v>20300</v>
+        <v>118</v>
+      </c>
+      <c r="C76" s="28" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="77" spans="2:3">
       <c r="B77" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C77" s="28" t="s">
-        <v>128</v>
+        <v>119</v>
+      </c>
+      <c r="C77" s="28">
+        <v>20300</v>
       </c>
     </row>
     <row r="78" spans="2:3">
       <c r="B78" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C78" s="28">
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="C78" s="28" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="79" spans="2:3">
       <c r="B79" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C79" s="28">
-        <v>1460</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="2:3">
       <c r="B80" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C80" s="28">
-        <v>637</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="81" spans="1:19">
       <c r="B81" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C81" s="28" t="s">
-        <v>128</v>
+        <v>123</v>
+      </c>
+      <c r="C81" s="28">
+        <v>637</v>
       </c>
     </row>
     <row r="82" spans="1:19">
       <c r="B82" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C82" s="28">
-        <v>0</v>
+        <v>124</v>
+      </c>
+      <c r="C82" s="28" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="83" spans="1:19">
       <c r="B83" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C83" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19">
+      <c r="B84" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C83" s="28" t="s">
+      <c r="C84" s="28" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="84" spans="1:19">
-      <c r="B84" s="8" t="s">
+    <row r="85" spans="1:19">
+      <c r="B85" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C84" s="37">
+      <c r="C85" s="36">
         <v>110000</v>
       </c>
     </row>
-    <row r="85" spans="1:19">
-      <c r="B85" s="12" t="s">
+    <row r="86" spans="1:19">
+      <c r="B86" s="12" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="87" spans="1:19">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
-      <c r="K87" s="1"/>
-      <c r="L87" s="1"/>
-      <c r="M87" s="1"/>
-      <c r="N87" s="1"/>
-      <c r="O87" s="1"/>
-      <c r="P87" s="1"/>
-      <c r="Q87" s="1"/>
-      <c r="R87" s="1"/>
-      <c r="S87" s="1"/>
-    </row>
-    <row r="89" spans="1:19" ht="24">
-      <c r="B89" s="3" t="s">
+    <row r="88" spans="1:19">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1"/>
+      <c r="N88" s="1"/>
+      <c r="O88" s="1"/>
+      <c r="P88" s="1"/>
+      <c r="Q88" s="1"/>
+      <c r="R88" s="1"/>
+      <c r="S88" s="1"/>
+    </row>
+    <row r="90" spans="1:19" ht="24">
+      <c r="B90" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="90" spans="1:19" ht="19">
-      <c r="B90" s="26" t="s">
+    <row r="91" spans="1:19" ht="19">
+      <c r="B91" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="H90" s="26" t="s">
+      <c r="H91" s="26" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="91" spans="1:19">
-      <c r="B91" s="14" t="s">
+    <row r="92" spans="1:19">
+      <c r="B92" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C91" s="16" t="s">
+      <c r="C92" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="H91" s="14" t="s">
+      <c r="H92" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="I91" s="16" t="s">
+      <c r="I92" s="16" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19">
-      <c r="B92" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C92" s="31">
-        <v>1944</v>
-      </c>
-      <c r="H92" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="I92" s="60">
-        <f>SUMIF($B$92:$B$113,H92,$C$92:$C$113)</f>
-        <v>1944</v>
       </c>
     </row>
     <row r="93" spans="1:19">
       <c r="B93" s="18" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="C93" s="31">
-        <v>3450</v>
+        <v>1944</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I93" s="60">
-        <f t="shared" ref="I93:I110" si="5">SUMIF($B$92:$B$113,H93,$C$92:$C$113)</f>
-        <v>3450</v>
+        <v>138</v>
+      </c>
+      <c r="I93" s="59">
+        <f>SUMIF($B$93:$B$114,H93,$C$93:$C$114)</f>
+        <v>1944</v>
       </c>
     </row>
     <row r="94" spans="1:19">
       <c r="B94" s="18" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C94" s="31">
-        <v>1329</v>
+        <v>3450</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I94" s="60">
-        <f t="shared" si="5"/>
-        <v>1329</v>
+        <v>114</v>
+      </c>
+      <c r="I94" s="59">
+        <f t="shared" ref="I94:I111" si="10">SUMIF($B$93:$B$114,H94,$C$93:$C$114)</f>
+        <v>3450</v>
       </c>
     </row>
     <row r="95" spans="1:19">
       <c r="B95" s="18" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="C95" s="31">
-        <v>3842</v>
+        <v>1329</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="I95" s="60">
-        <f t="shared" si="5"/>
-        <v>3842</v>
+        <v>89</v>
+      </c>
+      <c r="I95" s="59">
+        <f t="shared" si="10"/>
+        <v>1329</v>
       </c>
     </row>
     <row r="96" spans="1:19">
       <c r="B96" s="18" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C96" s="31">
-        <v>4778</v>
-      </c>
-      <c r="H96" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="I96" s="60">
-        <f t="shared" si="5"/>
-        <v>4778</v>
+        <v>3842</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="I96" s="59">
+        <f t="shared" si="10"/>
+        <v>3842</v>
       </c>
     </row>
     <row r="97" spans="2:9">
       <c r="B97" s="18" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="C97" s="31">
-        <v>3588</v>
-      </c>
-      <c r="H97" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="I97" s="60">
-        <f t="shared" si="5"/>
-        <v>3588</v>
+        <v>4778</v>
+      </c>
+      <c r="H97" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="I97" s="59">
+        <f t="shared" si="10"/>
+        <v>4778</v>
       </c>
     </row>
     <row r="98" spans="2:9">
       <c r="B98" s="18" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="C98" s="31">
-        <v>2778</v>
+        <v>3588</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I98" s="60">
-        <f t="shared" si="5"/>
-        <v>2778</v>
+        <v>137</v>
+      </c>
+      <c r="I98" s="59">
+        <f t="shared" si="10"/>
+        <v>3588</v>
       </c>
     </row>
     <row r="99" spans="2:9">
       <c r="B99" s="18" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C99" s="31">
-        <v>9860</v>
+        <v>2778</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="I99" s="60">
-        <f t="shared" si="5"/>
-        <v>9860</v>
+        <v>92</v>
+      </c>
+      <c r="I99" s="59">
+        <f t="shared" si="10"/>
+        <v>2778</v>
       </c>
     </row>
     <row r="100" spans="2:9">
       <c r="B100" s="18" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C100" s="31">
-        <v>6371</v>
+        <v>9860</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="I100" s="60">
-        <f t="shared" si="5"/>
-        <v>6371</v>
+        <v>101</v>
+      </c>
+      <c r="I100" s="59">
+        <f t="shared" si="10"/>
+        <v>9860</v>
       </c>
     </row>
     <row r="101" spans="2:9">
       <c r="B101" s="18" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="C101" s="31">
-        <v>6000</v>
+        <v>6371</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I101" s="60">
-        <f t="shared" si="5"/>
-        <v>6000</v>
+        <v>86</v>
+      </c>
+      <c r="I101" s="59">
+        <f t="shared" si="10"/>
+        <v>6371</v>
       </c>
     </row>
     <row r="102" spans="2:9">
       <c r="B102" s="18" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C102" s="31">
-        <v>2931</v>
+        <v>6000</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="I102" s="60">
-        <f t="shared" si="5"/>
-        <v>2931</v>
+        <v>135</v>
+      </c>
+      <c r="I102" s="59">
+        <f t="shared" si="10"/>
+        <v>6000</v>
       </c>
     </row>
     <row r="103" spans="2:9">
       <c r="B103" s="18" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C103" s="31">
-        <v>7893</v>
+        <v>2931</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="I103" s="60">
-        <f t="shared" si="5"/>
-        <v>7893</v>
+        <v>116</v>
+      </c>
+      <c r="I103" s="59">
+        <f t="shared" si="10"/>
+        <v>2931</v>
       </c>
     </row>
     <row r="104" spans="2:9">
       <c r="B104" s="18" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C104" s="31">
-        <v>2234</v>
+        <v>7893</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I104" s="60">
-        <f t="shared" si="5"/>
-        <v>2234</v>
+        <v>131</v>
+      </c>
+      <c r="I104" s="59">
+        <f t="shared" si="10"/>
+        <v>7893</v>
       </c>
     </row>
     <row r="105" spans="2:9">
       <c r="B105" s="18" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C105" s="31">
-        <v>6150</v>
+        <v>2234</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="I105" s="60">
-        <f>SUM(C105:C106)</f>
-        <v>11740</v>
+        <v>133</v>
+      </c>
+      <c r="I105" s="59">
+        <f t="shared" si="10"/>
+        <v>2234</v>
       </c>
     </row>
     <row r="106" spans="2:9">
       <c r="B106" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C106" s="31">
-        <v>5590</v>
+        <v>6150</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="I106" s="60">
-        <f t="shared" si="5"/>
-        <v>3037</v>
+        <v>119</v>
+      </c>
+      <c r="I106" s="59">
+        <f>SUM(C106:C107)</f>
+        <v>11740</v>
       </c>
     </row>
     <row r="107" spans="2:9">
       <c r="B107" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C107" s="31">
+        <v>5590</v>
+      </c>
+      <c r="H107" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C107" s="31">
+      <c r="I107" s="59">
+        <f t="shared" si="10"/>
         <v>3037</v>
-      </c>
-      <c r="H107" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I107" s="60">
-        <f t="shared" si="5"/>
-        <v>2811</v>
       </c>
     </row>
     <row r="108" spans="2:9">
       <c r="B108" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="C108" s="31">
+        <v>3037</v>
+      </c>
+      <c r="H108" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C108" s="31">
+      <c r="I108" s="59">
+        <f t="shared" si="10"/>
         <v>2811</v>
-      </c>
-      <c r="H108" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="I108" s="60">
-        <f t="shared" si="5"/>
-        <v>2450</v>
       </c>
     </row>
     <row r="109" spans="2:9">
       <c r="B109" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C109" s="31">
+        <v>2811</v>
+      </c>
+      <c r="H109" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C109" s="31">
+      <c r="I109" s="59">
+        <f t="shared" si="10"/>
         <v>2450</v>
-      </c>
-      <c r="H109" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="I109" s="60">
-        <f t="shared" si="5"/>
-        <v>8940</v>
       </c>
     </row>
     <row r="110" spans="2:9">
       <c r="B110" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C110" s="31">
-        <v>0</v>
+        <v>2450</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="I110" s="60">
-        <f t="shared" si="5"/>
-        <v>1458</v>
+        <v>82</v>
+      </c>
+      <c r="I110" s="59">
+        <f t="shared" si="10"/>
+        <v>8940</v>
       </c>
     </row>
     <row r="111" spans="2:9">
       <c r="B111" s="18" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="C111" s="31">
-        <v>8940</v>
-      </c>
-      <c r="H111" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="I111" s="37">
-        <f>SUM(I92:I110)</f>
-        <v>87434</v>
+        <v>0</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I111" s="59">
+        <f t="shared" si="10"/>
+        <v>1458</v>
       </c>
     </row>
     <row r="112" spans="2:9">
       <c r="B112" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C112" s="31">
+        <v>8940</v>
+      </c>
+      <c r="H112" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I112" s="36">
+        <f>SUM(I93:I111)</f>
+        <v>87434</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19">
+      <c r="B113" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C112" s="31">
+      <c r="C113" s="31">
         <v>1458</v>
       </c>
     </row>
-    <row r="113" spans="1:19">
-      <c r="B113" s="32" t="s">
+    <row r="114" spans="1:19">
+      <c r="B114" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="C113" s="33">
-        <f>SUM(C92:C112)</f>
+      <c r="C114" s="33">
+        <f>SUM(C93:C113)</f>
         <v>87434</v>
       </c>
     </row>
-    <row r="114" spans="1:19">
-      <c r="B114" s="13" t="s">
+    <row r="115" spans="1:19">
+      <c r="B115" s="13" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="115" spans="1:19">
-      <c r="B115" s="19"/>
-    </row>
     <row r="116" spans="1:19">
-      <c r="A116" s="1"/>
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
-      <c r="E116" s="1"/>
-      <c r="F116" s="1"/>
-      <c r="G116" s="1"/>
-      <c r="H116" s="1"/>
-      <c r="I116" s="1"/>
-      <c r="J116" s="1"/>
-      <c r="K116" s="1"/>
-      <c r="L116" s="1"/>
-      <c r="M116" s="1"/>
-      <c r="N116" s="1"/>
-      <c r="O116" s="1"/>
-      <c r="P116" s="1"/>
-      <c r="Q116" s="1"/>
-      <c r="R116" s="1"/>
-      <c r="S116" s="1"/>
-    </row>
-    <row r="118" spans="1:19" ht="24">
-      <c r="B118" s="3" t="s">
+      <c r="B116" s="19"/>
+    </row>
+    <row r="117" spans="1:19">
+      <c r="A117" s="1"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
+      <c r="K117" s="1"/>
+      <c r="L117" s="1"/>
+      <c r="M117" s="1"/>
+      <c r="N117" s="1"/>
+      <c r="O117" s="1"/>
+      <c r="P117" s="1"/>
+      <c r="Q117" s="1"/>
+      <c r="R117" s="1"/>
+      <c r="S117" s="1"/>
+    </row>
+    <row r="119" spans="1:19" ht="24">
+      <c r="B119" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="119" spans="1:19" ht="19">
-      <c r="B119" s="26" t="s">
+    <row r="120" spans="1:19" ht="19">
+      <c r="B120" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="H119" s="26" t="s">
+      <c r="H120" s="26" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="120" spans="1:19" ht="18">
-      <c r="B120" s="14" t="s">
+    <row r="121" spans="1:19" ht="18">
+      <c r="B121" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="C120" s="15" t="s">
+      <c r="C121" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="D120" s="16" t="s">
+      <c r="D121" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="H120" s="14" t="s">
+      <c r="H121" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="I120" s="16" t="s">
+      <c r="I121" s="16" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="121" spans="1:19">
-      <c r="B121" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C121" t="s">
-        <v>119</v>
-      </c>
-      <c r="D121" s="60">
-        <v>787292</v>
-      </c>
-      <c r="H121" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="I121" s="60" cm="1">
-        <f t="array" ref="I121">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H121," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>1419236</v>
       </c>
     </row>
     <row r="122" spans="1:19">
       <c r="B122" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C122" t="s">
-        <v>86</v>
-      </c>
-      <c r="D122" s="60">
-        <v>873429</v>
+        <v>119</v>
+      </c>
+      <c r="D122" s="59">
+        <v>787292</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I122" s="60" cm="1">
-        <f t="array" ref="I122">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H122," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>2934594</v>
+        <v>138</v>
+      </c>
+      <c r="I122" s="59" cm="1">
+        <f t="array" ref="I122">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H122," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>1419236</v>
       </c>
     </row>
     <row r="123" spans="1:19">
       <c r="B123" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C123" t="s">
-        <v>116</v>
-      </c>
-      <c r="D123" s="60">
-        <v>617861</v>
+        <v>86</v>
+      </c>
+      <c r="D123" s="59">
+        <v>873429</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I123" s="60" cm="1">
-        <f t="array" ref="I123">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H123," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>1142298</v>
+        <v>114</v>
+      </c>
+      <c r="I123" s="59" cm="1">
+        <f t="array" ref="I123">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H123," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>2934594</v>
       </c>
     </row>
     <row r="124" spans="1:19">
       <c r="B124" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C124" t="s">
-        <v>79</v>
-      </c>
-      <c r="D124" s="60">
-        <v>1058822</v>
+        <v>116</v>
+      </c>
+      <c r="D124" s="59">
+        <v>617861</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="I124" s="60" cm="1">
-        <f t="array" ref="I124">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H124," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>3285382</v>
+        <v>89</v>
+      </c>
+      <c r="I124" s="59" cm="1">
+        <f t="array" ref="I124">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H124," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>1142298</v>
       </c>
     </row>
     <row r="125" spans="1:19">
       <c r="B125" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C125" t="s">
-        <v>124</v>
-      </c>
-      <c r="D125" s="60">
-        <v>846192</v>
+        <v>79</v>
+      </c>
+      <c r="D125" s="59">
+        <v>1058822</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="I125" s="60" cm="1">
-        <f t="array" ref="I125">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H125," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>3198425</v>
+        <v>136</v>
+      </c>
+      <c r="I125" s="59" cm="1">
+        <f t="array" ref="I125">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H125," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>3285382</v>
       </c>
     </row>
     <row r="126" spans="1:19">
       <c r="B126" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C126" t="s">
-        <v>114</v>
-      </c>
-      <c r="D126" s="60">
-        <v>184561</v>
+        <v>124</v>
+      </c>
+      <c r="D126" s="59">
+        <v>846192</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="I126" s="60" cm="1">
-        <f t="array" ref="I126">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H126," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>2798493</v>
+        <v>98</v>
+      </c>
+      <c r="I126" s="59" cm="1">
+        <f t="array" ref="I126">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H126," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>3198425</v>
       </c>
     </row>
     <row r="127" spans="1:19">
       <c r="B127" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C127" t="s">
-        <v>92</v>
-      </c>
-      <c r="D127" s="60">
-        <v>1299990</v>
+        <v>114</v>
+      </c>
+      <c r="D127" s="59">
+        <v>184561</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I127" s="60" cm="1">
-        <f t="array" ref="I127">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H127," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>2239671</v>
+        <v>137</v>
+      </c>
+      <c r="I127" s="59" cm="1">
+        <f t="array" ref="I127">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H127," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>2798493</v>
       </c>
     </row>
     <row r="128" spans="1:19">
       <c r="B128" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C128" t="s">
-        <v>119</v>
-      </c>
-      <c r="D128" s="60">
-        <v>642168</v>
+        <v>92</v>
+      </c>
+      <c r="D128" s="59">
+        <v>1299990</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="I128" s="60" cm="1">
-        <f t="array" ref="I128">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H128," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>6864697</v>
+        <v>92</v>
+      </c>
+      <c r="I128" s="59" cm="1">
+        <f t="array" ref="I128">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H128," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>2239671</v>
       </c>
     </row>
     <row r="129" spans="2:9">
       <c r="B129" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C129" t="s">
-        <v>113</v>
-      </c>
-      <c r="D129" s="60">
-        <v>580299</v>
+        <v>119</v>
+      </c>
+      <c r="D129" s="59">
+        <v>642168</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="I129" s="60" cm="1">
-        <f t="array" ref="I129">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H129," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>4223240</v>
+        <v>101</v>
+      </c>
+      <c r="I129" s="59" cm="1">
+        <f t="array" ref="I129">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H129," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>6864697</v>
       </c>
     </row>
     <row r="130" spans="2:9">
       <c r="B130" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C130" t="s">
-        <v>120</v>
-      </c>
-      <c r="D130" s="60">
-        <v>548943</v>
+        <v>113</v>
+      </c>
+      <c r="D130" s="59">
+        <v>580299</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I130" s="60" cm="1">
-        <f t="array" ref="I130">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H130," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>4368519</v>
+        <v>86</v>
+      </c>
+      <c r="I130" s="59" cm="1">
+        <f t="array" ref="I130">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H130," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>4223240</v>
       </c>
     </row>
     <row r="131" spans="2:9">
       <c r="B131" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C131" t="s">
-        <v>103</v>
-      </c>
-      <c r="D131" s="60">
-        <v>612375</v>
+        <v>120</v>
+      </c>
+      <c r="D131" s="59">
+        <v>548943</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="I131" s="60" cm="1">
-        <f t="array" ref="I131">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H131," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>2322955</v>
+        <v>135</v>
+      </c>
+      <c r="I131" s="59" cm="1">
+        <f t="array" ref="I131">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H131," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>4368519</v>
       </c>
     </row>
     <row r="132" spans="2:9">
       <c r="B132" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C132" t="s">
-        <v>102</v>
-      </c>
-      <c r="D132" s="60">
-        <v>323958</v>
+        <v>103</v>
+      </c>
+      <c r="D132" s="59">
+        <v>612375</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="I132" s="60" cm="1">
-        <f t="array" ref="I132">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H132," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>6230375</v>
+        <v>116</v>
+      </c>
+      <c r="I132" s="59" cm="1">
+        <f t="array" ref="I132">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H132," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>2322955</v>
       </c>
     </row>
     <row r="133" spans="2:9">
       <c r="B133" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C133" t="s">
-        <v>123</v>
-      </c>
-      <c r="D133" s="60">
-        <v>367651</v>
+        <v>102</v>
+      </c>
+      <c r="D133" s="59">
+        <v>323958</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I133" s="60" cm="1">
-        <f t="array" ref="I133">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H133," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>2065476</v>
+        <v>131</v>
+      </c>
+      <c r="I133" s="59" cm="1">
+        <f t="array" ref="I133">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H133," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>6230375</v>
       </c>
     </row>
     <row r="134" spans="2:9">
       <c r="B134" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C134" t="s">
-        <v>81</v>
-      </c>
-      <c r="D134" s="60">
-        <v>884375</v>
+        <v>123</v>
+      </c>
+      <c r="D134" s="59">
+        <v>367651</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="I134" s="60" cm="1">
-        <f t="array" ref="I134">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H134," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>8749623</v>
+        <v>133</v>
+      </c>
+      <c r="I134" s="59" cm="1">
+        <f t="array" ref="I134">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H134," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>2065476</v>
       </c>
     </row>
     <row r="135" spans="2:9">
       <c r="B135" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C135" t="s">
-        <v>86</v>
-      </c>
-      <c r="D135" s="60">
-        <v>746907</v>
+        <v>81</v>
+      </c>
+      <c r="D135" s="59">
+        <v>884375</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="I135" s="60" cm="1">
-        <f t="array" ref="I135">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H135," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>2345226</v>
+        <v>119</v>
+      </c>
+      <c r="I135" s="59" cm="1">
+        <f t="array" ref="I135">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H135," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>8749623</v>
       </c>
     </row>
     <row r="136" spans="2:9">
       <c r="B136" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C136" t="s">
-        <v>82</v>
-      </c>
-      <c r="D136" s="60">
-        <v>991489</v>
+        <v>86</v>
+      </c>
+      <c r="D136" s="59">
+        <v>746907</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I136" s="60" cm="1">
-        <f t="array" ref="I136">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H136," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>2126767</v>
+        <v>132</v>
+      </c>
+      <c r="I136" s="59" cm="1">
+        <f t="array" ref="I136">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H136," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>2345226</v>
       </c>
     </row>
     <row r="137" spans="2:9">
       <c r="B137" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C137" t="s">
         <v>82</v>
       </c>
-      <c r="D137" s="60">
-        <v>1424150</v>
+      <c r="D137" s="59">
+        <v>991489</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="I137" s="60" cm="1">
-        <f t="array" ref="I137">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H137," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>2087707</v>
+        <v>134</v>
+      </c>
+      <c r="I137" s="59" cm="1">
+        <f t="array" ref="I137">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H137," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>2126767</v>
       </c>
     </row>
     <row r="138" spans="2:9">
       <c r="B138" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C138" t="s">
-        <v>80</v>
-      </c>
-      <c r="D138" s="60">
-        <v>789422</v>
+        <v>82</v>
+      </c>
+      <c r="D138" s="59">
+        <v>1424150</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="I138" s="60" cm="1">
-        <f t="array" ref="I138">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H138," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>7295297</v>
+        <v>140</v>
+      </c>
+      <c r="I138" s="59" cm="1">
+        <f t="array" ref="I138">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H138," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>2087707</v>
       </c>
     </row>
     <row r="139" spans="2:9">
       <c r="B139" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C139" t="s">
+        <v>80</v>
+      </c>
+      <c r="D139" s="59">
+        <v>789422</v>
+      </c>
+      <c r="H139" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D139" s="60">
-        <v>372759</v>
-      </c>
-      <c r="H139" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="I139" s="60" cm="1">
-        <f t="array" ref="I139">SUMPRODUCT(ISNUMBER(MATCH($C$121:$C$210,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H139," and ",","),",")),0))*$D$121:$D$210)</f>
-        <v>947950</v>
+      <c r="I139" s="59" cm="1">
+        <f t="array" ref="I139">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H139," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>7295297</v>
       </c>
     </row>
     <row r="140" spans="2:9">
       <c r="B140" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C140" t="s">
-        <v>119</v>
-      </c>
-      <c r="D140" s="60">
-        <v>492032</v>
-      </c>
-      <c r="H140" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="I140" s="37">
-        <f>SUM(D121:D210)</f>
-        <v>66645931</v>
+        <v>82</v>
+      </c>
+      <c r="D140" s="59">
+        <v>372759</v>
+      </c>
+      <c r="H140" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I140" s="59" cm="1">
+        <f t="array" ref="I140">SUMPRODUCT(ISNUMBER(MATCH($C$122:$C$211,TRIM(_xlfn.TEXTSPLIT(SUBSTITUTE(H140," and ",","),",")),0))*$D$122:$D$211)</f>
+        <v>947950</v>
       </c>
     </row>
     <row r="141" spans="2:9">
       <c r="B141" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C141" t="s">
-        <v>118</v>
-      </c>
-      <c r="D141" s="60">
-        <v>441463</v>
+        <v>119</v>
+      </c>
+      <c r="D141" s="59">
+        <v>492032</v>
+      </c>
+      <c r="H141" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I141" s="36">
+        <f>SUM(D122:D211)</f>
+        <v>66645931</v>
       </c>
     </row>
     <row r="142" spans="2:9">
       <c r="B142" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C142" t="s">
-        <v>82</v>
-      </c>
-      <c r="D142" s="60">
-        <v>1951045</v>
+        <v>118</v>
+      </c>
+      <c r="D142" s="59">
+        <v>441463</v>
       </c>
     </row>
     <row r="143" spans="2:9">
       <c r="B143" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C143" t="s">
-        <v>83</v>
-      </c>
-      <c r="D143" s="60">
-        <v>243722</v>
+        <v>82</v>
+      </c>
+      <c r="D143" s="59">
+        <v>1951045</v>
       </c>
     </row>
     <row r="144" spans="2:9">
       <c r="B144" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C144" t="s">
-        <v>119</v>
-      </c>
-      <c r="D144" s="60">
-        <v>1122560</v>
+        <v>83</v>
+      </c>
+      <c r="D144" s="59">
+        <v>243722</v>
       </c>
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C145" t="s">
-        <v>86</v>
-      </c>
-      <c r="D145" s="60">
-        <v>581354</v>
+        <v>119</v>
+      </c>
+      <c r="D145" s="59">
+        <v>1122560</v>
       </c>
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C146" t="s">
-        <v>87</v>
-      </c>
-      <c r="D146" s="60">
-        <v>405369</v>
+        <v>86</v>
+      </c>
+      <c r="D146" s="59">
+        <v>581354</v>
       </c>
     </row>
     <row r="147" spans="2:4">
       <c r="B147" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C147" t="s">
-        <v>79</v>
-      </c>
-      <c r="D147" s="60">
-        <v>520546</v>
+        <v>87</v>
+      </c>
+      <c r="D147" s="59">
+        <v>405369</v>
       </c>
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C148" t="s">
-        <v>112</v>
-      </c>
-      <c r="D148" s="60">
-        <v>494937</v>
+        <v>79</v>
+      </c>
+      <c r="D148" s="59">
+        <v>520546</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C149" t="s">
-        <v>101</v>
-      </c>
-      <c r="D149" s="60">
-        <v>780363</v>
+        <v>112</v>
+      </c>
+      <c r="D149" s="59">
+        <v>494937</v>
       </c>
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C150" t="s">
         <v>101</v>
       </c>
-      <c r="D150" s="60">
-        <v>548811</v>
+      <c r="D150" s="59">
+        <v>780363</v>
       </c>
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C151" t="s">
-        <v>91</v>
-      </c>
-      <c r="D151" s="60">
-        <v>841277</v>
+        <v>101</v>
+      </c>
+      <c r="D151" s="59">
+        <v>548811</v>
       </c>
     </row>
     <row r="152" spans="2:4">
       <c r="B152" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C152" t="s">
-        <v>95</v>
-      </c>
-      <c r="D152" s="60">
-        <v>236953</v>
+        <v>91</v>
+      </c>
+      <c r="D152" s="59">
+        <v>841277</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C153" t="s">
-        <v>80</v>
-      </c>
-      <c r="D153" s="60">
-        <v>483450</v>
+        <v>95</v>
+      </c>
+      <c r="D153" s="59">
+        <v>236953</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C154" t="s">
-        <v>111</v>
-      </c>
-      <c r="D154" s="60">
-        <v>478200</v>
+        <v>80</v>
+      </c>
+      <c r="D154" s="59">
+        <v>483450</v>
       </c>
     </row>
     <row r="155" spans="2:4">
       <c r="B155" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C155" t="s">
-        <v>117</v>
-      </c>
-      <c r="D155" s="60">
-        <v>825771</v>
+        <v>111</v>
+      </c>
+      <c r="D155" s="59">
+        <v>478200</v>
       </c>
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C156" t="s">
-        <v>119</v>
-      </c>
-      <c r="D156" s="60">
-        <v>309171</v>
+        <v>117</v>
+      </c>
+      <c r="D156" s="59">
+        <v>825771</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C157" t="s">
-        <v>83</v>
-      </c>
-      <c r="D157" s="60">
-        <v>623704</v>
+        <v>119</v>
+      </c>
+      <c r="D157" s="59">
+        <v>309171</v>
       </c>
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C158" t="s">
-        <v>107</v>
-      </c>
-      <c r="D158" s="60">
-        <v>304227</v>
+        <v>83</v>
+      </c>
+      <c r="D158" s="59">
+        <v>623704</v>
       </c>
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C159" t="s">
-        <v>116</v>
-      </c>
-      <c r="D159" s="60">
-        <v>499783</v>
+        <v>107</v>
+      </c>
+      <c r="D159" s="59">
+        <v>304227</v>
       </c>
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C160" t="s">
-        <v>90</v>
-      </c>
-      <c r="D160" s="60">
-        <v>444881</v>
+        <v>116</v>
+      </c>
+      <c r="D160" s="59">
+        <v>499783</v>
       </c>
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C161" t="s">
-        <v>114</v>
-      </c>
-      <c r="D161" s="60">
-        <v>583943</v>
+        <v>90</v>
+      </c>
+      <c r="D161" s="59">
+        <v>444881</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C162" t="s">
-        <v>108</v>
-      </c>
-      <c r="D162" s="60">
-        <v>61388</v>
+        <v>114</v>
+      </c>
+      <c r="D162" s="59">
+        <v>583943</v>
       </c>
     </row>
     <row r="163" spans="2:4">
@@ -5032,10 +5150,10 @@
         <v>196</v>
       </c>
       <c r="C163" t="s">
-        <v>90</v>
-      </c>
-      <c r="D163" s="60">
-        <v>67822</v>
+        <v>108</v>
+      </c>
+      <c r="D163" s="59">
+        <v>61388</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5043,10 +5161,10 @@
         <v>196</v>
       </c>
       <c r="C164" t="s">
-        <v>96</v>
-      </c>
-      <c r="D164" s="60">
-        <v>1857878</v>
+        <v>90</v>
+      </c>
+      <c r="D164" s="59">
+        <v>67822</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5054,65 +5172,65 @@
         <v>196</v>
       </c>
       <c r="C165" t="s">
-        <v>90</v>
-      </c>
-      <c r="D165" s="60">
-        <v>833267</v>
+        <v>96</v>
+      </c>
+      <c r="D165" s="59">
+        <v>1857878</v>
       </c>
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C166" t="s">
-        <v>114</v>
-      </c>
-      <c r="D166" s="60">
-        <v>646387</v>
+        <v>90</v>
+      </c>
+      <c r="D166" s="59">
+        <v>833267</v>
       </c>
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C167" t="s">
         <v>114</v>
       </c>
-      <c r="D167" s="60">
-        <v>456577</v>
+      <c r="D167" s="59">
+        <v>646387</v>
       </c>
     </row>
     <row r="168" spans="2:4">
       <c r="B168" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C168" t="s">
-        <v>79</v>
-      </c>
-      <c r="D168" s="60">
-        <v>522543</v>
+        <v>114</v>
+      </c>
+      <c r="D168" s="59">
+        <v>456577</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C169" t="s">
-        <v>112</v>
-      </c>
-      <c r="D169" s="60">
-        <v>429907</v>
+        <v>79</v>
+      </c>
+      <c r="D169" s="59">
+        <v>522543</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C170" t="s">
-        <v>119</v>
-      </c>
-      <c r="D170" s="60">
-        <v>1253349</v>
+        <v>112</v>
+      </c>
+      <c r="D170" s="59">
+        <v>429907</v>
       </c>
     </row>
     <row r="171" spans="2:4">
@@ -5120,1183 +5238,1194 @@
         <v>201</v>
       </c>
       <c r="C171" t="s">
-        <v>79</v>
-      </c>
-      <c r="D171" s="60">
-        <v>615636</v>
+        <v>119</v>
+      </c>
+      <c r="D171" s="59">
+        <v>1253349</v>
       </c>
     </row>
     <row r="172" spans="2:4">
       <c r="B172" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C172" t="s">
-        <v>116</v>
-      </c>
-      <c r="D172" s="60">
-        <v>1205311</v>
+        <v>79</v>
+      </c>
+      <c r="D172" s="59">
+        <v>615636</v>
       </c>
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C173" t="s">
-        <v>96</v>
-      </c>
-      <c r="D173" s="60">
-        <v>451527</v>
+        <v>116</v>
+      </c>
+      <c r="D173" s="59">
+        <v>1205311</v>
       </c>
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C174" t="s">
-        <v>98</v>
-      </c>
-      <c r="D174" s="60">
-        <v>1769013</v>
+        <v>96</v>
+      </c>
+      <c r="D174" s="59">
+        <v>451527</v>
       </c>
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="5" t="s">
-        <v>282</v>
+        <v>204</v>
       </c>
       <c r="C175" t="s">
-        <v>120</v>
-      </c>
-      <c r="D175" s="60">
-        <v>579152</v>
+        <v>98</v>
+      </c>
+      <c r="D175" s="59">
+        <v>1769013</v>
       </c>
     </row>
     <row r="176" spans="2:4">
       <c r="B176" s="5" t="s">
-        <v>205</v>
+        <v>282</v>
       </c>
       <c r="C176" t="s">
-        <v>89</v>
-      </c>
-      <c r="D176" s="60">
-        <v>380737</v>
+        <v>120</v>
+      </c>
+      <c r="D176" s="59">
+        <v>579152</v>
       </c>
     </row>
     <row r="177" spans="2:4">
       <c r="B177" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C177" t="s">
-        <v>83</v>
-      </c>
-      <c r="D177" s="60">
-        <v>737083</v>
+        <v>89</v>
+      </c>
+      <c r="D177" s="59">
+        <v>380737</v>
       </c>
     </row>
     <row r="178" spans="2:4">
       <c r="B178" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C178" t="s">
-        <v>101</v>
-      </c>
-      <c r="D178" s="60">
-        <v>2967851</v>
+        <v>83</v>
+      </c>
+      <c r="D178" s="59">
+        <v>737083</v>
       </c>
     </row>
     <row r="179" spans="2:4">
       <c r="B179" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C179" t="s">
-        <v>111</v>
-      </c>
-      <c r="D179" s="60">
-        <v>358128</v>
+        <v>101</v>
+      </c>
+      <c r="D179" s="59">
+        <v>2967851</v>
       </c>
     </row>
     <row r="180" spans="2:4">
       <c r="B180" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C180" t="s">
-        <v>89</v>
-      </c>
-      <c r="D180" s="60">
-        <v>761561</v>
+        <v>111</v>
+      </c>
+      <c r="D180" s="59">
+        <v>358128</v>
       </c>
     </row>
     <row r="181" spans="2:4">
       <c r="B181" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C181" t="s">
-        <v>114</v>
-      </c>
-      <c r="D181" s="60">
-        <v>684874</v>
+        <v>89</v>
+      </c>
+      <c r="D181" s="59">
+        <v>761561</v>
       </c>
     </row>
     <row r="182" spans="2:4">
       <c r="B182" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C182" t="s">
-        <v>93</v>
-      </c>
-      <c r="D182" s="60">
-        <v>1333431</v>
+        <v>114</v>
+      </c>
+      <c r="D182" s="59">
+        <v>684874</v>
       </c>
     </row>
     <row r="183" spans="2:4">
       <c r="B183" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C183" t="s">
-        <v>114</v>
-      </c>
-      <c r="D183" s="60">
-        <v>295726</v>
+        <v>93</v>
+      </c>
+      <c r="D183" s="59">
+        <v>1333431</v>
       </c>
     </row>
     <row r="184" spans="2:4">
       <c r="B184" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C184" t="s">
-        <v>108</v>
-      </c>
-      <c r="D184" s="60">
-        <v>1120895</v>
+        <v>114</v>
+      </c>
+      <c r="D184" s="59">
+        <v>295726</v>
       </c>
     </row>
     <row r="185" spans="2:4">
       <c r="B185" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C185" t="s">
-        <v>91</v>
-      </c>
-      <c r="D185" s="60">
-        <v>519070</v>
+        <v>108</v>
+      </c>
+      <c r="D185" s="59">
+        <v>1120895</v>
       </c>
     </row>
     <row r="186" spans="2:4">
       <c r="B186" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C186" t="s">
-        <v>119</v>
-      </c>
-      <c r="D186" s="60">
-        <v>80285</v>
+        <v>91</v>
+      </c>
+      <c r="D186" s="59">
+        <v>519070</v>
       </c>
     </row>
     <row r="187" spans="2:4">
       <c r="B187" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C187" t="s">
-        <v>114</v>
-      </c>
-      <c r="D187" s="60">
-        <v>82526</v>
+        <v>119</v>
+      </c>
+      <c r="D187" s="59">
+        <v>80285</v>
       </c>
     </row>
     <row r="188" spans="2:4">
       <c r="B188" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C188" t="s">
-        <v>112</v>
-      </c>
-      <c r="D188" s="60">
-        <v>256257</v>
+        <v>114</v>
+      </c>
+      <c r="D188" s="59">
+        <v>82526</v>
       </c>
     </row>
     <row r="189" spans="2:4">
       <c r="B189" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C189" t="s">
-        <v>101</v>
-      </c>
-      <c r="D189" s="60">
-        <v>1010547</v>
+        <v>112</v>
+      </c>
+      <c r="D189" s="59">
+        <v>256257</v>
       </c>
     </row>
     <row r="190" spans="2:4">
       <c r="B190" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C190" t="s">
-        <v>90</v>
-      </c>
-      <c r="D190" s="60">
-        <v>1103084</v>
+        <v>101</v>
+      </c>
+      <c r="D190" s="59">
+        <v>1010547</v>
       </c>
     </row>
     <row r="191" spans="2:4">
       <c r="B191" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C191" t="s">
-        <v>119</v>
-      </c>
-      <c r="D191" s="60">
-        <v>632181</v>
+        <v>90</v>
+      </c>
+      <c r="D191" s="59">
+        <v>1103084</v>
       </c>
     </row>
     <row r="192" spans="2:4">
       <c r="B192" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C192" t="s">
         <v>119</v>
       </c>
-      <c r="D192" s="60">
-        <v>1323231</v>
+      <c r="D192" s="59">
+        <v>632181</v>
       </c>
     </row>
     <row r="193" spans="2:4">
       <c r="B193" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C193" t="s">
         <v>119</v>
       </c>
-      <c r="D193" s="60">
-        <v>1289116</v>
+      <c r="D193" s="59">
+        <v>1323231</v>
       </c>
     </row>
     <row r="194" spans="2:4">
       <c r="B194" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C194" t="s">
-        <v>82</v>
-      </c>
-      <c r="D194" s="60">
-        <v>1221243</v>
+        <v>119</v>
+      </c>
+      <c r="D194" s="59">
+        <v>1289116</v>
       </c>
     </row>
     <row r="195" spans="2:4">
       <c r="B195" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C195" t="s">
-        <v>92</v>
-      </c>
-      <c r="D195" s="60">
-        <v>939681</v>
+        <v>82</v>
+      </c>
+      <c r="D195" s="59">
+        <v>1221243</v>
       </c>
     </row>
     <row r="196" spans="2:4">
       <c r="B196" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C196" t="s">
-        <v>126</v>
-      </c>
-      <c r="D196" s="60">
-        <v>522258</v>
+        <v>92</v>
+      </c>
+      <c r="D196" s="59">
+        <v>939681</v>
       </c>
     </row>
     <row r="197" spans="2:4">
       <c r="B197" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C197" t="s">
-        <v>79</v>
-      </c>
-      <c r="D197" s="60">
-        <v>923191</v>
+        <v>126</v>
+      </c>
+      <c r="D197" s="59">
+        <v>522258</v>
       </c>
     </row>
     <row r="198" spans="2:4">
       <c r="B198" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C198" t="s">
-        <v>82</v>
-      </c>
-      <c r="D198" s="60">
-        <v>807598</v>
+        <v>79</v>
+      </c>
+      <c r="D198" s="59">
+        <v>923191</v>
       </c>
     </row>
     <row r="199" spans="2:4">
       <c r="B199" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C199" t="s">
-        <v>104</v>
-      </c>
-      <c r="D199" s="60">
-        <v>385165</v>
+        <v>82</v>
+      </c>
+      <c r="D199" s="59">
+        <v>807598</v>
       </c>
     </row>
     <row r="200" spans="2:4">
       <c r="B200" s="5" t="s">
-        <v>283</v>
+        <v>228</v>
       </c>
       <c r="C200" t="s">
-        <v>80</v>
-      </c>
-      <c r="D200" s="60">
-        <v>768127</v>
+        <v>104</v>
+      </c>
+      <c r="D200" s="59">
+        <v>385165</v>
       </c>
     </row>
     <row r="201" spans="2:4">
       <c r="B201" s="5" t="s">
-        <v>229</v>
+        <v>283</v>
       </c>
       <c r="C201" t="s">
-        <v>101</v>
-      </c>
-      <c r="D201" s="60">
-        <v>1557125</v>
+        <v>80</v>
+      </c>
+      <c r="D201" s="59">
+        <v>768127</v>
       </c>
     </row>
     <row r="202" spans="2:4">
       <c r="B202" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C202" t="s">
-        <v>122</v>
-      </c>
-      <c r="D202" s="60">
-        <v>807553</v>
+        <v>101</v>
+      </c>
+      <c r="D202" s="59">
+        <v>1557125</v>
       </c>
     </row>
     <row r="203" spans="2:4">
       <c r="B203" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C203" t="s">
-        <v>118</v>
-      </c>
-      <c r="D203" s="60">
-        <v>814743</v>
+        <v>122</v>
+      </c>
+      <c r="D203" s="59">
+        <v>807553</v>
       </c>
     </row>
     <row r="204" spans="2:4">
       <c r="B204" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C204" t="s">
-        <v>98</v>
-      </c>
-      <c r="D204" s="60">
-        <v>1429412</v>
+        <v>118</v>
+      </c>
+      <c r="D204" s="59">
+        <v>814743</v>
       </c>
     </row>
     <row r="205" spans="2:4">
       <c r="B205" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C205" t="s">
-        <v>86</v>
-      </c>
-      <c r="D205" s="60">
-        <v>361182</v>
+        <v>98</v>
+      </c>
+      <c r="D205" s="59">
+        <v>1429412</v>
       </c>
     </row>
     <row r="206" spans="2:4">
       <c r="B206" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C206" t="s">
         <v>86</v>
       </c>
-      <c r="D206" s="60">
-        <v>567263</v>
+      <c r="D206" s="59">
+        <v>361182</v>
       </c>
     </row>
     <row r="207" spans="2:4">
       <c r="B207" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C207" t="s">
         <v>86</v>
       </c>
-      <c r="D207" s="60">
-        <v>1093105</v>
+      <c r="D207" s="59">
+        <v>567263</v>
       </c>
     </row>
     <row r="208" spans="2:4">
       <c r="B208" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C208" t="s">
-        <v>82</v>
-      </c>
-      <c r="D208" s="60">
-        <v>527013</v>
+        <v>86</v>
+      </c>
+      <c r="D208" s="59">
+        <v>1093105</v>
       </c>
     </row>
     <row r="209" spans="1:19">
       <c r="B209" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C209" t="s">
+        <v>82</v>
+      </c>
+      <c r="D209" s="59">
+        <v>527013</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19">
+      <c r="B210" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C209" t="s">
+      <c r="C210" t="s">
         <v>119</v>
       </c>
-      <c r="D209" s="60">
+      <c r="D210" s="59">
         <v>818238</v>
       </c>
     </row>
-    <row r="210" spans="1:19">
-      <c r="B210" s="8" t="s">
+    <row r="211" spans="1:19">
+      <c r="B211" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C210" s="9" t="s">
+      <c r="C211" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D210" s="37">
+      <c r="D211" s="36">
         <v>250489</v>
       </c>
     </row>
-    <row r="211" spans="1:19">
-      <c r="B211" s="12" t="s">
+    <row r="212" spans="1:19">
+      <c r="B212" s="12" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="213" spans="1:19">
-      <c r="A213" s="1"/>
-      <c r="B213" s="1"/>
-      <c r="C213" s="1"/>
-      <c r="D213" s="1"/>
-      <c r="E213" s="1"/>
-      <c r="F213" s="1"/>
-      <c r="G213" s="1"/>
-      <c r="H213" s="1"/>
-      <c r="I213" s="1"/>
-      <c r="J213" s="1"/>
-      <c r="K213" s="1"/>
-      <c r="L213" s="1"/>
-      <c r="M213" s="1"/>
-      <c r="N213" s="1"/>
-      <c r="O213" s="1"/>
-      <c r="P213" s="1"/>
-      <c r="Q213" s="1"/>
-      <c r="R213" s="1"/>
-      <c r="S213" s="1"/>
-    </row>
-    <row r="215" spans="1:19" ht="24">
-      <c r="B215" s="3" t="s">
+    <row r="214" spans="1:19">
+      <c r="A214" s="1"/>
+      <c r="B214" s="1"/>
+      <c r="C214" s="1"/>
+      <c r="D214" s="1"/>
+      <c r="E214" s="1"/>
+      <c r="F214" s="1"/>
+      <c r="G214" s="1"/>
+      <c r="H214" s="1"/>
+      <c r="I214" s="1"/>
+      <c r="J214" s="1"/>
+      <c r="K214" s="1"/>
+      <c r="L214" s="1"/>
+      <c r="M214" s="1"/>
+      <c r="N214" s="1"/>
+      <c r="O214" s="1"/>
+      <c r="P214" s="1"/>
+      <c r="Q214" s="1"/>
+      <c r="R214" s="1"/>
+      <c r="S214" s="1"/>
+    </row>
+    <row r="216" spans="1:19" ht="24">
+      <c r="B216" s="3" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="216" spans="1:19" ht="19">
-      <c r="B216" s="26" t="s">
+    <row r="217" spans="1:19" ht="19">
+      <c r="B217" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="H216" s="26" t="s">
+      <c r="H217" s="26" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="217" spans="1:19">
-      <c r="B217" s="14" t="s">
+    <row r="218" spans="1:19">
+      <c r="B218" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C217" s="16" t="s">
+      <c r="C218" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="H217" s="14" t="s">
+      <c r="H218" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="I217" s="16" t="s">
+      <c r="I218" s="16" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="218" spans="1:19">
-      <c r="B218" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C218" s="31">
-        <v>3258</v>
-      </c>
-      <c r="H218" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="I218" s="60">
-        <f>SUMIF($B$218:$B$238,H218,$C$218:$C$238)</f>
-        <v>3258</v>
       </c>
     </row>
     <row r="219" spans="1:19">
       <c r="B219" s="18" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="C219" s="31">
-        <v>5790</v>
+        <v>3258</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I219" s="60">
-        <f t="shared" ref="I219:I236" si="6">SUMIF($B$218:$B$238,H219,$C$218:$C$238)</f>
-        <v>5790</v>
+        <v>138</v>
+      </c>
+      <c r="I219" s="59">
+        <f>SUMIF($B$219:$B$239,H219,$C$219:$C$239)</f>
+        <v>3258</v>
       </c>
     </row>
     <row r="220" spans="1:19">
       <c r="B220" s="18" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C220" s="31">
-        <v>2531</v>
+        <v>5790</v>
       </c>
       <c r="H220" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I220" s="60">
-        <f t="shared" si="6"/>
-        <v>2531</v>
+        <v>114</v>
+      </c>
+      <c r="I220" s="59">
+        <f t="shared" ref="I220:I237" si="11">SUMIF($B$219:$B$239,H220,$C$219:$C$239)</f>
+        <v>5790</v>
       </c>
     </row>
     <row r="221" spans="1:19">
       <c r="B221" s="18" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="C221" s="31">
-        <v>5679</v>
+        <v>2531</v>
       </c>
       <c r="H221" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="I221" s="60">
-        <f t="shared" si="6"/>
-        <v>5679</v>
+        <v>89</v>
+      </c>
+      <c r="I221" s="59">
+        <f t="shared" si="11"/>
+        <v>2531</v>
       </c>
     </row>
     <row r="222" spans="1:19">
       <c r="B222" s="18" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C222" s="31">
-        <v>5738</v>
+        <v>5679</v>
       </c>
       <c r="H222" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="I222" s="60">
-        <f t="shared" si="6"/>
-        <v>5738</v>
+        <v>136</v>
+      </c>
+      <c r="I222" s="59">
+        <f t="shared" si="11"/>
+        <v>5679</v>
       </c>
     </row>
     <row r="223" spans="1:19">
       <c r="B223" s="18" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="C223" s="31">
-        <v>4285</v>
+        <v>5738</v>
       </c>
       <c r="H223" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="I223" s="60">
-        <f t="shared" si="6"/>
-        <v>4285</v>
+        <v>98</v>
+      </c>
+      <c r="I223" s="59">
+        <f t="shared" si="11"/>
+        <v>5738</v>
       </c>
     </row>
     <row r="224" spans="1:19">
       <c r="B224" s="18" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="C224" s="31">
-        <v>3172</v>
+        <v>4285</v>
       </c>
       <c r="H224" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I224" s="60">
-        <f t="shared" si="6"/>
-        <v>3172</v>
+        <v>137</v>
+      </c>
+      <c r="I224" s="59">
+        <f t="shared" si="11"/>
+        <v>4285</v>
       </c>
     </row>
     <row r="225" spans="2:9">
       <c r="B225" s="18" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C225" s="31">
-        <v>11227</v>
+        <v>3172</v>
       </c>
       <c r="H225" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="I225" s="60">
-        <f t="shared" si="6"/>
-        <v>11227</v>
+        <v>92</v>
+      </c>
+      <c r="I225" s="59">
+        <f t="shared" si="11"/>
+        <v>3172</v>
       </c>
     </row>
     <row r="226" spans="2:9">
       <c r="B226" s="18" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C226" s="31">
-        <v>10540</v>
+        <v>11227</v>
       </c>
       <c r="H226" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="I226" s="60">
-        <f t="shared" si="6"/>
-        <v>10540</v>
+        <v>101</v>
+      </c>
+      <c r="I226" s="59">
+        <f t="shared" si="11"/>
+        <v>11227</v>
       </c>
     </row>
     <row r="227" spans="2:9">
       <c r="B227" s="18" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="C227" s="31">
-        <v>7930</v>
+        <v>10540</v>
       </c>
       <c r="H227" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I227" s="60">
-        <f t="shared" si="6"/>
-        <v>7930</v>
+        <v>86</v>
+      </c>
+      <c r="I227" s="59">
+        <f t="shared" si="11"/>
+        <v>10540</v>
       </c>
     </row>
     <row r="228" spans="2:9">
       <c r="B228" s="18" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C228" s="31">
-        <v>5666</v>
+        <v>7930</v>
       </c>
       <c r="H228" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="I228" s="60">
-        <f t="shared" si="6"/>
-        <v>5666</v>
+        <v>135</v>
+      </c>
+      <c r="I228" s="59">
+        <f t="shared" si="11"/>
+        <v>7930</v>
       </c>
     </row>
     <row r="229" spans="2:9">
       <c r="B229" s="18" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C229" s="31">
-        <v>10124</v>
+        <v>5666</v>
       </c>
       <c r="H229" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="I229" s="60">
-        <f t="shared" si="6"/>
-        <v>10124</v>
+        <v>116</v>
+      </c>
+      <c r="I229" s="59">
+        <f t="shared" si="11"/>
+        <v>5666</v>
       </c>
     </row>
     <row r="230" spans="2:9">
       <c r="B230" s="18" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C230" s="31">
-        <v>3615</v>
+        <v>10124</v>
       </c>
       <c r="H230" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I230" s="60">
-        <f t="shared" si="6"/>
-        <v>3615</v>
+        <v>131</v>
+      </c>
+      <c r="I230" s="59">
+        <f t="shared" si="11"/>
+        <v>10124</v>
       </c>
     </row>
     <row r="231" spans="2:9">
       <c r="B231" s="18" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C231" s="31">
-        <v>8140</v>
+        <v>3615</v>
       </c>
       <c r="H231" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="I231" s="60">
-        <f>SUM(C231+C232)</f>
-        <v>15760</v>
+        <v>133</v>
+      </c>
+      <c r="I231" s="59">
+        <f t="shared" si="11"/>
+        <v>3615</v>
       </c>
     </row>
     <row r="232" spans="2:9">
       <c r="B232" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C232" s="31">
-        <v>7620</v>
+        <v>8140</v>
       </c>
       <c r="H232" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="I232" s="60">
-        <f t="shared" si="6"/>
-        <v>3375</v>
+        <v>119</v>
+      </c>
+      <c r="I232" s="59">
+        <f>SUM(C232+C233)</f>
+        <v>15760</v>
       </c>
     </row>
     <row r="233" spans="2:9">
       <c r="B233" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C233" s="31">
+        <v>7620</v>
+      </c>
+      <c r="H233" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C233" s="31">
+      <c r="I233" s="59">
+        <f t="shared" si="11"/>
         <v>3375</v>
-      </c>
-      <c r="H233" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I233" s="60">
-        <f t="shared" si="6"/>
-        <v>4275</v>
       </c>
     </row>
     <row r="234" spans="2:9">
       <c r="B234" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="C234" s="31">
+        <v>3375</v>
+      </c>
+      <c r="H234" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C234" s="31">
+      <c r="I234" s="59">
+        <f t="shared" si="11"/>
         <v>4275</v>
-      </c>
-      <c r="H234" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="I234" s="60">
-        <f t="shared" si="6"/>
-        <v>3201</v>
       </c>
     </row>
     <row r="235" spans="2:9">
       <c r="B235" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C235" s="31">
+        <v>4275</v>
+      </c>
+      <c r="H235" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C235" s="31">
+      <c r="I235" s="59">
+        <f t="shared" si="11"/>
         <v>3201</v>
-      </c>
-      <c r="H235" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="I235" s="60">
-        <f t="shared" si="6"/>
-        <v>11300</v>
       </c>
     </row>
     <row r="236" spans="2:9">
       <c r="B236" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C236" s="31">
-        <v>0</v>
+        <v>3201</v>
       </c>
       <c r="H236" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="I236" s="60">
-        <f t="shared" si="6"/>
-        <v>2563</v>
+        <v>82</v>
+      </c>
+      <c r="I236" s="59">
+        <f t="shared" si="11"/>
+        <v>11300</v>
       </c>
     </row>
     <row r="237" spans="2:9">
       <c r="B237" s="18" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="C237" s="31">
-        <v>11300</v>
-      </c>
-      <c r="H237" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="I237" s="37">
-        <f>SUM(I218:I236)</f>
-        <v>120029</v>
+        <v>0</v>
+      </c>
+      <c r="H237" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I237" s="59">
+        <f t="shared" si="11"/>
+        <v>2563</v>
       </c>
     </row>
     <row r="238" spans="2:9">
       <c r="B238" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C238" s="31">
+        <v>11300</v>
+      </c>
+      <c r="H238" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I238" s="36">
+        <f>SUM(I219:I237)</f>
+        <v>120029</v>
+      </c>
+    </row>
+    <row r="239" spans="2:9">
+      <c r="B239" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C238" s="31">
+      <c r="C239" s="31">
         <v>2563</v>
       </c>
     </row>
-    <row r="239" spans="2:9">
-      <c r="B239" s="32" t="s">
+    <row r="240" spans="2:9">
+      <c r="B240" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="C239" s="33">
-        <f>SUM(C218:C238)</f>
+      <c r="C240" s="33">
+        <f>SUM(C219:C239)</f>
         <v>120029</v>
       </c>
     </row>
-    <row r="240" spans="2:9">
-      <c r="B240" s="13" t="s">
+    <row r="241" spans="1:19">
+      <c r="B241" s="13" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="242" spans="1:19">
-      <c r="A242" s="1"/>
-      <c r="B242" s="1"/>
-      <c r="C242" s="1"/>
-      <c r="D242" s="1"/>
-      <c r="E242" s="1"/>
-      <c r="F242" s="1"/>
-      <c r="G242" s="1"/>
-      <c r="H242" s="1"/>
-      <c r="I242" s="1"/>
-      <c r="J242" s="1"/>
-      <c r="K242" s="1"/>
-      <c r="L242" s="1"/>
-      <c r="M242" s="1"/>
-      <c r="N242" s="1"/>
-      <c r="O242" s="1"/>
-      <c r="P242" s="1"/>
-      <c r="Q242" s="1"/>
-      <c r="R242" s="1"/>
-      <c r="S242" s="1"/>
-    </row>
-    <row r="244" spans="1:19" ht="24">
-      <c r="B244" s="3" t="s">
+    <row r="243" spans="1:19">
+      <c r="A243" s="1"/>
+      <c r="B243" s="1"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1"/>
+      <c r="E243" s="1"/>
+      <c r="F243" s="1"/>
+      <c r="G243" s="1"/>
+      <c r="H243" s="1"/>
+      <c r="I243" s="1"/>
+      <c r="J243" s="1"/>
+      <c r="K243" s="1"/>
+      <c r="L243" s="1"/>
+      <c r="M243" s="1"/>
+      <c r="N243" s="1"/>
+      <c r="O243" s="1"/>
+      <c r="P243" s="1"/>
+      <c r="Q243" s="1"/>
+      <c r="R243" s="1"/>
+      <c r="S243" s="1"/>
+    </row>
+    <row r="245" spans="1:19" ht="24">
+      <c r="B245" s="3" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="245" spans="1:19" ht="19">
-      <c r="B245" s="26" t="s">
+    <row r="246" spans="1:19" ht="19">
+      <c r="B246" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="H245" s="26" t="s">
+      <c r="H246" s="26" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="246" spans="1:19">
-      <c r="B246" s="14" t="s">
+    <row r="247" spans="1:19">
+      <c r="B247" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C246" s="16" t="s">
+      <c r="C247" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="H246" s="14" t="s">
+      <c r="H247" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="I246" s="16" t="s">
+      <c r="I247" s="16" t="s">
         <v>252</v>
-      </c>
-    </row>
-    <row r="247" spans="1:19">
-      <c r="B247" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C247" s="31">
-        <v>4</v>
-      </c>
-      <c r="H247" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="I247" s="28">
-        <f>SUMIF($B$247:$B$267,H247,$C$247:$C$267)</f>
-        <v>4</v>
       </c>
     </row>
     <row r="248" spans="1:19">
       <c r="B248" s="18" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="C248" s="31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H248" s="5" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="I248" s="28">
-        <f t="shared" ref="I248:I265" si="7">SUMIF($B$247:$B$267,H248,$C$247:$C$267)</f>
-        <v>7</v>
+        <f>SUMIF($B$248:$B$268,H248,$C$248:$C$268)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="249" spans="1:19">
       <c r="B249" s="18" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C249" s="31">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H249" s="5" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="I249" s="28">
-        <f t="shared" si="7"/>
-        <v>3</v>
+        <f t="shared" ref="I249:I266" si="12">SUMIF($B$248:$B$268,H249,$C$248:$C$268)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="250" spans="1:19">
       <c r="B250" s="18" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="C250" s="31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H250" s="5" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="I250" s="28">
-        <f t="shared" si="7"/>
-        <v>6</v>
+        <f t="shared" si="12"/>
+        <v>3</v>
       </c>
     </row>
     <row r="251" spans="1:19">
       <c r="B251" s="18" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C251" s="31">
-        <v>3</v>
-      </c>
-      <c r="H251" s="57" t="s">
-        <v>98</v>
+        <v>6</v>
+      </c>
+      <c r="H251" s="5" t="s">
+        <v>136</v>
       </c>
       <c r="I251" s="28">
-        <f t="shared" si="7"/>
-        <v>3</v>
+        <f t="shared" si="12"/>
+        <v>6</v>
       </c>
     </row>
     <row r="252" spans="1:19">
       <c r="B252" s="18" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="C252" s="31">
-        <v>4</v>
-      </c>
-      <c r="H252" s="5" t="s">
-        <v>137</v>
+        <v>3</v>
+      </c>
+      <c r="H252" s="56" t="s">
+        <v>98</v>
       </c>
       <c r="I252" s="28">
-        <f t="shared" si="7"/>
-        <v>4</v>
+        <f t="shared" si="12"/>
+        <v>3</v>
       </c>
     </row>
     <row r="253" spans="1:19">
       <c r="B253" s="18" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="C253" s="31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H253" s="5" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="I253" s="28">
-        <f t="shared" si="7"/>
-        <v>2</v>
+        <f t="shared" si="12"/>
+        <v>4</v>
       </c>
     </row>
     <row r="254" spans="1:19">
       <c r="B254" s="18" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C254" s="31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H254" s="5" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="I254" s="28">
-        <f t="shared" si="7"/>
-        <v>5</v>
+        <f t="shared" si="12"/>
+        <v>2</v>
       </c>
     </row>
     <row r="255" spans="1:19">
       <c r="B255" s="18" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C255" s="31">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H255" s="5" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="I255" s="28">
-        <f t="shared" si="7"/>
-        <v>8</v>
+        <f t="shared" si="12"/>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:19">
       <c r="B256" s="18" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="C256" s="31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H256" s="5" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="I256" s="28">
-        <f t="shared" si="7"/>
-        <v>6</v>
+        <f t="shared" si="12"/>
+        <v>8</v>
       </c>
     </row>
     <row r="257" spans="2:9">
       <c r="B257" s="18" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C257" s="31">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H257" s="5" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="I257" s="28">
-        <f t="shared" si="7"/>
-        <v>3</v>
+        <f t="shared" si="12"/>
+        <v>6</v>
       </c>
     </row>
     <row r="258" spans="2:9">
       <c r="B258" s="18" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C258" s="31">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H258" s="5" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="I258" s="28">
-        <f t="shared" si="7"/>
-        <v>8</v>
+        <f t="shared" si="12"/>
+        <v>3</v>
       </c>
     </row>
     <row r="259" spans="2:9">
       <c r="B259" s="18" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C259" s="31">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H259" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I259" s="28">
-        <f t="shared" si="7"/>
-        <v>4</v>
+        <f t="shared" si="12"/>
+        <v>8</v>
       </c>
     </row>
     <row r="260" spans="2:9">
       <c r="B260" s="18" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C260" s="31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H260" s="5" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="I260" s="28">
-        <f>SUM(C260:C261)</f>
-        <v>12</v>
+        <f t="shared" si="12"/>
+        <v>4</v>
       </c>
     </row>
     <row r="261" spans="2:9">
       <c r="B261" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C261" s="31">
         <v>6</v>
       </c>
       <c r="H261" s="5" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="I261" s="28">
-        <f t="shared" si="7"/>
-        <v>4</v>
+        <f>SUM(C261:C262)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="262" spans="2:9">
       <c r="B262" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C262" s="31">
+        <v>6</v>
+      </c>
+      <c r="H262" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C262" s="31">
-        <v>4</v>
-      </c>
-      <c r="H262" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="I262" s="28">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
     </row>
     <row r="263" spans="2:9">
       <c r="B263" s="18" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C263" s="31">
         <v>4</v>
       </c>
       <c r="H263" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="I263" s="28">
-        <f t="shared" si="7"/>
-        <v>5</v>
+        <f t="shared" si="12"/>
+        <v>4</v>
       </c>
     </row>
     <row r="264" spans="2:9">
       <c r="B264" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C264" s="31">
+        <v>4</v>
+      </c>
+      <c r="H264" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C264" s="31">
+      <c r="I264" s="28">
+        <f t="shared" si="12"/>
         <v>5</v>
-      </c>
-      <c r="H264" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="I264" s="28">
-        <f t="shared" si="7"/>
-        <v>7</v>
       </c>
     </row>
     <row r="265" spans="2:9">
       <c r="B265" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C265" s="31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H265" s="5" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="I265" s="28">
-        <f t="shared" si="7"/>
-        <v>4</v>
+        <f t="shared" si="12"/>
+        <v>7</v>
       </c>
     </row>
     <row r="266" spans="2:9">
       <c r="B266" s="18" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="C266" s="31">
-        <v>7</v>
-      </c>
-      <c r="H266" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="I266" s="29">
-        <f>SUM(I247:I265)</f>
-        <v>99</v>
+        <v>0</v>
+      </c>
+      <c r="H266" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I266" s="28">
+        <f t="shared" si="12"/>
+        <v>4</v>
       </c>
     </row>
     <row r="267" spans="2:9">
       <c r="B267" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C267" s="31">
+        <v>7</v>
+      </c>
+      <c r="H267" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I267" s="29">
+        <f>SUM(I248:I266)</f>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="268" spans="2:9">
+      <c r="B268" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C267" s="31">
+      <c r="C268" s="31">
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="2:9">
-      <c r="B268" s="32" t="s">
+    <row r="269" spans="2:9">
+      <c r="B269" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="C268" s="33">
-        <f>SUM(C247:C267)</f>
+      <c r="C269" s="33">
+        <f>SUM(C248:C268)</f>
         <v>99</v>
       </c>
     </row>
-    <row r="269" spans="2:9">
-      <c r="B269" s="12" t="s">
+    <row r="270" spans="2:9">
+      <c r="B270" s="12" t="s">
         <v>150</v>
       </c>
     </row>
@@ -6305,11 +6434,11 @@
     <mergeCell ref="B5:G5"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B85" r:id="rId1" display="(1) Source: USGS Minerals Yearbook 2023, Stone (Crushed)" xr:uid="{548A430C-0933-BD46-A04D-233F7DCA4B56}"/>
-    <hyperlink ref="B114" r:id="rId2" xr:uid="{4B034E86-59D1-304B-8834-F1902822A2FF}"/>
-    <hyperlink ref="B211" r:id="rId3" xr:uid="{176BB449-00A6-5A4B-9A59-B49C345D7031}"/>
-    <hyperlink ref="B240" r:id="rId4" xr:uid="{F2BB5557-79DD-B342-AB22-1D24B525ACC2}"/>
-    <hyperlink ref="B269" r:id="rId5" xr:uid="{50D54AA6-37A8-4F43-94FB-1A76AEB23900}"/>
+    <hyperlink ref="B86" r:id="rId1" display="(1) Source: USGS Minerals Yearbook 2023, Stone (Crushed)" xr:uid="{548A430C-0933-BD46-A04D-233F7DCA4B56}"/>
+    <hyperlink ref="B115" r:id="rId2" xr:uid="{4B034E86-59D1-304B-8834-F1902822A2FF}"/>
+    <hyperlink ref="B212" r:id="rId3" xr:uid="{176BB449-00A6-5A4B-9A59-B49C345D7031}"/>
+    <hyperlink ref="B241" r:id="rId4" xr:uid="{F2BB5557-79DD-B342-AB22-1D24B525ACC2}"/>
+    <hyperlink ref="B270" r:id="rId5" xr:uid="{50D54AA6-37A8-4F43-94FB-1A76AEB23900}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -6546,7 +6675,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39DB559A-5247-2C42-B0F2-E0D90400AC57}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="35.6640625" customWidth="1"/>
@@ -6555,7 +6684,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="str" cm="1">
-        <f t="array" ref="A1:F20">'V3. Disaggregation Proxies'!B8:G27</f>
+        <f t="array" ref="A1:F21">'V3. Disaggregation Proxies'!B8:G28</f>
         <v>District</v>
       </c>
       <c r="B1" t="str">
@@ -6619,7 +6748,7 @@
         <v>Illinois</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>–</v>
       </c>
       <c r="C4">
         <v>1.52000365990347E-2</v>
@@ -6659,7 +6788,7 @@
         <v>Michigan</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>–</v>
       </c>
       <c r="C6">
         <v>5.4646933687124005E-2</v>
@@ -6679,7 +6808,7 @@
         <v>Iowa, Nebraska, South Dakota</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>–</v>
       </c>
       <c r="C7">
         <v>4.1036667657890526E-2</v>
@@ -6699,7 +6828,7 @@
         <v>Kansas</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>–</v>
       </c>
       <c r="C8">
         <v>3.1772536999336645E-2</v>
@@ -6759,7 +6888,7 @@
         <v>Georgia, Maryland, Virginia, West Virginia</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>–</v>
       </c>
       <c r="C11">
         <v>6.862319006336208E-2</v>
@@ -6799,7 +6928,7 @@
         <v>Alabama, Kentucky, Tennessee</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>–</v>
       </c>
       <c r="C13">
         <v>9.0273806528352818E-2</v>
@@ -6819,7 +6948,7 @@
         <v>Arkansas and Oklahoma</v>
       </c>
       <c r="B14" t="str">
-        <v/>
+        <v>–</v>
       </c>
       <c r="C14">
         <v>2.5550701100258481E-2</v>
@@ -6859,7 +6988,7 @@
         <v>Arizona and New Mexico</v>
       </c>
       <c r="B16" t="str">
-        <v/>
+        <v>–</v>
       </c>
       <c r="C16">
         <v>3.4734771370405107E-2</v>
@@ -6879,7 +7008,7 @@
         <v>Colorado and Wyoming</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>–</v>
       </c>
       <c r="C17">
         <v>3.2149964544685133E-2</v>
@@ -6899,7 +7028,7 @@
         <v>Montana, Nevada, Utah</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>–</v>
       </c>
       <c r="C18">
         <v>2.8021135942539514E-2</v>
@@ -6939,7 +7068,7 @@
         <v>Oregon and Washington</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>–</v>
       </c>
       <c r="C20">
         <v>1.6675435185396985E-2</v>
@@ -6952,6 +7081,26 @@
       </c>
       <c r="F20">
         <v>4.0404040404040407E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="str">
+        <v>Mean Absolute Error (MAE)</v>
+      </c>
+      <c r="B21" t="str">
+        <v>–</v>
+      </c>
+      <c r="C21">
+        <v>1.4183702408258074E-2</v>
+      </c>
+      <c r="D21">
+        <v>1.29232563020239E-2</v>
+      </c>
+      <c r="E21">
+        <v>2.0382343244322018E-2</v>
+      </c>
+      <c r="F21">
+        <v>3.3091414141414144E-2</v>
       </c>
     </row>
   </sheetData>
